--- a/Base_DP.xlsx
+++ b/Base_DP.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\USUARIO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEF03CF5-197C-438F-BAF9-DC1CB4E184FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{27E0575E-B6AC-4C09-9E43-3E041ED63075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-3345" windowWidth="29040" windowHeight="15720" xr2:uid="{8E2DDD2B-FB0B-43D7-BEBE-7B75A2E2565E}"/>
+    <workbookView xWindow="20370" yWindow="-3345" windowWidth="29040" windowHeight="15720" xr2:uid="{525D4D22-31C3-47D6-A01E-494618E018D1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Navegador de incidentes_16_10_2" sheetId="1" r:id="rId1"/>
+    <sheet name="Navegador de incidentes_17_10_2" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1972" uniqueCount="521">
-  <si>
-    <t>Navegador de incidentesNavegador de incidentes-16/10/2026 15:21:00.019</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="534">
+  <si>
+    <t>Navegador de incidentesNavegador de incidentes-17/10/2026 08:52:35.323</t>
   </si>
   <si>
     <t>AND Instrucción contiene dp</t>
@@ -256,6 +256,9 @@
     <t>Alimentador/Troncal MT</t>
   </si>
   <si>
+    <t>Sí</t>
+  </si>
+  <si>
     <t>DP-BT</t>
   </si>
   <si>
@@ -361,12 +364,12 @@
     <t>BOLM-369 (M-20A); DP-CA-S-NorteTolima</t>
   </si>
   <si>
+    <t>LIBANO 3 13.2 KV; ARRIEROS CTO 1; ARRIEROS LIBANO 34.5 kV; LIBANO 34.5 KV</t>
+  </si>
+  <si>
     <t>OTR</t>
   </si>
   <si>
-    <t>Sí</t>
-  </si>
-  <si>
     <t>No restablecido</t>
   </si>
   <si>
@@ -541,6 +544,9 @@
     <t>NUEVA CAJAMARCA</t>
   </si>
   <si>
+    <t>BOLV-303</t>
+  </si>
+  <si>
     <t>(-8402147.2, 483370.1)</t>
   </si>
   <si>
@@ -667,7 +673,7 @@
     <t>BOLM-309 (I-9); CUAD-302</t>
   </si>
   <si>
-    <t>Finalizada; Iniciada</t>
+    <t>Finalizada; Finalizada</t>
   </si>
   <si>
     <t>(-8363526.4, 500943.5)</t>
@@ -766,297 +772,294 @@
     <t>BOLM-320; CUAD-356</t>
   </si>
   <si>
+    <t>Cancelada; Finalizada</t>
+  </si>
+  <si>
+    <t>L2 L3</t>
+  </si>
+  <si>
+    <t>(-8351584.2, 558510.3)</t>
+  </si>
+  <si>
+    <t>CORE\avalenciac</t>
+  </si>
+  <si>
+    <t>VDA PATIBURRI</t>
+  </si>
+  <si>
+    <t>INC 146609774</t>
+  </si>
+  <si>
+    <t>INC 146608782</t>
+  </si>
+  <si>
+    <t>SAC329071</t>
+  </si>
+  <si>
+    <t>BRISAS 3 13.2 KV</t>
+  </si>
+  <si>
+    <t>BRISAS</t>
+  </si>
+  <si>
+    <t>Alta vegetación</t>
+  </si>
+  <si>
+    <t>CUAD-306</t>
+  </si>
+  <si>
+    <t>Finalizada</t>
+  </si>
+  <si>
+    <t>(-8377753.2, 491504.4)</t>
+  </si>
+  <si>
+    <t>VDA BOQUERON RANCHO TOLEDO</t>
+  </si>
+  <si>
+    <t>INC 146609886</t>
+  </si>
+  <si>
+    <t>SAC199981</t>
+  </si>
+  <si>
+    <t>ARRIEROS CTO 1</t>
+  </si>
+  <si>
+    <t>66631672A</t>
+  </si>
+  <si>
+    <t>LRD</t>
+  </si>
+  <si>
+    <t>(-8352029.2, 556608.0)</t>
+  </si>
+  <si>
+    <t>VDA EL CIRPE FCA TERAMA</t>
+  </si>
+  <si>
+    <t>INC 146609913</t>
+  </si>
+  <si>
+    <t>S07685</t>
+  </si>
+  <si>
+    <t>1469118A</t>
+  </si>
+  <si>
+    <t>(-8349970.3, 574469.5)</t>
+  </si>
+  <si>
+    <t>VDA LA SIERRA</t>
+  </si>
+  <si>
+    <t>INC 146610431</t>
+  </si>
+  <si>
+    <t>INC 146608671</t>
+  </si>
+  <si>
+    <t>SAC376300</t>
+  </si>
+  <si>
+    <t>PASTALES 13.2 KV</t>
+  </si>
+  <si>
+    <t>CHAPETON</t>
+  </si>
+  <si>
+    <t>CUAD-304</t>
+  </si>
+  <si>
+    <t>(-8381004.0, 500561.9)</t>
+  </si>
+  <si>
+    <t>VDA MARIA PIEDRA GRANDE VIA VALLE ESCONDIDO</t>
+  </si>
+  <si>
+    <t>INC 146611075</t>
+  </si>
+  <si>
+    <t>SAC133557</t>
+  </si>
+  <si>
+    <t>65612747A</t>
+  </si>
+  <si>
+    <t>(-8364749.7, 501022.3)</t>
+  </si>
+  <si>
+    <t>VDA CARRISALES F TESORITO</t>
+  </si>
+  <si>
+    <t>DP / BT</t>
+  </si>
+  <si>
+    <t>INC 146611166</t>
+  </si>
+  <si>
+    <t>66035670A</t>
+  </si>
+  <si>
+    <t>BOLV-396 (Apoyo); DP-CA-S-NorteTolima</t>
+  </si>
+  <si>
+    <t>66035743A</t>
+  </si>
+  <si>
+    <t>(-8346068.6, 584531.2)</t>
+  </si>
+  <si>
+    <t>VRD LA MESA</t>
+  </si>
+  <si>
+    <t>INC 146611183</t>
+  </si>
+  <si>
+    <t>66038106A</t>
+  </si>
+  <si>
+    <t>JUNIN 13.2 KV</t>
+  </si>
+  <si>
+    <t>SANTA ISABEL; LERIDA</t>
+  </si>
+  <si>
+    <t>BOLM-328 (I-28); TRAF-394</t>
+  </si>
+  <si>
+    <t>S07092</t>
+  </si>
+  <si>
+    <t>(-8352253.5, 535624.2)</t>
+  </si>
+  <si>
+    <t>VRD EL JARDIN</t>
+  </si>
+  <si>
+    <t>INC 146611720</t>
+  </si>
+  <si>
+    <t>INC 146610076</t>
+  </si>
+  <si>
+    <t>SAC264344</t>
+  </si>
+  <si>
+    <t>PIEDRAS 13.2 KV</t>
+  </si>
+  <si>
+    <t>ALVARADO</t>
+  </si>
+  <si>
+    <t>(-8335093.4, 506178.5)</t>
+  </si>
+  <si>
+    <t>VDA EL BEBEDERO LA PUNTA</t>
+  </si>
+  <si>
+    <t>INC 146612033</t>
+  </si>
+  <si>
+    <t>2227886A</t>
+  </si>
+  <si>
+    <t>S06098</t>
+  </si>
+  <si>
+    <t>(-8353595.1, 534721.2)</t>
+  </si>
+  <si>
+    <t>VDA EL JARDIN</t>
+  </si>
+  <si>
+    <t>INC 146612900</t>
+  </si>
+  <si>
+    <t>3418676-A</t>
+  </si>
+  <si>
+    <t>EL TABLAZO 13.2 KV</t>
+  </si>
+  <si>
+    <t>PADUA</t>
+  </si>
+  <si>
+    <t>(-8355263.8, 586716.2)</t>
+  </si>
+  <si>
+    <t>VDA ESPAÑA FCA COLONIA</t>
+  </si>
+  <si>
+    <t>INC 146613285</t>
+  </si>
+  <si>
+    <t>INC 146612298</t>
+  </si>
+  <si>
+    <t>S06766</t>
+  </si>
+  <si>
+    <t>VENADILLO 2 13.2 KV</t>
+  </si>
+  <si>
+    <t>VENADILLO</t>
+  </si>
+  <si>
+    <t>L1 L2 L3</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>(-8341062.9, 518346.3)</t>
+  </si>
+  <si>
+    <t>CORE\eilenis</t>
+  </si>
+  <si>
+    <t>Ramal MT</t>
+  </si>
+  <si>
+    <t>INC 146613549</t>
+  </si>
+  <si>
+    <t>66856216A</t>
+  </si>
+  <si>
+    <t>BOLV-372 (M-21B); DP-CA-S-NorteTolima</t>
+  </si>
+  <si>
+    <t>S04769</t>
+  </si>
+  <si>
+    <t>(-8343611.7, 544895.6)</t>
+  </si>
+  <si>
+    <t>VDA COLOYA</t>
+  </si>
+  <si>
+    <t>INC 146613559</t>
+  </si>
+  <si>
+    <t>66629228A</t>
+  </si>
+  <si>
+    <t>VENADILLO; SANTA ISABEL</t>
+  </si>
+  <si>
+    <t>BOLV-360; DP-CA-S-NorteTolima</t>
+  </si>
+  <si>
+    <t>RC1382</t>
+  </si>
+  <si>
+    <t>ANZOATEGUI 13.2 KV; VENADILLO 2 13.2 KV</t>
+  </si>
+  <si>
     <t>Cancelada; Pendiente</t>
   </si>
   <si>
-    <t>L2 L3</t>
-  </si>
-  <si>
-    <t>(-8351584.2, 558510.3)</t>
-  </si>
-  <si>
-    <t>CORE\avalenciac</t>
-  </si>
-  <si>
-    <t>VDA PATIBURRI</t>
-  </si>
-  <si>
-    <t>INC 146609774</t>
-  </si>
-  <si>
-    <t>INC 146608782</t>
-  </si>
-  <si>
-    <t>SAC329071</t>
-  </si>
-  <si>
-    <t>BRISAS 3 13.2 KV</t>
-  </si>
-  <si>
-    <t>BRISAS</t>
-  </si>
-  <si>
-    <t>Alta vegetación</t>
-  </si>
-  <si>
-    <t>CUAD-306</t>
-  </si>
-  <si>
-    <t>Finalizada</t>
-  </si>
-  <si>
-    <t>(-8377753.2, 491504.4)</t>
-  </si>
-  <si>
-    <t>VDA BOQUERON RANCHO TOLEDO</t>
-  </si>
-  <si>
-    <t>INC 146609886</t>
-  </si>
-  <si>
-    <t>SAC199981</t>
-  </si>
-  <si>
-    <t>ARRIEROS CTO 1</t>
-  </si>
-  <si>
-    <t>66631672A</t>
-  </si>
-  <si>
-    <t>LRD</t>
-  </si>
-  <si>
-    <t>(-8352029.2, 556608.0)</t>
-  </si>
-  <si>
-    <t>VDA EL CIRPE FCA TERAMA</t>
-  </si>
-  <si>
-    <t>INC 146609913</t>
-  </si>
-  <si>
-    <t>S07685</t>
-  </si>
-  <si>
-    <t>1469118A</t>
-  </si>
-  <si>
-    <t>MARIQUITA 4 13.2 KV; FRESNO 3 13.2 KV</t>
-  </si>
-  <si>
-    <t>(-8349970.3, 574469.5)</t>
-  </si>
-  <si>
-    <t>VDA LA SIERRA</t>
-  </si>
-  <si>
-    <t>INC 146610431</t>
-  </si>
-  <si>
-    <t>INC 146608671</t>
-  </si>
-  <si>
-    <t>SAC376300</t>
-  </si>
-  <si>
-    <t>PASTALES 13.2 KV</t>
-  </si>
-  <si>
-    <t>CHAPETON</t>
-  </si>
-  <si>
-    <t>CUAD-304</t>
-  </si>
-  <si>
-    <t>(-8381004.0, 500561.9)</t>
-  </si>
-  <si>
-    <t>VDA MARIA PIEDRA GRANDE VIA VALLE ESCONDIDO</t>
-  </si>
-  <si>
-    <t>INC 146611075</t>
-  </si>
-  <si>
-    <t>SAC133557</t>
-  </si>
-  <si>
-    <t>65612747A</t>
-  </si>
-  <si>
-    <t>Finalizada; Finalizada</t>
-  </si>
-  <si>
-    <t>(-8364749.7, 501022.3)</t>
-  </si>
-  <si>
-    <t>VDA CARRISALES F TESORITO</t>
-  </si>
-  <si>
-    <t>DP / BT</t>
-  </si>
-  <si>
-    <t>INC 146611166</t>
-  </si>
-  <si>
-    <t>66035670A</t>
-  </si>
-  <si>
-    <t>BOLV-396 (Apoyo); DP-CA-S-NorteTolima</t>
-  </si>
-  <si>
-    <t>66035743A</t>
-  </si>
-  <si>
-    <t>(-8346068.6, 584531.2)</t>
-  </si>
-  <si>
-    <t>VRD LA MESA</t>
-  </si>
-  <si>
-    <t>INC 146611183</t>
-  </si>
-  <si>
-    <t>66038106A</t>
-  </si>
-  <si>
-    <t>JUNIN 13.2 KV</t>
-  </si>
-  <si>
-    <t>SANTA ISABEL; LERIDA</t>
-  </si>
-  <si>
-    <t>BOLM-328 (I-28); TRAF-394</t>
-  </si>
-  <si>
-    <t>S07092</t>
-  </si>
-  <si>
-    <t>(-8352253.5, 535624.2)</t>
-  </si>
-  <si>
-    <t>VRD EL JARDIN</t>
-  </si>
-  <si>
-    <t>INC 146611720</t>
-  </si>
-  <si>
-    <t>INC 146610076</t>
-  </si>
-  <si>
-    <t>SAC264344</t>
-  </si>
-  <si>
-    <t>PIEDRAS 13.2 KV</t>
-  </si>
-  <si>
-    <t>ALVARADO</t>
-  </si>
-  <si>
-    <t>(-8335093.4, 506178.5)</t>
-  </si>
-  <si>
-    <t>VDA EL BEBEDERO LA PUNTA</t>
-  </si>
-  <si>
-    <t>INC 146612033</t>
-  </si>
-  <si>
-    <t>2227886A</t>
-  </si>
-  <si>
-    <t>S06098</t>
-  </si>
-  <si>
-    <t>(-8353595.1, 534721.2)</t>
-  </si>
-  <si>
-    <t>VDA EL JARDIN</t>
-  </si>
-  <si>
-    <t>INC 146612900</t>
-  </si>
-  <si>
-    <t>3418676-A</t>
-  </si>
-  <si>
-    <t>EL TABLAZO 13.2 KV</t>
-  </si>
-  <si>
-    <t>PADUA</t>
-  </si>
-  <si>
-    <t>(-8355263.8, 586716.2)</t>
-  </si>
-  <si>
-    <t>VDA ESPAÑA FCA COLONIA</t>
-  </si>
-  <si>
-    <t>INC 146613285</t>
-  </si>
-  <si>
-    <t>INC 146612298</t>
-  </si>
-  <si>
-    <t>S06766</t>
-  </si>
-  <si>
-    <t>VENADILLO 2 13.2 KV</t>
-  </si>
-  <si>
-    <t>VENADILLO</t>
-  </si>
-  <si>
-    <t>L1 L2 L3</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>(-8341062.9, 518346.3)</t>
-  </si>
-  <si>
-    <t>CORE\eilenis</t>
-  </si>
-  <si>
-    <t>Ramal MT</t>
-  </si>
-  <si>
-    <t>INC 146613549</t>
-  </si>
-  <si>
-    <t>66856216A</t>
-  </si>
-  <si>
-    <t>BOLV-372 (M-21B); DP-CA-S-NorteTolima</t>
-  </si>
-  <si>
-    <t>S04769</t>
-  </si>
-  <si>
-    <t>(-8343611.7, 544895.6)</t>
-  </si>
-  <si>
-    <t>VDA COLOYA</t>
-  </si>
-  <si>
-    <t>INC 146613559</t>
-  </si>
-  <si>
-    <t>66629228A</t>
-  </si>
-  <si>
-    <t>VENADILLO; SANTA ISABEL</t>
-  </si>
-  <si>
-    <t>BOLV-360; DP-CA-S-NorteTolima</t>
-  </si>
-  <si>
-    <t>RC1382</t>
-  </si>
-  <si>
-    <t>ANZOATEGUI 13.2 KV; VENADILLO 2 13.2 KV</t>
-  </si>
-  <si>
     <t>(-8344869.9, 520745.2)</t>
   </si>
   <si>
@@ -1084,6 +1087,27 @@
     <t>VDA EL CURAL SAN ISIDRO</t>
   </si>
   <si>
+    <t>INC 146614215</t>
+  </si>
+  <si>
+    <t>MP30491A</t>
+  </si>
+  <si>
+    <t>LIBANO 2 13.2 KV</t>
+  </si>
+  <si>
+    <t>Error de operación en Campo</t>
+  </si>
+  <si>
+    <t>LIBANO 2 13.2 KV; LIBANO 5 13.2 KV</t>
+  </si>
+  <si>
+    <t>(-8355912.2, 548391.9)</t>
+  </si>
+  <si>
+    <t>CRA 8</t>
+  </si>
+  <si>
     <t>INC 146614536</t>
   </si>
   <si>
@@ -1243,24 +1267,6 @@
     <t>VDA SAN LORENZO BAJO</t>
   </si>
   <si>
-    <t>INC 146615663</t>
-  </si>
-  <si>
-    <t>1997653-A</t>
-  </si>
-  <si>
-    <t>MARIQUITA 1 13.2 KV</t>
-  </si>
-  <si>
-    <t>BOLV-368 (M-19B)</t>
-  </si>
-  <si>
-    <t>(-8343116.5, 575702.1)</t>
-  </si>
-  <si>
-    <t>VDA SAN DIEGO</t>
-  </si>
-  <si>
     <t>INC 146615729</t>
   </si>
   <si>
@@ -1456,6 +1462,9 @@
     <t>L250</t>
   </si>
   <si>
+    <t>ARRIEROS CTO 1; ARRIEROS LIBANO 34.5 kV; LIBANO 3 13.2 KV; LIBANO 34.5 KV</t>
+  </si>
+  <si>
     <t>RSL; VCD</t>
   </si>
   <si>
@@ -1522,28 +1531,58 @@
     <t>VDA LA SIERRA S/E RIORECIO</t>
   </si>
   <si>
-    <t>INC 146617640</t>
-  </si>
-  <si>
-    <t>66588920A</t>
-  </si>
-  <si>
-    <t>LA MIEL 2 13.2 KV</t>
-  </si>
-  <si>
-    <t>LA MIEL</t>
-  </si>
-  <si>
-    <t>BOLV-333 (M-8A); DP-CA-S-CentroTolima</t>
-  </si>
-  <si>
-    <t>66589005A</t>
-  </si>
-  <si>
-    <t>(-8358762.2, 486887.0)</t>
-  </si>
-  <si>
-    <t>SIN INFORMACION</t>
+    <t>INC 146617798</t>
+  </si>
+  <si>
+    <t>66752331A</t>
+  </si>
+  <si>
+    <t>LERIDA 3 13.2 KV</t>
+  </si>
+  <si>
+    <t>S07470</t>
+  </si>
+  <si>
+    <t>(-8335995.1, 545597.3)</t>
+  </si>
+  <si>
+    <t>VDA BLEDONIA</t>
+  </si>
+  <si>
+    <t>INC 146617966</t>
+  </si>
+  <si>
+    <t>SAC133793</t>
+  </si>
+  <si>
+    <t>BOLV-399 (Apoyo); DP-CA-S-CentroTolima</t>
+  </si>
+  <si>
+    <t>(-8366956.0, 495866.9)</t>
+  </si>
+  <si>
+    <t>VDA CHEMBE</t>
+  </si>
+  <si>
+    <t>DP - Revisar Posible puente averiado, entre el Cto. 1 13.2 kV S/E Arrieros y el RC1212 Frontera con el Cto. 3 13.2 kV S/E Libano</t>
+  </si>
+  <si>
+    <t>INC 146618019</t>
+  </si>
+  <si>
+    <t>Punto caliente</t>
+  </si>
+  <si>
+    <t>DP-CA-S-NorteTolima; BOLM-369 (M-20A)</t>
+  </si>
+  <si>
+    <t>Pendiente; Iniciada</t>
+  </si>
+  <si>
+    <t>(-8357159.6, 548664.4)</t>
+  </si>
+  <si>
+    <t>Interruptor</t>
   </si>
   <si>
     <t>INC 146618105</t>
@@ -2427,8 +2466,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EBA95B0-7FE1-4FC4-A432-F68B16307DCD}">
-  <dimension ref="A1:AV68"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6310389-F91D-43B3-B5A5-AF584BBA4434}">
+  <dimension ref="A1:AV70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
@@ -2713,7 +2752,7 @@
         <v>73</v>
       </c>
       <c r="AO7" s="1">
-        <v>46309.730060092596</v>
+        <v>46311.903002384257</v>
       </c>
       <c r="AP7" t="s">
         <v>74</v>
@@ -2734,7 +2773,7 @@
         <v>77</v>
       </c>
       <c r="AV7" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:48" x14ac:dyDescent="0.25">
@@ -2742,31 +2781,31 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="2">
         <v>46308.125798182868</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -2784,13 +2823,13 @@
         <v>61</v>
       </c>
       <c r="P8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U8" t="s">
         <v>64</v>
@@ -2820,7 +2859,7 @@
         <v>69</v>
       </c>
       <c r="AE8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF8" s="1">
         <v>46302.922558368053</v>
@@ -2841,22 +2880,22 @@
         <v>0</v>
       </c>
       <c r="AL8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AM8">
         <v>0</v>
       </c>
       <c r="AN8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AO8" s="1">
-        <v>46308.497916678243</v>
+        <v>46311.951288958335</v>
       </c>
       <c r="AP8" t="s">
         <v>74</v>
       </c>
       <c r="AQ8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AR8" t="s">
         <v>65</v>
@@ -2868,7 +2907,7 @@
         <v>76</v>
       </c>
       <c r="AU8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AV8" t="s">
         <v>65</v>
@@ -2879,28 +2918,28 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C9" s="2">
         <v>46308.333507453703</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -2924,10 +2963,10 @@
         <v>63</v>
       </c>
       <c r="R9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="U9" t="s">
         <v>64</v>
@@ -2954,10 +2993,10 @@
         <v>0</v>
       </c>
       <c r="AD9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AE9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF9" s="1">
         <v>46308.333506273149</v>
@@ -2969,7 +3008,7 @@
         <v>1</v>
       </c>
       <c r="AI9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AJ9">
         <v>6</v>
@@ -2978,22 +3017,22 @@
         <v>0</v>
       </c>
       <c r="AL9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM9">
         <v>0</v>
       </c>
       <c r="AN9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AO9" s="1">
         <v>46311.235955150463</v>
       </c>
       <c r="AP9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AR9" t="s">
         <v>65</v>
@@ -3016,28 +3055,28 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C10" s="2">
         <v>46308.366301817128</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K10">
         <v>14</v>
@@ -3061,7 +3100,7 @@
         <v>63</v>
       </c>
       <c r="T10" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="U10" t="s">
         <v>64</v>
@@ -3076,25 +3115,25 @@
         <v>66</v>
       </c>
       <c r="Y10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Z10" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AA10" t="s">
         <v>67</v>
       </c>
       <c r="AB10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC10">
         <v>0</v>
       </c>
       <c r="AD10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AE10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AF10" s="1">
         <v>46308.366301215276</v>
@@ -3115,19 +3154,19 @@
         <v>0</v>
       </c>
       <c r="AL10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AM10">
         <v>0</v>
       </c>
       <c r="AN10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AR10" t="s">
         <v>65</v>
@@ -3139,7 +3178,7 @@
         <v>76</v>
       </c>
       <c r="AU10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AV10" t="s">
         <v>65</v>
@@ -3150,28 +3189,28 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" s="2">
         <v>46294.380958240741</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K11">
         <v>6</v>
@@ -3195,10 +3234,10 @@
         <v>63</v>
       </c>
       <c r="R11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="T11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="U11" t="s">
         <v>64</v>
@@ -3213,22 +3252,22 @@
         <v>66</v>
       </c>
       <c r="Z11" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AA11" t="s">
         <v>67</v>
       </c>
       <c r="AB11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC11">
         <v>0</v>
       </c>
       <c r="AD11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AE11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AF11" s="1">
         <v>46294.380957696761</v>
@@ -3249,19 +3288,19 @@
         <v>0</v>
       </c>
       <c r="AL11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM11">
         <v>0</v>
       </c>
       <c r="AN11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AR11" t="s">
         <v>65</v>
@@ -3284,28 +3323,28 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" s="2">
         <v>46296.351475081021</v>
       </c>
       <c r="D12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -3329,10 +3368,10 @@
         <v>63</v>
       </c>
       <c r="R12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="T12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="U12" t="s">
         <v>64</v>
@@ -3359,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="AD12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AE12" t="s">
         <v>70</v>
@@ -3383,13 +3422,13 @@
         <v>0</v>
       </c>
       <c r="AL12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AM12">
         <v>0</v>
       </c>
       <c r="AN12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AO12" s="1">
         <v>46311.032022500003</v>
@@ -3398,7 +3437,7 @@
         <v>74</v>
       </c>
       <c r="AQ12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AR12" t="s">
         <v>65</v>
@@ -3421,28 +3460,28 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" s="2">
         <v>46296.366125613429</v>
       </c>
       <c r="D13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -3466,10 +3505,10 @@
         <v>63</v>
       </c>
       <c r="R13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="T13" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="U13" t="s">
         <v>64</v>
@@ -3484,7 +3523,7 @@
         <v>66</v>
       </c>
       <c r="Z13" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AA13" t="s">
         <v>67</v>
@@ -3493,13 +3532,13 @@
         <v>68</v>
       </c>
       <c r="AC13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AD13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AE13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AF13" s="1">
         <v>46296.366125115739</v>
@@ -3511,7 +3550,7 @@
         <v>1</v>
       </c>
       <c r="AI13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AJ13">
         <v>9</v>
@@ -3520,22 +3559,22 @@
         <v>0</v>
       </c>
       <c r="AL13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AM13">
         <v>0</v>
       </c>
       <c r="AN13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AO13" s="1">
         <v>46309.705413090276</v>
       </c>
       <c r="AP13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AQ13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AR13" t="s">
         <v>65</v>
@@ -3547,7 +3586,7 @@
         <v>76</v>
       </c>
       <c r="AU13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AV13" t="s">
         <v>65</v>
@@ -3558,28 +3597,28 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2">
         <v>46296.679013796296</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J14" t="s">
         <v>59</v>
@@ -3606,7 +3645,7 @@
         <v>63</v>
       </c>
       <c r="T14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="U14" t="s">
         <v>64</v>
@@ -3636,7 +3675,7 @@
         <v>69</v>
       </c>
       <c r="AE14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF14" s="1">
         <v>46289.379973622687</v>
@@ -3657,13 +3696,13 @@
         <v>0</v>
       </c>
       <c r="AL14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM14">
         <v>0</v>
       </c>
       <c r="AN14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AO14" s="1">
         <v>46307.074902766202</v>
@@ -3672,7 +3711,7 @@
         <v>74</v>
       </c>
       <c r="AQ14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AR14" t="s">
         <v>65</v>
@@ -3695,28 +3734,28 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C15" s="2">
         <v>46297.341610752315</v>
       </c>
       <c r="D15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -3740,13 +3779,13 @@
         <v>63</v>
       </c>
       <c r="R15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="T15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="U15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="V15">
         <v>1</v>
@@ -3764,16 +3803,16 @@
         <v>67</v>
       </c>
       <c r="AB15" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AC15">
         <v>0</v>
       </c>
       <c r="AD15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AE15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AF15" s="1">
         <v>46297.341610208336</v>
@@ -3794,22 +3833,22 @@
         <v>0</v>
       </c>
       <c r="AL15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AM15">
         <v>0</v>
       </c>
       <c r="AN15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AO15" s="1">
         <v>46297.99215583333</v>
       </c>
       <c r="AP15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AR15" t="s">
         <v>65</v>
@@ -3832,28 +3871,28 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2">
         <v>46297.979948715278</v>
       </c>
       <c r="D16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J16" t="s">
-        <v>85</v>
+        <v>174</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -3871,16 +3910,16 @@
         <v>61</v>
       </c>
       <c r="P16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="U16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="V16">
         <v>1</v>
@@ -3898,7 +3937,7 @@
         <v>67</v>
       </c>
       <c r="AB16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3907,7 +3946,7 @@
         <v>69</v>
       </c>
       <c r="AE16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AF16" s="1">
         <v>46297.979948715278</v>
@@ -3919,7 +3958,7 @@
         <v>0</v>
       </c>
       <c r="AI16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AJ16">
         <v>0</v>
@@ -3928,19 +3967,19 @@
         <v>0</v>
       </c>
       <c r="AL16" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AM16">
         <v>0</v>
       </c>
       <c r="AN16" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AP16" t="s">
         <v>74</v>
       </c>
       <c r="AQ16" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AR16" t="s">
         <v>65</v>
@@ -3963,28 +4002,28 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C17" s="2">
         <v>46299.483265034723</v>
       </c>
       <c r="D17" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E17" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F17" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G17" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H17" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J17" t="s">
         <v>59</v>
@@ -4011,10 +4050,10 @@
         <v>63</v>
       </c>
       <c r="R17" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="T17" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="U17" t="s">
         <v>64</v>
@@ -4029,13 +4068,13 @@
         <v>66</v>
       </c>
       <c r="Z17" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AA17" t="s">
         <v>67</v>
       </c>
       <c r="AB17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -4044,7 +4083,7 @@
         <v>69</v>
       </c>
       <c r="AE17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AF17" s="1">
         <v>46298.27023321759</v>
@@ -4056,7 +4095,7 @@
         <v>1</v>
       </c>
       <c r="AI17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AJ17">
         <v>1</v>
@@ -4065,19 +4104,19 @@
         <v>0</v>
       </c>
       <c r="AL17" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AM17">
         <v>0</v>
       </c>
       <c r="AN17" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AP17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ17" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AR17" t="s">
         <v>65</v>
@@ -4089,7 +4128,7 @@
         <v>76</v>
       </c>
       <c r="AU17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AV17" t="s">
         <v>65</v>
@@ -4100,28 +4139,28 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C18" s="2">
         <v>46300.424044398147</v>
       </c>
       <c r="D18" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F18" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G18" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H18" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -4145,10 +4184,10 @@
         <v>63</v>
       </c>
       <c r="R18" t="s">
+        <v>189</v>
+      </c>
+      <c r="T18" t="s">
         <v>187</v>
-      </c>
-      <c r="T18" t="s">
-        <v>185</v>
       </c>
       <c r="U18" t="s">
         <v>64</v>
@@ -4175,10 +4214,10 @@
         <v>0</v>
       </c>
       <c r="AD18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AE18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF18" s="1">
         <v>46300.424043900464</v>
@@ -4199,13 +4238,13 @@
         <v>0</v>
       </c>
       <c r="AL18" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AM18">
         <v>0</v>
       </c>
       <c r="AN18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AO18" s="1">
         <v>46308.672449560188</v>
@@ -4214,7 +4253,7 @@
         <v>74</v>
       </c>
       <c r="AQ18" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AR18" t="s">
         <v>65</v>
@@ -4237,28 +4276,28 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C19" s="2">
         <v>46301.524036666669</v>
       </c>
       <c r="D19" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F19" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G19" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H19" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I19" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J19" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K19">
         <v>9</v>
@@ -4282,10 +4321,10 @@
         <v>63</v>
       </c>
       <c r="R19" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="T19" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="U19" t="s">
         <v>64</v>
@@ -4300,22 +4339,22 @@
         <v>66</v>
       </c>
       <c r="Z19" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AA19" t="s">
         <v>67</v>
       </c>
       <c r="AB19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC19">
         <v>0</v>
       </c>
       <c r="AD19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AE19" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AF19" s="1">
         <v>46301.52403630787</v>
@@ -4336,19 +4375,19 @@
         <v>0</v>
       </c>
       <c r="AL19" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AM19">
         <v>0</v>
       </c>
       <c r="AN19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ19" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AR19" t="s">
         <v>65</v>
@@ -4371,28 +4410,28 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C20" s="2">
         <v>46301.888473657411</v>
       </c>
       <c r="D20" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F20" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G20" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H20" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J20" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -4416,10 +4455,10 @@
         <v>63</v>
       </c>
       <c r="R20" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="T20" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="U20" t="s">
         <v>64</v>
@@ -4446,10 +4485,10 @@
         <v>0</v>
       </c>
       <c r="AD20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AE20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF20" s="1">
         <v>46301.888473043982</v>
@@ -4470,13 +4509,13 @@
         <v>0</v>
       </c>
       <c r="AL20" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AM20">
         <v>0</v>
       </c>
       <c r="AN20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AO20" s="1">
         <v>46307.074997673612</v>
@@ -4485,7 +4524,7 @@
         <v>74</v>
       </c>
       <c r="AQ20" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AR20" t="s">
         <v>65</v>
@@ -4508,28 +4547,28 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C21" s="2">
         <v>46302.362088240741</v>
       </c>
       <c r="D21" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F21" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G21" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H21" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I21" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K21">
         <v>11</v>
@@ -4553,10 +4592,10 @@
         <v>63</v>
       </c>
       <c r="R21" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="T21" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="U21" t="s">
         <v>64</v>
@@ -4571,22 +4610,22 @@
         <v>66</v>
       </c>
       <c r="Z21" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AA21" t="s">
         <v>67</v>
       </c>
       <c r="AB21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC21">
         <v>0</v>
       </c>
       <c r="AD21" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AE21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AF21" s="1">
         <v>46302.362087696762</v>
@@ -4607,19 +4646,19 @@
         <v>0</v>
       </c>
       <c r="AL21" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AM21">
         <v>0</v>
       </c>
       <c r="AN21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ21" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AR21" t="s">
         <v>65</v>
@@ -4642,28 +4681,28 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C22" s="2">
         <v>46302.470203912038</v>
       </c>
       <c r="D22" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F22" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G22" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J22" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -4681,16 +4720,16 @@
         <v>61</v>
       </c>
       <c r="P22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R22">
         <v>65612895</v>
       </c>
       <c r="T22" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="U22" t="s">
         <v>64</v>
@@ -4717,10 +4756,10 @@
         <v>0</v>
       </c>
       <c r="AD22" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AE22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF22" s="1">
         <v>46302.470066608796</v>
@@ -4741,13 +4780,13 @@
         <v>0</v>
       </c>
       <c r="AL22" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AM22">
         <v>0</v>
       </c>
       <c r="AN22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AO22" s="1">
         <v>46310.136818657411</v>
@@ -4756,7 +4795,7 @@
         <v>74</v>
       </c>
       <c r="AQ22" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AR22" t="s">
         <v>65</v>
@@ -4768,7 +4807,7 @@
         <v>76</v>
       </c>
       <c r="AU22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AV22" t="s">
         <v>65</v>
@@ -4779,28 +4818,28 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C23" s="2">
         <v>46302.813058368054</v>
       </c>
       <c r="D23" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F23" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H23" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I23" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J23" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K23">
         <v>13</v>
@@ -4824,10 +4863,10 @@
         <v>63</v>
       </c>
       <c r="R23" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="T23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="U23" t="s">
         <v>64</v>
@@ -4842,22 +4881,22 @@
         <v>66</v>
       </c>
       <c r="Z23" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AA23" t="s">
         <v>67</v>
       </c>
       <c r="AB23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC23">
         <v>0</v>
       </c>
       <c r="AD23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AE23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AF23" s="1">
         <v>46302.813057141204</v>
@@ -4869,7 +4908,7 @@
         <v>1</v>
       </c>
       <c r="AI23" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AJ23">
         <v>1</v>
@@ -4878,19 +4917,19 @@
         <v>0</v>
       </c>
       <c r="AL23" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AM23">
         <v>0</v>
       </c>
       <c r="AN23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ23" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AR23" t="s">
         <v>65</v>
@@ -4902,7 +4941,7 @@
         <v>76</v>
       </c>
       <c r="AU23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AV23" t="s">
         <v>65</v>
@@ -4913,28 +4952,28 @@
         <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C24" s="2">
         <v>46302.834448912035</v>
       </c>
       <c r="D24" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E24" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F24" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G24" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H24" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J24" t="s">
         <v>59</v>
@@ -4961,7 +5000,7 @@
         <v>63</v>
       </c>
       <c r="T24" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="U24" t="s">
         <v>64</v>
@@ -4991,7 +5030,7 @@
         <v>69</v>
       </c>
       <c r="AE24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF24" s="1">
         <v>46300.903073344911</v>
@@ -5012,13 +5051,13 @@
         <v>0</v>
       </c>
       <c r="AL24" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AM24">
         <v>0</v>
       </c>
       <c r="AN24" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AO24" s="1">
         <v>46302.835580543979</v>
@@ -5027,7 +5066,7 @@
         <v>74</v>
       </c>
       <c r="AQ24" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AR24" t="s">
         <v>65</v>
@@ -5050,25 +5089,25 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C25" s="2">
         <v>46302.938876782406</v>
       </c>
       <c r="D25" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F25" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G25" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H25" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J25" t="s">
         <v>59</v>
@@ -5095,10 +5134,10 @@
         <v>63</v>
       </c>
       <c r="R25" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="T25" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="U25" t="s">
         <v>64</v>
@@ -5128,7 +5167,7 @@
         <v>69</v>
       </c>
       <c r="AE25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF25" s="1">
         <v>46302.379120381942</v>
@@ -5149,13 +5188,13 @@
         <v>0</v>
       </c>
       <c r="AL25" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AM25">
         <v>0</v>
       </c>
       <c r="AN25" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO25" s="1">
         <v>46307.074997673612</v>
@@ -5164,7 +5203,7 @@
         <v>74</v>
       </c>
       <c r="AQ25" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AR25" t="s">
         <v>65</v>
@@ -5176,7 +5215,7 @@
         <v>76</v>
       </c>
       <c r="AU25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AV25" t="s">
         <v>65</v>
@@ -5187,28 +5226,28 @@
         <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C26" s="2">
         <v>46303.452258657409</v>
       </c>
       <c r="D26" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F26" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G26" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H26" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J26" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K26">
         <v>5</v>
@@ -5226,16 +5265,16 @@
         <v>61</v>
       </c>
       <c r="P26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R26" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="T26" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="U26" t="s">
         <v>64</v>
@@ -5250,22 +5289,22 @@
         <v>66</v>
       </c>
       <c r="Z26" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AA26" t="s">
         <v>67</v>
       </c>
       <c r="AB26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC26">
         <v>0</v>
       </c>
       <c r="AD26" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AE26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AF26" s="1">
         <v>46303.452257789351</v>
@@ -5286,19 +5325,19 @@
         <v>0</v>
       </c>
       <c r="AL26" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AM26">
         <v>0</v>
       </c>
       <c r="AN26" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ26" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AR26" t="s">
         <v>65</v>
@@ -5321,31 +5360,31 @@
         <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C27" s="2">
         <v>46303.507397453701</v>
       </c>
       <c r="D27" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E27" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F27" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H27" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I27" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="J27" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K27">
         <v>10</v>
@@ -5369,10 +5408,10 @@
         <v>63</v>
       </c>
       <c r="R27" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="T27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="U27" t="s">
         <v>64</v>
@@ -5393,16 +5432,16 @@
         <v>67</v>
       </c>
       <c r="AB27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC27">
         <v>0</v>
       </c>
       <c r="AD27" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AE27" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AF27" s="1">
         <v>46302.777953750003</v>
@@ -5423,19 +5462,19 @@
         <v>0</v>
       </c>
       <c r="AL27" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AM27">
         <v>0</v>
       </c>
       <c r="AN27" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AP27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ27" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AR27" t="s">
         <v>65</v>
@@ -5458,31 +5497,31 @@
         <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C28" s="2">
         <v>46303.582614988423</v>
       </c>
       <c r="D28" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E28" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F28" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G28" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H28" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I28" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -5500,13 +5539,13 @@
         <v>61</v>
       </c>
       <c r="P28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T28" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="U28" t="s">
         <v>64</v>
@@ -5533,10 +5572,10 @@
         <v>0</v>
       </c>
       <c r="AD28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AE28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AF28" s="1">
         <v>46303.079102731484</v>
@@ -5557,13 +5596,13 @@
         <v>0</v>
       </c>
       <c r="AL28" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AM28">
         <v>0</v>
       </c>
       <c r="AN28" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AO28" s="1">
         <v>46305.528276307872</v>
@@ -5572,7 +5611,7 @@
         <v>74</v>
       </c>
       <c r="AQ28" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AR28" t="s">
         <v>65</v>
@@ -5595,28 +5634,28 @@
         <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C29" s="2">
         <v>46303.620899606482</v>
       </c>
       <c r="D29" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F29" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G29" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J29" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -5640,10 +5679,10 @@
         <v>63</v>
       </c>
       <c r="R29" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T29" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="U29" t="s">
         <v>64</v>
@@ -5658,7 +5697,7 @@
         <v>66</v>
       </c>
       <c r="Y29" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Z29" t="s">
         <v>65</v>
@@ -5673,10 +5712,10 @@
         <v>0</v>
       </c>
       <c r="AD29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AE29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF29" s="1">
         <v>46303.618267685182</v>
@@ -5697,13 +5736,13 @@
         <v>0</v>
       </c>
       <c r="AL29" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AM29">
         <v>0</v>
       </c>
       <c r="AN29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AO29" s="1">
         <v>46311.501728425923</v>
@@ -5712,7 +5751,7 @@
         <v>74</v>
       </c>
       <c r="AQ29" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AR29" t="s">
         <v>65</v>
@@ -5727,7 +5766,7 @@
         <v>77</v>
       </c>
       <c r="AV29" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:48" x14ac:dyDescent="0.25">
@@ -5735,28 +5774,28 @@
         <v>24</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C30" s="2">
         <v>46303.625136435185</v>
       </c>
       <c r="D30" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F30" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K30">
         <v>10</v>
@@ -5780,10 +5819,10 @@
         <v>63</v>
       </c>
       <c r="R30" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="T30" t="s">
-        <v>273</v>
+        <v>97</v>
       </c>
       <c r="U30" t="s">
         <v>64</v>
@@ -5798,22 +5837,22 @@
         <v>66</v>
       </c>
       <c r="Z30" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AA30" t="s">
         <v>67</v>
       </c>
       <c r="AB30" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC30">
         <v>0</v>
       </c>
       <c r="AD30" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AE30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AF30" s="1">
         <v>46303.625135486109</v>
@@ -5834,19 +5873,19 @@
         <v>0</v>
       </c>
       <c r="AL30" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM30">
         <v>0</v>
       </c>
       <c r="AN30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ30" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AR30" t="s">
         <v>65</v>
@@ -5869,31 +5908,31 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C31" s="2">
         <v>46303.834263124998</v>
       </c>
       <c r="D31" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E31" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F31" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G31" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H31" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I31" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J31" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -5911,13 +5950,13 @@
         <v>61</v>
       </c>
       <c r="P31" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T31" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="U31" t="s">
         <v>64</v>
@@ -5944,10 +5983,10 @@
         <v>0</v>
       </c>
       <c r="AD31" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AE31" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF31" s="1">
         <v>46302.85321872685</v>
@@ -5968,13 +6007,13 @@
         <v>0</v>
       </c>
       <c r="AL31" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM31">
         <v>0</v>
       </c>
       <c r="AN31" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AO31" s="1">
         <v>46309.96033440972</v>
@@ -5983,7 +6022,7 @@
         <v>74</v>
       </c>
       <c r="AQ31" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AR31" t="s">
         <v>65</v>
@@ -5995,7 +6034,7 @@
         <v>76</v>
       </c>
       <c r="AU31" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AV31" t="s">
         <v>65</v>
@@ -6006,28 +6045,28 @@
         <v>26</v>
       </c>
       <c r="B32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C32" s="2">
         <v>46304.417614247686</v>
       </c>
       <c r="D32" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F32" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G32" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J32" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -6045,19 +6084,19 @@
         <v>61</v>
       </c>
       <c r="P32" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R32" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="S32" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="T32" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="U32" t="s">
         <v>64</v>
@@ -6084,10 +6123,10 @@
         <v>0</v>
       </c>
       <c r="AD32" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="AE32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF32" s="1">
         <v>46304.417613530095</v>
@@ -6114,7 +6153,7 @@
         <v>0</v>
       </c>
       <c r="AN32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AO32" s="1">
         <v>46310.136818657411</v>
@@ -6138,7 +6177,7 @@
         <v>77</v>
       </c>
       <c r="AV32" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:48" x14ac:dyDescent="0.25">
@@ -6158,13 +6197,13 @@
         <v>292</v>
       </c>
       <c r="G33" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H33" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J33" t="s">
         <v>293</v>
@@ -6194,7 +6233,7 @@
         <v>294</v>
       </c>
       <c r="T33" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="U33" t="s">
         <v>64</v>
@@ -6215,16 +6254,16 @@
         <v>67</v>
       </c>
       <c r="AB33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AC33">
         <v>0</v>
       </c>
       <c r="AD33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AE33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF33" s="1">
         <v>46304.447403692131</v>
@@ -6236,7 +6275,7 @@
         <v>1</v>
       </c>
       <c r="AI33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AJ33">
         <v>1</v>
@@ -6251,10 +6290,10 @@
         <v>0</v>
       </c>
       <c r="AN33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ33" t="s">
         <v>296</v>
@@ -6269,7 +6308,7 @@
         <v>76</v>
       </c>
       <c r="AU33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AV33" t="s">
         <v>65</v>
@@ -6280,7 +6319,7 @@
         <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C34" s="2">
         <v>46304.454942291668</v>
@@ -6298,7 +6337,7 @@
         <v>300</v>
       </c>
       <c r="I34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J34" t="s">
         <v>301</v>
@@ -6343,22 +6382,22 @@
         <v>66</v>
       </c>
       <c r="Z34" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AA34" t="s">
         <v>67</v>
       </c>
       <c r="AB34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC34">
         <v>0</v>
       </c>
       <c r="AD34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AE34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AF34" s="1">
         <v>46304.454941678239</v>
@@ -6385,10 +6424,10 @@
         <v>0</v>
       </c>
       <c r="AN34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ34" t="s">
         <v>304</v>
@@ -6414,7 +6453,7 @@
         <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C35" s="2">
         <v>46304.693424247685</v>
@@ -6435,10 +6474,10 @@
         <v>309</v>
       </c>
       <c r="I35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J35" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -6456,10 +6495,10 @@
         <v>61</v>
       </c>
       <c r="P35" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T35" t="s">
         <v>308</v>
@@ -6492,7 +6531,7 @@
         <v>69</v>
       </c>
       <c r="AE35" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AF35" s="1">
         <v>46303.667550081016</v>
@@ -6519,7 +6558,7 @@
         <v>0</v>
       </c>
       <c r="AN35" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AO35" s="1">
         <v>46310.105611516206</v>
@@ -6551,7 +6590,7 @@
         <v>30</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C36" s="2">
         <v>46304.920313912036</v>
@@ -6569,7 +6608,7 @@
         <v>300</v>
       </c>
       <c r="I36" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J36" t="s">
         <v>301</v>
@@ -6614,22 +6653,22 @@
         <v>66</v>
       </c>
       <c r="Z36" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AA36" t="s">
         <v>67</v>
       </c>
       <c r="AB36" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC36">
         <v>0</v>
       </c>
       <c r="AD36" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AE36" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AF36" s="1">
         <v>46304.920313368057</v>
@@ -6656,10 +6695,10 @@
         <v>0</v>
       </c>
       <c r="AN36" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP36" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ36" t="s">
         <v>316</v>
@@ -6674,7 +6713,7 @@
         <v>76</v>
       </c>
       <c r="AU36" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AV36" t="s">
         <v>65</v>
@@ -6685,7 +6724,7 @@
         <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C37" s="2">
         <v>46305.443223935188</v>
@@ -6703,10 +6742,10 @@
         <v>320</v>
       </c>
       <c r="I37" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J37" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K37">
         <v>12</v>
@@ -6745,22 +6784,22 @@
         <v>66</v>
       </c>
       <c r="Z37" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AA37" t="s">
         <v>67</v>
       </c>
       <c r="AB37" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC37">
         <v>0</v>
       </c>
       <c r="AD37" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AE37" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AF37" s="1">
         <v>46305.443222581016</v>
@@ -6787,10 +6826,10 @@
         <v>0</v>
       </c>
       <c r="AN37" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP37" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ37" t="s">
         <v>322</v>
@@ -6816,7 +6855,7 @@
         <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C38" s="2">
         <v>46305.656685613423</v>
@@ -6837,7 +6876,7 @@
         <v>327</v>
       </c>
       <c r="I38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J38" t="s">
         <v>59</v>
@@ -6861,7 +6900,7 @@
         <v>62</v>
       </c>
       <c r="Q38" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R38" t="s">
         <v>325</v>
@@ -6882,13 +6921,13 @@
         <v>66</v>
       </c>
       <c r="Z38" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AA38" t="s">
         <v>67</v>
       </c>
       <c r="AB38" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -6927,10 +6966,10 @@
         <v>331</v>
       </c>
       <c r="AP38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ38" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AR38" t="s">
         <v>65</v>
@@ -6953,7 +6992,7 @@
         <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C39" s="2">
         <v>46305.89986020833</v>
@@ -6965,13 +7004,13 @@
         <v>334</v>
       </c>
       <c r="G39" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I39" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J39" t="s">
         <v>335</v>
@@ -7001,7 +7040,7 @@
         <v>336</v>
       </c>
       <c r="T39" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="U39" t="s">
         <v>64</v>
@@ -7016,22 +7055,22 @@
         <v>66</v>
       </c>
       <c r="Z39" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AA39" t="s">
         <v>67</v>
       </c>
       <c r="AB39" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC39">
         <v>0</v>
       </c>
       <c r="AD39" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AE39" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AF39" s="1">
         <v>46305.899859259262</v>
@@ -7058,10 +7097,10 @@
         <v>0</v>
       </c>
       <c r="AN39" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP39" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ39" t="s">
         <v>338</v>
@@ -7087,7 +7126,7 @@
         <v>34</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C40" s="2">
         <v>46305.919607268515</v>
@@ -7105,7 +7144,7 @@
         <v>341</v>
       </c>
       <c r="I40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J40" t="s">
         <v>342</v>
@@ -7126,10 +7165,10 @@
         <v>61</v>
       </c>
       <c r="P40" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R40" t="s">
         <v>343</v>
@@ -7150,22 +7189,22 @@
         <v>66</v>
       </c>
       <c r="Z40" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AA40" t="s">
         <v>67</v>
       </c>
       <c r="AB40" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC40">
         <v>0</v>
       </c>
       <c r="AD40" t="s">
-        <v>248</v>
+        <v>345</v>
       </c>
       <c r="AE40" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AF40" s="1">
         <v>46304.50348003472</v>
@@ -7186,19 +7225,19 @@
         <v>0</v>
       </c>
       <c r="AL40" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM40">
         <v>0</v>
       </c>
       <c r="AN40" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP40" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ40" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AR40" t="s">
         <v>65</v>
@@ -7221,31 +7260,31 @@
         <v>35</v>
       </c>
       <c r="B41" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C41" s="2">
         <v>46306.538759444447</v>
       </c>
       <c r="D41" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E41" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F41" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G41" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H41" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I41" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J41" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -7263,13 +7302,13 @@
         <v>61</v>
       </c>
       <c r="P41" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T41" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U41" t="s">
         <v>64</v>
@@ -7284,7 +7323,7 @@
         <v>66</v>
       </c>
       <c r="Y41" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Z41" t="s">
         <v>65</v>
@@ -7299,10 +7338,10 @@
         <v>0</v>
       </c>
       <c r="AD41" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AE41" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AF41" s="1">
         <v>46304.418572407405</v>
@@ -7323,13 +7362,13 @@
         <v>0</v>
       </c>
       <c r="AL41" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AM41">
         <v>0</v>
       </c>
       <c r="AN41" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO41" s="1">
         <v>46310.830416273151</v>
@@ -7338,7 +7377,7 @@
         <v>74</v>
       </c>
       <c r="AQ41" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AR41" t="s">
         <v>65</v>
@@ -7361,37 +7400,37 @@
         <v>36</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C42" s="2">
-        <v>46307.312114722219</v>
+        <v>46306.692922222224</v>
       </c>
       <c r="D42" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F42" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G42" t="s">
-        <v>109</v>
+        <v>357</v>
       </c>
       <c r="H42" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I42" t="s">
-        <v>194</v>
+        <v>358</v>
       </c>
       <c r="J42" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="K42">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L42">
         <v>0</v>
       </c>
       <c r="M42">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N42" t="s">
         <v>60</v>
@@ -7406,10 +7445,10 @@
         <v>63</v>
       </c>
       <c r="T42" t="s">
-        <v>109</v>
+        <v>359</v>
       </c>
       <c r="U42" t="s">
-        <v>64</v>
+        <v>164</v>
       </c>
       <c r="V42">
         <v>1</v>
@@ -7421,55 +7460,55 @@
         <v>66</v>
       </c>
       <c r="Z42" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="AA42" t="s">
         <v>67</v>
       </c>
       <c r="AB42" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="AC42">
         <v>0</v>
       </c>
       <c r="AD42" t="s">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="AE42" t="s">
-        <v>117</v>
+        <v>167</v>
       </c>
       <c r="AF42" s="1">
-        <v>46307.312114097222</v>
+        <v>46306.692922222224</v>
       </c>
       <c r="AG42">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AH42">
         <v>0</v>
       </c>
       <c r="AI42" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="AJ42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK42">
         <v>0</v>
       </c>
       <c r="AL42" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="AM42">
         <v>0</v>
       </c>
       <c r="AN42" t="s">
-        <v>104</v>
+        <v>353</v>
       </c>
       <c r="AP42" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ42" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="AR42" t="s">
         <v>65</v>
@@ -7481,7 +7520,7 @@
         <v>76</v>
       </c>
       <c r="AU42" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="AV42" t="s">
         <v>65</v>
@@ -7492,37 +7531,37 @@
         <v>37</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C43" s="2">
-        <v>46307.315618969908</v>
+        <v>46307.312114722219</v>
       </c>
       <c r="D43" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F43" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="G43" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H43" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I43" t="s">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="J43" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="K43">
+        <v>15</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
         <v>8</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>1</v>
       </c>
       <c r="N43" t="s">
         <v>60</v>
@@ -7536,11 +7575,8 @@
       <c r="Q43" t="s">
         <v>63</v>
       </c>
-      <c r="R43" t="s">
-        <v>360</v>
-      </c>
       <c r="T43" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="U43" t="s">
         <v>64</v>
@@ -7555,28 +7591,28 @@
         <v>66</v>
       </c>
       <c r="Z43" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AA43" t="s">
         <v>67</v>
       </c>
       <c r="AB43" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC43">
         <v>0</v>
       </c>
       <c r="AD43" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AE43" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AF43" s="1">
-        <v>46307.315617800923</v>
+        <v>46307.312114097222</v>
       </c>
       <c r="AG43">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AH43">
         <v>0</v>
@@ -7591,19 +7627,19 @@
         <v>0</v>
       </c>
       <c r="AL43" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AM43">
         <v>0</v>
       </c>
       <c r="AN43" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP43" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ43" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AR43" t="s">
         <v>65</v>
@@ -7615,7 +7651,7 @@
         <v>76</v>
       </c>
       <c r="AU43" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AV43" t="s">
         <v>65</v>
@@ -7626,34 +7662,31 @@
         <v>38</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C44" s="2">
-        <v>46307.480043946758</v>
+        <v>46307.315618969908</v>
       </c>
       <c r="D44" t="s">
-        <v>363</v>
-      </c>
-      <c r="E44" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F44" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G44" t="s">
-        <v>279</v>
+        <v>110</v>
       </c>
       <c r="H44" t="s">
-        <v>280</v>
+        <v>111</v>
       </c>
       <c r="I44" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="J44" t="s">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -7668,13 +7701,16 @@
         <v>61</v>
       </c>
       <c r="P44" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="Q44" t="s">
-        <v>87</v>
+        <v>63</v>
+      </c>
+      <c r="R44" t="s">
+        <v>368</v>
       </c>
       <c r="T44" t="s">
-        <v>279</v>
+        <v>114</v>
       </c>
       <c r="U44" t="s">
         <v>64</v>
@@ -7689,28 +7725,28 @@
         <v>66</v>
       </c>
       <c r="Z44" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="AA44" t="s">
         <v>67</v>
       </c>
       <c r="AB44" t="s">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="AC44">
         <v>0</v>
       </c>
       <c r="AD44" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="AE44" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="AF44" s="1">
-        <v>46306.394415243056</v>
+        <v>46307.315617800923</v>
       </c>
       <c r="AG44">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AH44">
         <v>0</v>
@@ -7719,28 +7755,25 @@
         <v>71</v>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK44">
         <v>0</v>
       </c>
       <c r="AL44" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AM44">
         <v>0</v>
       </c>
       <c r="AN44" t="s">
-        <v>367</v>
-      </c>
-      <c r="AO44" s="1">
-        <v>46309.96033440972</v>
+        <v>105</v>
       </c>
       <c r="AP44" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AQ44" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AR44" t="s">
         <v>65</v>
@@ -7763,37 +7796,40 @@
         <v>39</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C45" s="2">
-        <v>46307.845660590276</v>
+        <v>46307.480043946758</v>
       </c>
       <c r="D45" t="s">
-        <v>369</v>
+        <v>371</v>
+      </c>
+      <c r="E45" t="s">
+        <v>372</v>
       </c>
       <c r="F45" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="G45" t="s">
-        <v>109</v>
+        <v>280</v>
       </c>
       <c r="H45" t="s">
-        <v>110</v>
+        <v>281</v>
       </c>
       <c r="I45" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="J45" t="s">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="K45">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L45">
         <v>0</v>
       </c>
       <c r="M45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N45" t="s">
         <v>60</v>
@@ -7802,13 +7838,13 @@
         <v>61</v>
       </c>
       <c r="P45" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="Q45" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="T45" t="s">
-        <v>109</v>
+        <v>280</v>
       </c>
       <c r="U45" t="s">
         <v>64</v>
@@ -7823,28 +7859,28 @@
         <v>66</v>
       </c>
       <c r="Z45" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="AA45" t="s">
         <v>67</v>
       </c>
       <c r="AB45" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="AC45">
         <v>0</v>
       </c>
       <c r="AD45" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="AE45" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="AF45" s="1">
-        <v>46307.84565974537</v>
+        <v>46306.394415243056</v>
       </c>
       <c r="AG45">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AH45">
         <v>0</v>
@@ -7853,25 +7889,28 @@
         <v>71</v>
       </c>
       <c r="AJ45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK45">
         <v>0</v>
       </c>
       <c r="AL45" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AM45">
         <v>0</v>
       </c>
       <c r="AN45" t="s">
-        <v>104</v>
+        <v>375</v>
+      </c>
+      <c r="AO45" s="1">
+        <v>46309.96033440972</v>
       </c>
       <c r="AP45" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="AQ45" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AR45" t="s">
         <v>65</v>
@@ -7883,7 +7922,7 @@
         <v>76</v>
       </c>
       <c r="AU45" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="AV45" t="s">
         <v>65</v>
@@ -7894,37 +7933,37 @@
         <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C46" s="2">
-        <v>46308.689703449076</v>
+        <v>46307.845660590276</v>
       </c>
       <c r="D46" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F46" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G46" t="s">
-        <v>326</v>
+        <v>110</v>
       </c>
       <c r="H46" t="s">
-        <v>327</v>
+        <v>111</v>
       </c>
       <c r="I46" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="J46" t="s">
-        <v>59</v>
+        <v>141</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N46" t="s">
         <v>60</v>
@@ -7933,16 +7972,16 @@
         <v>61</v>
       </c>
       <c r="P46" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="Q46" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="T46" t="s">
-        <v>375</v>
+        <v>114</v>
       </c>
       <c r="U46" t="s">
-        <v>163</v>
+        <v>64</v>
       </c>
       <c r="V46">
         <v>1</v>
@@ -7954,55 +7993,55 @@
         <v>66</v>
       </c>
       <c r="Z46" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="AA46" t="s">
         <v>67</v>
       </c>
       <c r="AB46" t="s">
-        <v>164</v>
+        <v>116</v>
       </c>
       <c r="AC46">
         <v>0</v>
       </c>
       <c r="AD46" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="AE46" t="s">
-        <v>166</v>
+        <v>118</v>
       </c>
       <c r="AF46" s="1">
-        <v>46308.689703449076</v>
+        <v>46307.84565974537</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH46">
         <v>0</v>
       </c>
       <c r="AI46" t="s">
-        <v>166</v>
+        <v>71</v>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK46">
         <v>0</v>
       </c>
       <c r="AL46" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AM46">
         <v>0</v>
       </c>
       <c r="AN46" t="s">
-        <v>377</v>
+        <v>105</v>
       </c>
       <c r="AP46" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ46" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AR46" t="s">
         <v>65</v>
@@ -8014,7 +8053,7 @@
         <v>76</v>
       </c>
       <c r="AU46" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AV46" t="s">
         <v>65</v>
@@ -8025,31 +8064,28 @@
         <v>41</v>
       </c>
       <c r="B47" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="C47" s="2">
-        <v>46308.724995983794</v>
+        <v>46308.689703449076</v>
       </c>
       <c r="D47" t="s">
-        <v>379</v>
-      </c>
-      <c r="E47" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F47" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G47" t="s">
-        <v>382</v>
+        <v>326</v>
       </c>
       <c r="H47" t="s">
-        <v>172</v>
+        <v>327</v>
       </c>
       <c r="I47" t="s">
-        <v>58</v>
+        <v>125</v>
       </c>
       <c r="J47" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -8058,7 +8094,7 @@
         <v>0</v>
       </c>
       <c r="M47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" t="s">
         <v>60</v>
@@ -8067,16 +8103,16 @@
         <v>61</v>
       </c>
       <c r="P47" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q47" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T47" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="U47" t="s">
-        <v>64</v>
+        <v>164</v>
       </c>
       <c r="V47">
         <v>1</v>
@@ -8094,7 +8130,7 @@
         <v>67</v>
       </c>
       <c r="AB47" t="s">
-        <v>68</v>
+        <v>165</v>
       </c>
       <c r="AC47">
         <v>0</v>
@@ -8103,19 +8139,19 @@
         <v>69</v>
       </c>
       <c r="AE47" t="s">
-        <v>88</v>
+        <v>167</v>
       </c>
       <c r="AF47" s="1">
-        <v>46308.308068101855</v>
+        <v>46308.689703449076</v>
       </c>
       <c r="AG47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH47">
         <v>0</v>
       </c>
       <c r="AI47" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="AJ47">
         <v>0</v>
@@ -8124,22 +8160,19 @@
         <v>0</v>
       </c>
       <c r="AL47" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM47">
         <v>0</v>
       </c>
       <c r="AN47" t="s">
-        <v>384</v>
-      </c>
-      <c r="AO47" s="1">
-        <v>46309.598431041668</v>
+        <v>385</v>
       </c>
       <c r="AP47" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AQ47" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AR47" t="s">
         <v>65</v>
@@ -8151,7 +8184,7 @@
         <v>76</v>
       </c>
       <c r="AU47" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="AV47" t="s">
         <v>65</v>
@@ -8162,31 +8195,31 @@
         <v>42</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="C48" s="2">
-        <v>46308.791972488427</v>
+        <v>46308.724995983794</v>
       </c>
       <c r="D48" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E48" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F48" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G48" t="s">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="H48" t="s">
-        <v>83</v>
+        <v>173</v>
       </c>
       <c r="I48" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="J48" t="s">
-        <v>389</v>
+        <v>86</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -8195,7 +8228,7 @@
         <v>0</v>
       </c>
       <c r="M48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N48" t="s">
         <v>60</v>
@@ -8204,13 +8237,13 @@
         <v>61</v>
       </c>
       <c r="P48" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q48" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T48" t="s">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="U48" t="s">
         <v>64</v>
@@ -8237,13 +8270,13 @@
         <v>0</v>
       </c>
       <c r="AD48" t="s">
-        <v>390</v>
+        <v>69</v>
       </c>
       <c r="AE48" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF48" s="1">
-        <v>46308.254661377316</v>
+        <v>46308.308068101855</v>
       </c>
       <c r="AG48">
         <v>1</v>
@@ -8261,22 +8294,22 @@
         <v>0</v>
       </c>
       <c r="AL48" t="s">
-        <v>89</v>
+        <v>391</v>
       </c>
       <c r="AM48">
         <v>0</v>
       </c>
       <c r="AN48" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO48" s="1">
-        <v>46308.497916678243</v>
+        <v>46309.598431041668</v>
       </c>
       <c r="AP48" t="s">
         <v>74</v>
       </c>
       <c r="AQ48" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AR48" t="s">
         <v>65</v>
@@ -8288,7 +8321,7 @@
         <v>76</v>
       </c>
       <c r="AU48" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AV48" t="s">
         <v>65</v>
@@ -8299,32 +8332,32 @@
         <v>43</v>
       </c>
       <c r="B49" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="C49" s="2">
-        <v>46308.841964930558</v>
+        <v>46308.791972488427</v>
       </c>
       <c r="D49" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E49" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F49" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G49" t="s">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="H49" t="s">
+        <v>84</v>
+      </c>
+      <c r="I49" t="s">
+        <v>85</v>
+      </c>
+      <c r="J49" t="s">
         <v>397</v>
       </c>
-      <c r="I49" t="s">
-        <v>133</v>
-      </c>
-      <c r="J49" t="s">
-        <v>59</v>
-      </c>
       <c r="K49">
         <v>0</v>
       </c>
@@ -8332,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="M49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N49" t="s">
         <v>60</v>
@@ -8341,13 +8374,13 @@
         <v>61</v>
       </c>
       <c r="P49" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q49" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T49" t="s">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="U49" t="s">
         <v>64</v>
@@ -8374,13 +8407,13 @@
         <v>0</v>
       </c>
       <c r="AD49" t="s">
-        <v>69</v>
+        <v>398</v>
       </c>
       <c r="AE49" t="s">
-        <v>198</v>
+        <v>89</v>
       </c>
       <c r="AF49" s="1">
-        <v>46308.585931307869</v>
+        <v>46308.254661377316</v>
       </c>
       <c r="AG49">
         <v>1</v>
@@ -8389,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="AI49" t="s">
-        <v>398</v>
+        <v>71</v>
       </c>
       <c r="AJ49">
         <v>0</v>
@@ -8398,16 +8431,16 @@
         <v>0</v>
       </c>
       <c r="AL49" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM49">
+        <v>0</v>
+      </c>
+      <c r="AN49" t="s">
         <v>399</v>
       </c>
-      <c r="AM49">
-        <v>0</v>
-      </c>
-      <c r="AN49" t="s">
-        <v>391</v>
-      </c>
       <c r="AO49" s="1">
-        <v>46310.11667166667</v>
+        <v>46311.951288958335</v>
       </c>
       <c r="AP49" t="s">
         <v>74</v>
@@ -8436,28 +8469,31 @@
         <v>44</v>
       </c>
       <c r="B50" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C50" s="2">
-        <v>46308.912080636575</v>
+        <v>46308.841964930558</v>
       </c>
       <c r="D50" t="s">
         <v>401</v>
       </c>
+      <c r="E50" t="s">
+        <v>402</v>
+      </c>
       <c r="F50" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G50" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="H50" t="s">
-        <v>172</v>
+        <v>405</v>
       </c>
       <c r="I50" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="J50" t="s">
-        <v>403</v>
+        <v>59</v>
       </c>
       <c r="K50">
         <v>0</v>
@@ -8475,16 +8511,13 @@
         <v>61</v>
       </c>
       <c r="P50" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q50" t="s">
-        <v>87</v>
-      </c>
-      <c r="R50" t="s">
+        <v>88</v>
+      </c>
+      <c r="T50" t="s">
         <v>404</v>
-      </c>
-      <c r="T50" t="s">
-        <v>382</v>
       </c>
       <c r="U50" t="s">
         <v>64</v>
@@ -8505,49 +8538,52 @@
         <v>67</v>
       </c>
       <c r="AB50" t="s">
-        <v>164</v>
+        <v>68</v>
       </c>
       <c r="AC50">
         <v>0</v>
       </c>
       <c r="AD50" t="s">
-        <v>165</v>
+        <v>69</v>
       </c>
       <c r="AE50" t="s">
-        <v>88</v>
+        <v>200</v>
       </c>
       <c r="AF50" s="1">
-        <v>46308.912080196758</v>
+        <v>46308.585931307869</v>
       </c>
       <c r="AG50">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AH50">
         <v>0</v>
       </c>
       <c r="AI50" t="s">
-        <v>71</v>
+        <v>406</v>
       </c>
       <c r="AJ50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK50">
         <v>0</v>
       </c>
       <c r="AL50" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AM50">
         <v>0</v>
       </c>
       <c r="AN50" t="s">
-        <v>104</v>
+        <v>399</v>
+      </c>
+      <c r="AO50" s="1">
+        <v>46310.11667166667</v>
       </c>
       <c r="AP50" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="AQ50" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AR50" t="s">
         <v>65</v>
@@ -8559,7 +8595,7 @@
         <v>76</v>
       </c>
       <c r="AU50" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="AV50" t="s">
         <v>65</v>
@@ -8570,37 +8606,37 @@
         <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="C51" s="2">
-        <v>46309.289360104165</v>
+        <v>46308.912080636575</v>
       </c>
       <c r="D51" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F51" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G51" t="s">
-        <v>409</v>
+        <v>390</v>
       </c>
       <c r="H51" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="I51" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="J51" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K51">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L51">
         <v>0</v>
       </c>
       <c r="M51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N51" t="s">
         <v>60</v>
@@ -8609,13 +8645,16 @@
         <v>61</v>
       </c>
       <c r="P51" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="Q51" t="s">
-        <v>63</v>
+        <v>88</v>
+      </c>
+      <c r="R51" t="s">
+        <v>412</v>
       </c>
       <c r="T51" t="s">
-        <v>409</v>
+        <v>390</v>
       </c>
       <c r="U51" t="s">
         <v>64</v>
@@ -8630,28 +8669,28 @@
         <v>66</v>
       </c>
       <c r="Z51" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="AA51" t="s">
         <v>67</v>
       </c>
       <c r="AB51" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="AC51">
         <v>0</v>
       </c>
       <c r="AD51" t="s">
-        <v>260</v>
+        <v>166</v>
       </c>
       <c r="AE51" t="s">
-        <v>127</v>
+        <v>89</v>
       </c>
       <c r="AF51" s="1">
-        <v>46309.289359513888</v>
+        <v>46308.912080196758</v>
       </c>
       <c r="AG51">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AH51">
         <v>0</v>
@@ -8666,19 +8705,19 @@
         <v>0</v>
       </c>
       <c r="AL51" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AM51">
         <v>0</v>
       </c>
       <c r="AN51" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP51" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ51" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AR51" t="s">
         <v>65</v>
@@ -8690,7 +8729,7 @@
         <v>76</v>
       </c>
       <c r="AU51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AV51" t="s">
         <v>65</v>
@@ -8701,28 +8740,28 @@
         <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C52" s="2">
         <v>46309.345147569446</v>
       </c>
       <c r="D52" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="F52" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="G52" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H52" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I52" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J52" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K52">
         <v>0</v>
@@ -8746,10 +8785,10 @@
         <v>63</v>
       </c>
       <c r="R52" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="T52" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="U52" t="s">
         <v>64</v>
@@ -8776,7 +8815,7 @@
         <v>0</v>
       </c>
       <c r="AD52" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AE52" t="s">
         <v>70</v>
@@ -8800,13 +8839,13 @@
         <v>0</v>
       </c>
       <c r="AL52" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AM52">
         <v>0</v>
       </c>
       <c r="AN52" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AO52" s="1">
         <v>46310.978230243054</v>
@@ -8815,7 +8854,7 @@
         <v>74</v>
       </c>
       <c r="AQ52" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AR52" t="s">
         <v>65</v>
@@ -8827,10 +8866,10 @@
         <v>76</v>
       </c>
       <c r="AU52" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AV52" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
     </row>
     <row r="53" spans="1:48" x14ac:dyDescent="0.25">
@@ -8838,28 +8877,28 @@
         <v>47</v>
       </c>
       <c r="B53" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C53" s="2">
         <v>46309.623780254631</v>
       </c>
       <c r="D53" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F53" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="G53" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H53" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I53" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J53" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="K53">
         <v>0</v>
@@ -8877,16 +8916,16 @@
         <v>61</v>
       </c>
       <c r="P53" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q53" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R53" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="T53" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="U53" t="s">
         <v>64</v>
@@ -8907,13 +8946,13 @@
         <v>67</v>
       </c>
       <c r="AB53" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AC53">
         <v>0</v>
       </c>
       <c r="AD53" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AE53" t="s">
         <v>328</v>
@@ -8928,7 +8967,7 @@
         <v>0</v>
       </c>
       <c r="AI53" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="AJ53">
         <v>1</v>
@@ -8937,19 +8976,19 @@
         <v>0</v>
       </c>
       <c r="AL53" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AM53">
         <v>0</v>
       </c>
       <c r="AN53" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP53" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ53" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AR53" t="s">
         <v>65</v>
@@ -8961,7 +9000,7 @@
         <v>76</v>
       </c>
       <c r="AU53" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AV53" t="s">
         <v>65</v>
@@ -8972,28 +9011,28 @@
         <v>48</v>
       </c>
       <c r="B54" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C54" s="2">
         <v>46309.635386435184</v>
       </c>
       <c r="D54" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E54" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F54" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G54" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H54" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I54" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J54" t="s">
         <v>59</v>
@@ -9020,7 +9059,7 @@
         <v>63</v>
       </c>
       <c r="T54" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="U54" t="s">
         <v>64</v>
@@ -9050,7 +9089,7 @@
         <v>69</v>
       </c>
       <c r="AE54" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AF54" s="1">
         <v>46309.635022604169</v>
@@ -9071,13 +9110,13 @@
         <v>0</v>
       </c>
       <c r="AL54" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AM54">
         <v>0</v>
       </c>
       <c r="AN54" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO54" s="1">
         <v>46311.032022500003</v>
@@ -9086,7 +9125,7 @@
         <v>74</v>
       </c>
       <c r="AQ54" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AR54" t="s">
         <v>65</v>
@@ -9098,7 +9137,7 @@
         <v>76</v>
       </c>
       <c r="AU54" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AV54" t="s">
         <v>65</v>
@@ -9109,28 +9148,28 @@
         <v>49</v>
       </c>
       <c r="B55" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C55" s="2">
         <v>46309.765710081017</v>
       </c>
       <c r="D55" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E55" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F55" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G55" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H55" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I55" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J55" t="s">
         <v>59</v>
@@ -9157,7 +9196,7 @@
         <v>63</v>
       </c>
       <c r="T55" t="s">
-        <v>226</v>
+        <v>97</v>
       </c>
       <c r="U55" t="s">
         <v>64</v>
@@ -9187,7 +9226,7 @@
         <v>69</v>
       </c>
       <c r="AE55" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF55" s="1">
         <v>46308.667246944446</v>
@@ -9208,22 +9247,22 @@
         <v>0</v>
       </c>
       <c r="AL55" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AM55">
         <v>0</v>
       </c>
       <c r="AN55" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO55" s="1">
-        <v>46311.590830636575</v>
+        <v>46312.07108627315</v>
       </c>
       <c r="AP55" t="s">
         <v>74</v>
       </c>
       <c r="AQ55" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AR55" t="s">
         <v>65</v>
@@ -9235,7 +9274,7 @@
         <v>76</v>
       </c>
       <c r="AU55" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AV55" t="s">
         <v>65</v>
@@ -9246,25 +9285,25 @@
         <v>50</v>
       </c>
       <c r="B56" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C56" s="2">
         <v>46309.971438715278</v>
       </c>
       <c r="D56" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F56" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G56" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H56" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I56" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="J56" t="s">
         <v>59</v>
@@ -9285,7 +9324,7 @@
         <v>61</v>
       </c>
       <c r="U56" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="V56">
         <v>1</v>
@@ -9303,13 +9342,13 @@
         <v>67</v>
       </c>
       <c r="AB56" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD56" t="s">
         <v>69</v>
       </c>
       <c r="AE56" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AF56" s="1">
         <v>46309.971438715278</v>
@@ -9321,7 +9360,7 @@
         <v>0</v>
       </c>
       <c r="AI56" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AJ56">
         <v>0</v>
@@ -9330,7 +9369,7 @@
         <v>0</v>
       </c>
       <c r="AL56" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AM56">
         <v>0</v>
@@ -9339,10 +9378,10 @@
         <v>73</v>
       </c>
       <c r="AP56" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AQ56" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AR56" t="s">
         <v>65</v>
@@ -9362,28 +9401,28 @@
         <v>51</v>
       </c>
       <c r="B57" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C57" s="2">
         <v>46310.345687685185</v>
       </c>
       <c r="D57" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F57" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G57" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H57" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I57" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J57" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="K57">
         <v>67</v>
@@ -9407,10 +9446,10 @@
         <v>63</v>
       </c>
       <c r="R57" t="s">
+        <v>447</v>
+      </c>
+      <c r="T57" t="s">
         <v>445</v>
-      </c>
-      <c r="T57" t="s">
-        <v>443</v>
       </c>
       <c r="U57" t="s">
         <v>64</v>
@@ -9425,19 +9464,19 @@
         <v>66</v>
       </c>
       <c r="Z57" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AA57" t="s">
         <v>67</v>
       </c>
       <c r="AB57" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC57">
         <v>0</v>
       </c>
       <c r="AD57" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AE57" t="s">
         <v>328</v>
@@ -9452,7 +9491,7 @@
         <v>1</v>
       </c>
       <c r="AI57" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AJ57">
         <v>1</v>
@@ -9461,19 +9500,19 @@
         <v>0</v>
       </c>
       <c r="AL57" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AM57">
         <v>0</v>
       </c>
       <c r="AN57" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP57" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ57" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AR57" t="s">
         <v>65</v>
@@ -9496,28 +9535,28 @@
         <v>52</v>
       </c>
       <c r="B58" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C58" s="2">
         <v>46310.360796608795</v>
       </c>
       <c r="D58" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F58" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="G58" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="H58" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="I58" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J58" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K58">
         <v>10</v>
@@ -9535,19 +9574,19 @@
         <v>61</v>
       </c>
       <c r="P58" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q58" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R58" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="S58" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="T58" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="U58" t="s">
         <v>64</v>
@@ -9562,22 +9601,22 @@
         <v>66</v>
       </c>
       <c r="Z58" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AA58" t="s">
         <v>67</v>
       </c>
       <c r="AB58" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC58">
         <v>0</v>
       </c>
       <c r="AD58" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AE58" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AF58" s="1">
         <v>46310.360796064815</v>
@@ -9598,19 +9637,19 @@
         <v>0</v>
       </c>
       <c r="AL58" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AM58">
         <v>0</v>
       </c>
       <c r="AN58" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP58" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ58" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AR58" t="s">
         <v>65</v>
@@ -9633,28 +9672,28 @@
         <v>53</v>
       </c>
       <c r="B59" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C59" s="2">
         <v>46310.365529490744</v>
       </c>
       <c r="D59" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F59" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G59" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H59" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I59" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J59" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -9678,13 +9717,13 @@
         <v>63</v>
       </c>
       <c r="R59" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="S59" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="T59" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="U59" t="s">
         <v>64</v>
@@ -9699,7 +9738,7 @@
         <v>66</v>
       </c>
       <c r="Y59" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Z59" t="s">
         <v>65</v>
@@ -9708,16 +9747,16 @@
         <v>67</v>
       </c>
       <c r="AB59" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AC59">
         <v>0</v>
       </c>
       <c r="AD59" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AE59" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF59" s="1">
         <v>46310.364017199077</v>
@@ -9738,19 +9777,19 @@
         <v>0</v>
       </c>
       <c r="AL59" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AM59">
         <v>0</v>
       </c>
       <c r="AN59" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP59" t="s">
         <v>74</v>
       </c>
       <c r="AQ59" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AR59" t="s">
         <v>65</v>
@@ -9773,25 +9812,25 @@
         <v>54</v>
       </c>
       <c r="B60" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C60" s="2">
         <v>46310.367131909719</v>
       </c>
       <c r="D60" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F60" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G60" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="H60" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="I60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J60" t="s">
         <v>342</v>
@@ -9818,7 +9857,7 @@
         <v>63</v>
       </c>
       <c r="T60" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="U60" t="s">
         <v>64</v>
@@ -9833,19 +9872,19 @@
         <v>66</v>
       </c>
       <c r="Z60" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AA60" t="s">
         <v>67</v>
       </c>
       <c r="AB60" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC60">
         <v>0</v>
       </c>
       <c r="AD60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AE60" t="s">
         <v>328</v>
@@ -9869,19 +9908,19 @@
         <v>0</v>
       </c>
       <c r="AL60" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AM60">
         <v>0</v>
       </c>
       <c r="AN60" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP60" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ60" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AR60" t="s">
         <v>65</v>
@@ -9904,28 +9943,28 @@
         <v>55</v>
       </c>
       <c r="B61" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C61" s="2">
         <v>46310.386779826389</v>
       </c>
       <c r="D61" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F61" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G61" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="H61" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I61" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J61" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K61">
         <v>0</v>
@@ -9949,10 +9988,10 @@
         <v>63</v>
       </c>
       <c r="R61" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="T61" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="U61" t="s">
         <v>64</v>
@@ -9979,10 +10018,10 @@
         <v>0</v>
       </c>
       <c r="AD61" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AE61" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF61" s="1">
         <v>46310.386627222222</v>
@@ -10003,13 +10042,13 @@
         <v>0</v>
       </c>
       <c r="AL61" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AM61">
         <v>0</v>
       </c>
       <c r="AN61" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AO61" s="1">
         <v>46311.235778055554</v>
@@ -10018,7 +10057,7 @@
         <v>74</v>
       </c>
       <c r="AQ61" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AR61" t="s">
         <v>65</v>
@@ -10030,7 +10069,7 @@
         <v>76</v>
       </c>
       <c r="AU61" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AV61" t="s">
         <v>65</v>
@@ -10041,28 +10080,28 @@
         <v>56</v>
       </c>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C62" s="2">
         <v>46310.545142060182</v>
       </c>
       <c r="D62" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F62" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="G62" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H62" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I62" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J62" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="K62">
         <v>0</v>
@@ -10071,7 +10110,7 @@
         <v>0</v>
       </c>
       <c r="M62">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="N62" t="s">
         <v>60</v>
@@ -10086,13 +10125,13 @@
         <v>63</v>
       </c>
       <c r="R62" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="S62" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="T62" t="s">
-        <v>109</v>
+        <v>480</v>
       </c>
       <c r="U62" t="s">
         <v>64</v>
@@ -10107,7 +10146,7 @@
         <v>66</v>
       </c>
       <c r="Y62" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="Z62" t="s">
         <v>65</v>
@@ -10122,7 +10161,7 @@
         <v>0</v>
       </c>
       <c r="AD62" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AE62" t="s">
         <v>328</v>
@@ -10137,7 +10176,7 @@
         <v>32</v>
       </c>
       <c r="AI62" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="AJ62">
         <v>147</v>
@@ -10146,22 +10185,22 @@
         <v>0</v>
       </c>
       <c r="AL62" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AM62">
         <v>0</v>
       </c>
       <c r="AN62" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AO62" s="1">
         <v>46311.501728425923</v>
       </c>
       <c r="AP62" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ62" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AR62" t="s">
         <v>65</v>
@@ -10176,7 +10215,7 @@
         <v>77</v>
       </c>
       <c r="AV62" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:48" x14ac:dyDescent="0.25">
@@ -10184,31 +10223,31 @@
         <v>57</v>
       </c>
       <c r="B63" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C63" s="2">
         <v>46310.548003460652</v>
       </c>
       <c r="D63" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E63" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F63" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="G63" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H63" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I63" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J63" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -10226,13 +10265,13 @@
         <v>61</v>
       </c>
       <c r="P63" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q63" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T63" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="U63" t="s">
         <v>64</v>
@@ -10262,7 +10301,7 @@
         <v>69</v>
       </c>
       <c r="AE63" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF63" s="1">
         <v>46310.293574374999</v>
@@ -10274,7 +10313,7 @@
         <v>0</v>
       </c>
       <c r="AI63" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="AJ63">
         <v>0</v>
@@ -10283,13 +10322,13 @@
         <v>0</v>
       </c>
       <c r="AL63" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AM63">
         <v>0</v>
       </c>
       <c r="AN63" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AO63" s="1">
         <v>46310.501391770835</v>
@@ -10298,7 +10337,7 @@
         <v>74</v>
       </c>
       <c r="AQ63" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AR63" t="s">
         <v>65</v>
@@ -10310,10 +10349,10 @@
         <v>76</v>
       </c>
       <c r="AU63" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AV63" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:48" x14ac:dyDescent="0.25">
@@ -10321,28 +10360,28 @@
         <v>58</v>
       </c>
       <c r="B64" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C64" s="2">
         <v>46310.550791365742</v>
       </c>
       <c r="D64" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E64" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F64" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="G64" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H64" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I64" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J64" t="s">
         <v>59</v>
@@ -10369,7 +10408,7 @@
         <v>63</v>
       </c>
       <c r="T64" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="U64" t="s">
         <v>64</v>
@@ -10420,13 +10459,13 @@
         <v>0</v>
       </c>
       <c r="AL64" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="AM64">
         <v>0</v>
       </c>
       <c r="AN64" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AO64" s="1">
         <v>46310.482646111108</v>
@@ -10435,7 +10474,7 @@
         <v>74</v>
       </c>
       <c r="AQ64" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="AR64" t="s">
         <v>65</v>
@@ -10458,25 +10497,25 @@
         <v>59</v>
       </c>
       <c r="B65" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C65" s="2">
         <v>46310.585787812503</v>
       </c>
       <c r="D65" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F65" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="G65" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="H65" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="I65" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J65" t="s">
         <v>335</v>
@@ -10497,16 +10536,16 @@
         <v>61</v>
       </c>
       <c r="P65" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q65" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T65" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="U65" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="V65">
         <v>1</v>
@@ -10524,16 +10563,16 @@
         <v>67</v>
       </c>
       <c r="AB65" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AC65">
         <v>0</v>
       </c>
       <c r="AD65" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AE65" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AF65" s="1">
         <v>46310.585787812503</v>
@@ -10545,7 +10584,7 @@
         <v>0</v>
       </c>
       <c r="AI65" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AJ65">
         <v>0</v>
@@ -10554,19 +10593,19 @@
         <v>0</v>
       </c>
       <c r="AL65" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AM65">
         <v>0</v>
       </c>
       <c r="AN65" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AP65" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AQ65" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AR65" t="s">
         <v>65</v>
@@ -10589,37 +10628,37 @@
         <v>60</v>
       </c>
       <c r="B66" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C66" s="2">
-        <v>46311.294469386572</v>
+        <v>46311.382125937504</v>
       </c>
       <c r="D66" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="F66" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="G66" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="H66" t="s">
-        <v>503</v>
+        <v>468</v>
       </c>
       <c r="I66" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="J66" t="s">
-        <v>504</v>
+        <v>335</v>
       </c>
       <c r="K66">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L66">
         <v>0</v>
       </c>
       <c r="M66">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N66" t="s">
         <v>60</v>
@@ -10628,22 +10667,22 @@
         <v>61</v>
       </c>
       <c r="P66" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="Q66" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="R66" t="s">
+        <v>506</v>
+      </c>
+      <c r="T66" t="s">
         <v>505</v>
-      </c>
-      <c r="T66" t="s">
-        <v>502</v>
       </c>
       <c r="U66" t="s">
         <v>64</v>
       </c>
       <c r="V66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W66" t="s">
         <v>65</v>
@@ -10652,34 +10691,34 @@
         <v>66</v>
       </c>
       <c r="Z66" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AA66" t="s">
         <v>67</v>
       </c>
       <c r="AB66" t="s">
-        <v>164</v>
+        <v>116</v>
       </c>
       <c r="AC66">
         <v>0</v>
       </c>
       <c r="AD66" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AE66" t="s">
-        <v>70</v>
+        <v>328</v>
       </c>
       <c r="AF66" s="1">
-        <v>46311.294468900465</v>
+        <v>46311.382125277778</v>
       </c>
       <c r="AG66">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AH66">
         <v>0</v>
       </c>
       <c r="AI66" t="s">
-        <v>71</v>
+        <v>406</v>
       </c>
       <c r="AJ66">
         <v>1</v>
@@ -10688,19 +10727,19 @@
         <v>0</v>
       </c>
       <c r="AL66" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AM66">
         <v>0</v>
       </c>
       <c r="AN66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP66" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ66" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AR66" t="s">
         <v>65</v>
@@ -10723,31 +10762,28 @@
         <v>61</v>
       </c>
       <c r="B67" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C67" s="2">
-        <v>46311.632166111114</v>
+        <v>46311.493548206017</v>
       </c>
       <c r="D67" t="s">
-        <v>508</v>
-      </c>
-      <c r="E67" t="s">
         <v>509</v>
       </c>
       <c r="F67" t="s">
         <v>510</v>
       </c>
       <c r="G67" t="s">
-        <v>256</v>
+        <v>83</v>
       </c>
       <c r="H67" t="s">
-        <v>257</v>
+        <v>84</v>
       </c>
       <c r="I67" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="J67" t="s">
-        <v>85</v>
+        <v>511</v>
       </c>
       <c r="K67">
         <v>0</v>
@@ -10765,19 +10801,22 @@
         <v>61</v>
       </c>
       <c r="P67" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q67" t="s">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R67">
+        <v>65557835</v>
       </c>
       <c r="T67" t="s">
-        <v>256</v>
+        <v>83</v>
       </c>
       <c r="U67" t="s">
         <v>64</v>
       </c>
       <c r="V67">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W67" t="s">
         <v>65</v>
@@ -10792,19 +10831,19 @@
         <v>67</v>
       </c>
       <c r="AB67" t="s">
-        <v>164</v>
+        <v>68</v>
       </c>
       <c r="AC67">
         <v>0</v>
       </c>
       <c r="AD67" t="s">
-        <v>69</v>
+        <v>166</v>
       </c>
       <c r="AE67" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF67" s="1">
-        <v>46310.403628622684</v>
+        <v>46311.493545960649</v>
       </c>
       <c r="AG67">
         <v>1</v>
@@ -10822,19 +10861,22 @@
         <v>0</v>
       </c>
       <c r="AL67" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AM67">
         <v>0</v>
       </c>
       <c r="AN67" t="s">
-        <v>73</v>
+        <v>105</v>
+      </c>
+      <c r="AO67" s="1">
+        <v>46311.951299652777</v>
       </c>
       <c r="AP67" t="s">
         <v>74</v>
       </c>
       <c r="AQ67" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AR67" t="s">
         <v>65</v>
@@ -10857,32 +10899,26 @@
         <v>62</v>
       </c>
       <c r="B68" t="s">
-        <v>130</v>
+        <v>514</v>
       </c>
       <c r="C68" s="2">
-        <v>46311.634805428243</v>
+        <v>46311.551411377317</v>
       </c>
       <c r="D68" t="s">
-        <v>513</v>
-      </c>
-      <c r="E68" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F68" t="s">
-        <v>515</v>
-      </c>
-      <c r="G68" t="s">
+        <v>479</v>
+      </c>
+      <c r="H68" t="s">
+        <v>153</v>
+      </c>
+      <c r="I68" t="s">
         <v>516</v>
       </c>
-      <c r="H68" t="s">
+      <c r="J68" t="s">
         <v>517</v>
       </c>
-      <c r="I68" t="s">
-        <v>84</v>
-      </c>
-      <c r="J68" t="s">
-        <v>85</v>
-      </c>
       <c r="K68">
         <v>0</v>
       </c>
@@ -10890,7 +10926,7 @@
         <v>0</v>
       </c>
       <c r="M68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N68" t="s">
         <v>60</v>
@@ -10899,19 +10935,22 @@
         <v>61</v>
       </c>
       <c r="P68" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="Q68" t="s">
-        <v>87</v>
+        <v>63</v>
+      </c>
+      <c r="S68" t="s">
+        <v>237</v>
       </c>
       <c r="T68" t="s">
-        <v>171</v>
+        <v>114</v>
       </c>
       <c r="U68" t="s">
-        <v>64</v>
+        <v>164</v>
       </c>
       <c r="V68">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W68" t="s">
         <v>65</v>
@@ -10926,28 +10965,28 @@
         <v>67</v>
       </c>
       <c r="AB68" t="s">
-        <v>68</v>
+        <v>165</v>
       </c>
       <c r="AC68">
         <v>0</v>
       </c>
       <c r="AD68" t="s">
-        <v>69</v>
+        <v>518</v>
       </c>
       <c r="AE68" t="s">
-        <v>88</v>
+        <v>167</v>
       </c>
       <c r="AF68" s="1">
-        <v>46310.849041469904</v>
+        <v>46311.551411377317</v>
       </c>
       <c r="AG68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH68">
         <v>0</v>
       </c>
       <c r="AI68" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="AJ68">
         <v>0</v>
@@ -10956,21 +10995,15 @@
         <v>0</v>
       </c>
       <c r="AL68" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AM68">
         <v>0</v>
       </c>
       <c r="AN68" t="s">
-        <v>519</v>
-      </c>
-      <c r="AO68" s="1">
-        <v>46311.555555567131</v>
+        <v>155</v>
       </c>
       <c r="AP68" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ68" t="s">
         <v>520</v>
       </c>
       <c r="AR68" t="s">
@@ -10978,19 +11011,286 @@
       </c>
       <c r="AS68" t="s">
         <v>65</v>
-      </c>
-      <c r="AT68" t="s">
-        <v>76</v>
       </c>
       <c r="AU68" t="s">
         <v>77</v>
       </c>
       <c r="AV68" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="69" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>63</v>
+      </c>
+      <c r="B69" t="s">
+        <v>131</v>
+      </c>
+      <c r="C69" s="2">
+        <v>46311.632166111114</v>
+      </c>
+      <c r="D69" t="s">
+        <v>521</v>
+      </c>
+      <c r="E69" t="s">
+        <v>522</v>
+      </c>
+      <c r="F69" t="s">
+        <v>523</v>
+      </c>
+      <c r="G69" t="s">
+        <v>258</v>
+      </c>
+      <c r="H69" t="s">
+        <v>259</v>
+      </c>
+      <c r="I69" t="s">
+        <v>85</v>
+      </c>
+      <c r="J69" t="s">
+        <v>86</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>1</v>
+      </c>
+      <c r="N69" t="s">
+        <v>60</v>
+      </c>
+      <c r="O69" t="s">
+        <v>61</v>
+      </c>
+      <c r="P69" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>88</v>
+      </c>
+      <c r="T69" t="s">
+        <v>258</v>
+      </c>
+      <c r="U69" t="s">
+        <v>64</v>
+      </c>
+      <c r="V69">
+        <v>1</v>
+      </c>
+      <c r="W69" t="s">
+        <v>65</v>
+      </c>
+      <c r="X69" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA69" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB69" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC69">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE69" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF69" s="1">
+        <v>46310.403628622684</v>
+      </c>
+      <c r="AG69">
+        <v>1</v>
+      </c>
+      <c r="AH69">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ69">
+        <v>0</v>
+      </c>
+      <c r="AK69">
+        <v>0</v>
+      </c>
+      <c r="AL69" t="s">
+        <v>524</v>
+      </c>
+      <c r="AM69">
+        <v>0</v>
+      </c>
+      <c r="AN69" t="s">
+        <v>73</v>
+      </c>
+      <c r="AP69" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ69" t="s">
+        <v>525</v>
+      </c>
+      <c r="AR69" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS69" t="s">
+        <v>65</v>
+      </c>
+      <c r="AT69" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU69" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV69" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>64</v>
+      </c>
+      <c r="B70" t="s">
+        <v>131</v>
+      </c>
+      <c r="C70" s="2">
+        <v>46311.634805428243</v>
+      </c>
+      <c r="D70" t="s">
+        <v>526</v>
+      </c>
+      <c r="E70" t="s">
+        <v>527</v>
+      </c>
+      <c r="F70" t="s">
+        <v>528</v>
+      </c>
+      <c r="G70" t="s">
+        <v>529</v>
+      </c>
+      <c r="H70" t="s">
+        <v>530</v>
+      </c>
+      <c r="I70" t="s">
+        <v>85</v>
+      </c>
+      <c r="J70" t="s">
+        <v>86</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>1</v>
+      </c>
+      <c r="N70" t="s">
+        <v>60</v>
+      </c>
+      <c r="O70" t="s">
+        <v>61</v>
+      </c>
+      <c r="P70" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>88</v>
+      </c>
+      <c r="T70" t="s">
+        <v>172</v>
+      </c>
+      <c r="U70" t="s">
+        <v>64</v>
+      </c>
+      <c r="V70">
+        <v>1</v>
+      </c>
+      <c r="W70" t="s">
+        <v>65</v>
+      </c>
+      <c r="X70" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA70" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB70" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC70">
+        <v>0</v>
+      </c>
+      <c r="AD70" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE70" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF70" s="1">
+        <v>46310.849041469904</v>
+      </c>
+      <c r="AG70">
+        <v>1</v>
+      </c>
+      <c r="AH70">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ70">
+        <v>0</v>
+      </c>
+      <c r="AK70">
+        <v>0</v>
+      </c>
+      <c r="AL70" t="s">
+        <v>531</v>
+      </c>
+      <c r="AM70">
+        <v>0</v>
+      </c>
+      <c r="AN70" t="s">
+        <v>532</v>
+      </c>
+      <c r="AO70" s="1">
+        <v>46311.555555567131</v>
+      </c>
+      <c r="AP70" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ70" t="s">
+        <v>533</v>
+      </c>
+      <c r="AR70" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS70" t="s">
+        <v>65</v>
+      </c>
+      <c r="AT70" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU70" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV70" t="s">
         <v>65</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Base_DP.xlsx
+++ b/Base_DP.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\USUARIO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27E0575E-B6AC-4C09-9E43-3E041ED63075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C04A345F-545E-4C6D-B4AF-3DD671FB45E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-3345" windowWidth="29040" windowHeight="15720" xr2:uid="{525D4D22-31C3-47D6-A01E-494618E018D1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{E657E9F2-7909-48AC-9DF9-C9CAA913937F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Navegador de incidentes_17_10_2" sheetId="1" r:id="rId1"/>
+    <sheet name="Navegador de incidentes_18_10_2" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="534">
-  <si>
-    <t>Navegador de incidentesNavegador de incidentes-17/10/2026 08:52:35.323</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2302" uniqueCount="588">
+  <si>
+    <t>Navegador de incidentesNavegador de incidentes-18/10/2026 08:58:04.870</t>
   </si>
   <si>
     <t>AND Instrucción contiene dp</t>
@@ -256,96 +256,99 @@
     <t>Alimentador/Troncal MT</t>
   </si>
   <si>
+    <t>DP-BT</t>
+  </si>
+  <si>
+    <t>INC 145565412</t>
+  </si>
+  <si>
+    <t>INC 146609163</t>
+  </si>
+  <si>
+    <t>SAC302955</t>
+  </si>
+  <si>
+    <t>VERDESOL 13.2 KV</t>
+  </si>
+  <si>
+    <t>SALADO</t>
+  </si>
+  <si>
+    <t>Línea reventada</t>
+  </si>
+  <si>
+    <t>DP-CA-S-CentroTolima</t>
+  </si>
+  <si>
+    <t>CELSIA - TOLIMA CENTRO</t>
+  </si>
+  <si>
+    <t>CO-TOL-DI-CELSIA-TNORTE-CENTRO</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>(-8366976.4, 498691.2)</t>
+  </si>
+  <si>
+    <t>CORE\lhernandez</t>
+  </si>
+  <si>
+    <t>VDA LA CAIMA FCA ALTO BONITO</t>
+  </si>
+  <si>
+    <t>Transformador de Distribución MT</t>
+  </si>
+  <si>
+    <t>DP</t>
+  </si>
+  <si>
+    <t>INC 145565615</t>
+  </si>
+  <si>
+    <t>S06931</t>
+  </si>
+  <si>
+    <t>FRESNO 3 13.2 KV</t>
+  </si>
+  <si>
+    <t>FRESNO</t>
+  </si>
+  <si>
+    <t>Puente averiado</t>
+  </si>
+  <si>
+    <t>BOLM-316 (I-16); DP-CA-S-NorteTolima</t>
+  </si>
+  <si>
+    <t>RB2218</t>
+  </si>
+  <si>
+    <t>No restablecido</t>
+  </si>
+  <si>
+    <t>Finalizada; Cancelada</t>
+  </si>
+  <si>
+    <t>Raised</t>
+  </si>
+  <si>
+    <t>(-8351989.6, 584146.8)</t>
+  </si>
+  <si>
+    <t>Llamada</t>
+  </si>
+  <si>
+    <t>Interruptor compuesto</t>
+  </si>
+  <si>
+    <t>SIN DIRECCION</t>
+  </si>
+  <si>
     <t>Sí</t>
   </si>
   <si>
-    <t>DP-BT</t>
-  </si>
-  <si>
-    <t>INC 145565412</t>
-  </si>
-  <si>
-    <t>INC 146609163</t>
-  </si>
-  <si>
-    <t>SAC302955</t>
-  </si>
-  <si>
-    <t>VERDESOL 13.2 KV</t>
-  </si>
-  <si>
-    <t>SALADO</t>
-  </si>
-  <si>
-    <t>Línea reventada</t>
-  </si>
-  <si>
-    <t>DP-CA-S-CentroTolima</t>
-  </si>
-  <si>
-    <t>CELSIA - TOLIMA CENTRO</t>
-  </si>
-  <si>
-    <t>CO-TOL-DI-CELSIA-TNORTE-CENTRO</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>(-8366976.4, 498691.2)</t>
-  </si>
-  <si>
-    <t>CORE\lhernandez</t>
-  </si>
-  <si>
-    <t>VDA LA CAIMA FCA ALTO BONITO</t>
-  </si>
-  <si>
-    <t>Transformador de Distribución MT</t>
-  </si>
-  <si>
-    <t>DP</t>
-  </si>
-  <si>
-    <t>INC 145565615</t>
-  </si>
-  <si>
-    <t>S06931</t>
-  </si>
-  <si>
-    <t>FRESNO 3 13.2 KV</t>
-  </si>
-  <si>
-    <t>FRESNO</t>
-  </si>
-  <si>
-    <t>Puente averiado</t>
-  </si>
-  <si>
-    <t>BOLM-316 (I-16); DP-CA-S-NorteTolima</t>
-  </si>
-  <si>
-    <t>RB2218</t>
-  </si>
-  <si>
-    <t>Finalizada; Cancelada</t>
-  </si>
-  <si>
-    <t>Raised</t>
-  </si>
-  <si>
-    <t>(-8351989.6, 584146.8)</t>
-  </si>
-  <si>
-    <t>Llamada</t>
-  </si>
-  <si>
-    <t>Interruptor compuesto</t>
-  </si>
-  <si>
-    <t>SIN DIRECCION</t>
-  </si>
-  <si>
     <t>INC 145565698</t>
   </si>
   <si>
@@ -364,15 +367,9 @@
     <t>BOLM-369 (M-20A); DP-CA-S-NorteTolima</t>
   </si>
   <si>
-    <t>LIBANO 3 13.2 KV; ARRIEROS CTO 1; ARRIEROS LIBANO 34.5 kV; LIBANO 34.5 KV</t>
-  </si>
-  <si>
     <t>OTR</t>
   </si>
   <si>
-    <t>No restablecido</t>
-  </si>
-  <si>
     <t>Finalizada; Pendiente</t>
   </si>
   <si>
@@ -544,7 +541,10 @@
     <t>NUEVA CAJAMARCA</t>
   </si>
   <si>
-    <t>BOLV-303</t>
+    <t>BOLV-303; BOLM-353</t>
+  </si>
+  <si>
+    <t>Finalizada; Finalizada</t>
   </si>
   <si>
     <t>(-8402147.2, 483370.1)</t>
@@ -655,6 +655,9 @@
     <t>66583368A</t>
   </si>
   <si>
+    <t>BOLM-316 (I-16); OBRAS-5</t>
+  </si>
+  <si>
     <t>(-8355760.9, 573704.5)</t>
   </si>
   <si>
@@ -673,9 +676,6 @@
     <t>BOLM-309 (I-9); CUAD-302</t>
   </si>
   <si>
-    <t>Finalizada; Finalizada</t>
-  </si>
-  <si>
     <t>(-8363526.4, 500943.5)</t>
   </si>
   <si>
@@ -760,306 +760,285 @@
     <t>VDA LIMONCITO</t>
   </si>
   <si>
-    <t>INC 146609617</t>
-  </si>
-  <si>
-    <t>INC 146609003</t>
-  </si>
-  <si>
-    <t>2221705A</t>
-  </si>
-  <si>
-    <t>BOLM-320; CUAD-356</t>
-  </si>
-  <si>
-    <t>Cancelada; Finalizada</t>
+    <t>INC 146609774</t>
+  </si>
+  <si>
+    <t>INC 146608782</t>
+  </si>
+  <si>
+    <t>SAC329071</t>
+  </si>
+  <si>
+    <t>BRISAS 3 13.2 KV</t>
+  </si>
+  <si>
+    <t>BRISAS</t>
+  </si>
+  <si>
+    <t>Alta vegetación</t>
+  </si>
+  <si>
+    <t>CUAD-306</t>
+  </si>
+  <si>
+    <t>Finalizada</t>
+  </si>
+  <si>
+    <t>(-8377753.2, 491504.4)</t>
+  </si>
+  <si>
+    <t>CORE\avalenciac</t>
+  </si>
+  <si>
+    <t>VDA BOQUERON RANCHO TOLEDO</t>
+  </si>
+  <si>
+    <t>INC 146609886</t>
+  </si>
+  <si>
+    <t>SAC199981</t>
+  </si>
+  <si>
+    <t>ARRIEROS CTO 1</t>
+  </si>
+  <si>
+    <t>66631672A</t>
+  </si>
+  <si>
+    <t>LRD</t>
+  </si>
+  <si>
+    <t>(-8352029.2, 556608.0)</t>
+  </si>
+  <si>
+    <t>VDA EL CIRPE FCA TERAMA</t>
+  </si>
+  <si>
+    <t>INC 146609913</t>
+  </si>
+  <si>
+    <t>S07685</t>
+  </si>
+  <si>
+    <t>1469118A</t>
+  </si>
+  <si>
+    <t>(-8349970.3, 574469.5)</t>
+  </si>
+  <si>
+    <t>VDA LA SIERRA</t>
+  </si>
+  <si>
+    <t>INC 146610431</t>
+  </si>
+  <si>
+    <t>INC 146608671</t>
+  </si>
+  <si>
+    <t>SAC376300</t>
+  </si>
+  <si>
+    <t>PASTALES 13.2 KV</t>
+  </si>
+  <si>
+    <t>CHAPETON</t>
+  </si>
+  <si>
+    <t>CUAD-304</t>
+  </si>
+  <si>
+    <t>(-8381004.0, 500561.9)</t>
+  </si>
+  <si>
+    <t>VDA MARIA PIEDRA GRANDE VIA VALLE ESCONDIDO</t>
+  </si>
+  <si>
+    <t>INC 146611075</t>
+  </si>
+  <si>
+    <t>SAC133557</t>
+  </si>
+  <si>
+    <t>65612747A</t>
+  </si>
+  <si>
+    <t>(-8364749.7, 501022.3)</t>
+  </si>
+  <si>
+    <t>VDA CARRISALES F TESORITO</t>
+  </si>
+  <si>
+    <t>DP / BT</t>
+  </si>
+  <si>
+    <t>INC 146611166</t>
+  </si>
+  <si>
+    <t>66035670A</t>
+  </si>
+  <si>
+    <t>BOLV-396 (Apoyo); DP-CA-S-NorteTolima</t>
+  </si>
+  <si>
+    <t>66035743A</t>
+  </si>
+  <si>
+    <t>(-8346068.6, 584531.2)</t>
+  </si>
+  <si>
+    <t>VRD LA MESA</t>
+  </si>
+  <si>
+    <t>INC 146611183</t>
+  </si>
+  <si>
+    <t>66038106A</t>
+  </si>
+  <si>
+    <t>JUNIN 13.2 KV</t>
+  </si>
+  <si>
+    <t>SANTA ISABEL; LERIDA</t>
+  </si>
+  <si>
+    <t>BOLM-328 (I-28); TRAF-394</t>
+  </si>
+  <si>
+    <t>S07092</t>
+  </si>
+  <si>
+    <t>(-8352253.5, 535624.2)</t>
+  </si>
+  <si>
+    <t>VRD EL JARDIN</t>
+  </si>
+  <si>
+    <t>INC 146611720</t>
+  </si>
+  <si>
+    <t>INC 146610076</t>
+  </si>
+  <si>
+    <t>SAC264344</t>
+  </si>
+  <si>
+    <t>PIEDRAS 13.2 KV</t>
+  </si>
+  <si>
+    <t>ALVARADO</t>
+  </si>
+  <si>
+    <t>(-8335093.4, 506178.5)</t>
+  </si>
+  <si>
+    <t>VDA EL BEBEDERO LA PUNTA</t>
+  </si>
+  <si>
+    <t>INC 146612033</t>
+  </si>
+  <si>
+    <t>2227886A</t>
+  </si>
+  <si>
+    <t>S06098</t>
+  </si>
+  <si>
+    <t>(-8353595.1, 534721.2)</t>
+  </si>
+  <si>
+    <t>VDA EL JARDIN</t>
+  </si>
+  <si>
+    <t>INC 146612900</t>
+  </si>
+  <si>
+    <t>3418676-A</t>
+  </si>
+  <si>
+    <t>EL TABLAZO 13.2 KV</t>
+  </si>
+  <si>
+    <t>PADUA</t>
+  </si>
+  <si>
+    <t>(-8355263.8, 586716.2)</t>
+  </si>
+  <si>
+    <t>VDA ESPAÑA FCA COLONIA</t>
+  </si>
+  <si>
+    <t>INC 146613285</t>
+  </si>
+  <si>
+    <t>INC 146612298</t>
+  </si>
+  <si>
+    <t>S06766</t>
+  </si>
+  <si>
+    <t>VENADILLO 2 13.2 KV</t>
+  </si>
+  <si>
+    <t>VENADILLO</t>
+  </si>
+  <si>
+    <t>L1 L2 L3</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>(-8341062.9, 518346.3)</t>
+  </si>
+  <si>
+    <t>CORE\eilenis</t>
+  </si>
+  <si>
+    <t>Ramal MT</t>
+  </si>
+  <si>
+    <t>INC 146613549</t>
+  </si>
+  <si>
+    <t>66856216A</t>
+  </si>
+  <si>
+    <t>BOLV-372 (M-21B); DP-CA-S-NorteTolima</t>
+  </si>
+  <si>
+    <t>S04769</t>
+  </si>
+  <si>
+    <t>(-8343611.7, 544895.6)</t>
+  </si>
+  <si>
+    <t>VDA COLOYA</t>
+  </si>
+  <si>
+    <t>INC 146613559</t>
+  </si>
+  <si>
+    <t>66629228A</t>
+  </si>
+  <si>
+    <t>VENADILLO; SANTA ISABEL</t>
+  </si>
+  <si>
+    <t>BOLV-360; DP-CA-S-NorteTolima</t>
+  </si>
+  <si>
+    <t>RC1382</t>
+  </si>
+  <si>
+    <t>SAN JUAN 13.2 KV; VENADILLO 2 13.2 KV</t>
+  </si>
+  <si>
+    <t>Cancelada; Pendiente</t>
   </si>
   <si>
     <t>L2 L3</t>
   </si>
   <si>
-    <t>(-8351584.2, 558510.3)</t>
-  </si>
-  <si>
-    <t>CORE\avalenciac</t>
-  </si>
-  <si>
-    <t>VDA PATIBURRI</t>
-  </si>
-  <si>
-    <t>INC 146609774</t>
-  </si>
-  <si>
-    <t>INC 146608782</t>
-  </si>
-  <si>
-    <t>SAC329071</t>
-  </si>
-  <si>
-    <t>BRISAS 3 13.2 KV</t>
-  </si>
-  <si>
-    <t>BRISAS</t>
-  </si>
-  <si>
-    <t>Alta vegetación</t>
-  </si>
-  <si>
-    <t>CUAD-306</t>
-  </si>
-  <si>
-    <t>Finalizada</t>
-  </si>
-  <si>
-    <t>(-8377753.2, 491504.4)</t>
-  </si>
-  <si>
-    <t>VDA BOQUERON RANCHO TOLEDO</t>
-  </si>
-  <si>
-    <t>INC 146609886</t>
-  </si>
-  <si>
-    <t>SAC199981</t>
-  </si>
-  <si>
-    <t>ARRIEROS CTO 1</t>
-  </si>
-  <si>
-    <t>66631672A</t>
-  </si>
-  <si>
-    <t>LRD</t>
-  </si>
-  <si>
-    <t>(-8352029.2, 556608.0)</t>
-  </si>
-  <si>
-    <t>VDA EL CIRPE FCA TERAMA</t>
-  </si>
-  <si>
-    <t>INC 146609913</t>
-  </si>
-  <si>
-    <t>S07685</t>
-  </si>
-  <si>
-    <t>1469118A</t>
-  </si>
-  <si>
-    <t>(-8349970.3, 574469.5)</t>
-  </si>
-  <si>
-    <t>VDA LA SIERRA</t>
-  </si>
-  <si>
-    <t>INC 146610431</t>
-  </si>
-  <si>
-    <t>INC 146608671</t>
-  </si>
-  <si>
-    <t>SAC376300</t>
-  </si>
-  <si>
-    <t>PASTALES 13.2 KV</t>
-  </si>
-  <si>
-    <t>CHAPETON</t>
-  </si>
-  <si>
-    <t>CUAD-304</t>
-  </si>
-  <si>
-    <t>(-8381004.0, 500561.9)</t>
-  </si>
-  <si>
-    <t>VDA MARIA PIEDRA GRANDE VIA VALLE ESCONDIDO</t>
-  </si>
-  <si>
-    <t>INC 146611075</t>
-  </si>
-  <si>
-    <t>SAC133557</t>
-  </si>
-  <si>
-    <t>65612747A</t>
-  </si>
-  <si>
-    <t>(-8364749.7, 501022.3)</t>
-  </si>
-  <si>
-    <t>VDA CARRISALES F TESORITO</t>
-  </si>
-  <si>
-    <t>DP / BT</t>
-  </si>
-  <si>
-    <t>INC 146611166</t>
-  </si>
-  <si>
-    <t>66035670A</t>
-  </si>
-  <si>
-    <t>BOLV-396 (Apoyo); DP-CA-S-NorteTolima</t>
-  </si>
-  <si>
-    <t>66035743A</t>
-  </si>
-  <si>
-    <t>(-8346068.6, 584531.2)</t>
-  </si>
-  <si>
-    <t>VRD LA MESA</t>
-  </si>
-  <si>
-    <t>INC 146611183</t>
-  </si>
-  <si>
-    <t>66038106A</t>
-  </si>
-  <si>
-    <t>JUNIN 13.2 KV</t>
-  </si>
-  <si>
-    <t>SANTA ISABEL; LERIDA</t>
-  </si>
-  <si>
-    <t>BOLM-328 (I-28); TRAF-394</t>
-  </si>
-  <si>
-    <t>S07092</t>
-  </si>
-  <si>
-    <t>(-8352253.5, 535624.2)</t>
-  </si>
-  <si>
-    <t>VRD EL JARDIN</t>
-  </si>
-  <si>
-    <t>INC 146611720</t>
-  </si>
-  <si>
-    <t>INC 146610076</t>
-  </si>
-  <si>
-    <t>SAC264344</t>
-  </si>
-  <si>
-    <t>PIEDRAS 13.2 KV</t>
-  </si>
-  <si>
-    <t>ALVARADO</t>
-  </si>
-  <si>
-    <t>(-8335093.4, 506178.5)</t>
-  </si>
-  <si>
-    <t>VDA EL BEBEDERO LA PUNTA</t>
-  </si>
-  <si>
-    <t>INC 146612033</t>
-  </si>
-  <si>
-    <t>2227886A</t>
-  </si>
-  <si>
-    <t>S06098</t>
-  </si>
-  <si>
-    <t>(-8353595.1, 534721.2)</t>
-  </si>
-  <si>
-    <t>VDA EL JARDIN</t>
-  </si>
-  <si>
-    <t>INC 146612900</t>
-  </si>
-  <si>
-    <t>3418676-A</t>
-  </si>
-  <si>
-    <t>EL TABLAZO 13.2 KV</t>
-  </si>
-  <si>
-    <t>PADUA</t>
-  </si>
-  <si>
-    <t>(-8355263.8, 586716.2)</t>
-  </si>
-  <si>
-    <t>VDA ESPAÑA FCA COLONIA</t>
-  </si>
-  <si>
-    <t>INC 146613285</t>
-  </si>
-  <si>
-    <t>INC 146612298</t>
-  </si>
-  <si>
-    <t>S06766</t>
-  </si>
-  <si>
-    <t>VENADILLO 2 13.2 KV</t>
-  </si>
-  <si>
-    <t>VENADILLO</t>
-  </si>
-  <si>
-    <t>L1 L2 L3</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>(-8341062.9, 518346.3)</t>
-  </si>
-  <si>
-    <t>CORE\eilenis</t>
-  </si>
-  <si>
-    <t>Ramal MT</t>
-  </si>
-  <si>
-    <t>INC 146613549</t>
-  </si>
-  <si>
-    <t>66856216A</t>
-  </si>
-  <si>
-    <t>BOLV-372 (M-21B); DP-CA-S-NorteTolima</t>
-  </si>
-  <si>
-    <t>S04769</t>
-  </si>
-  <si>
-    <t>(-8343611.7, 544895.6)</t>
-  </si>
-  <si>
-    <t>VDA COLOYA</t>
-  </si>
-  <si>
-    <t>INC 146613559</t>
-  </si>
-  <si>
-    <t>66629228A</t>
-  </si>
-  <si>
-    <t>VENADILLO; SANTA ISABEL</t>
-  </si>
-  <si>
-    <t>BOLV-360; DP-CA-S-NorteTolima</t>
-  </si>
-  <si>
-    <t>RC1382</t>
-  </si>
-  <si>
-    <t>ANZOATEGUI 13.2 KV; VENADILLO 2 13.2 KV</t>
-  </si>
-  <si>
-    <t>Cancelada; Pendiente</t>
-  </si>
-  <si>
     <t>(-8344869.9, 520745.2)</t>
   </si>
   <si>
@@ -1099,7 +1078,7 @@
     <t>Error de operación en Campo</t>
   </si>
   <si>
-    <t>LIBANO 2 13.2 KV; LIBANO 5 13.2 KV</t>
+    <t>LIBANO 5 13.2 KV; LIBANO 2 13.2 KV</t>
   </si>
   <si>
     <t>(-8355912.2, 548391.9)</t>
@@ -1114,6 +1093,9 @@
     <t>2089106-A</t>
   </si>
   <si>
+    <t>BOLM-369 (M-20A); CUAD-353</t>
+  </si>
+  <si>
     <t>(-8349359.0, 546132.9)</t>
   </si>
   <si>
@@ -1126,9 +1108,15 @@
     <t>4022330-A</t>
   </si>
   <si>
+    <t>BOLV-370 (M-20B); DP-CA-S-NorteTolima; CUAD-353</t>
+  </si>
+  <si>
     <t>S05578</t>
   </si>
   <si>
+    <t>Finalizada; Cancelada; Finalizada</t>
+  </si>
+  <si>
     <t>(-8345826.4, 543450.2)</t>
   </si>
   <si>
@@ -1171,9 +1159,6 @@
     <t>S06323</t>
   </si>
   <si>
-    <t>VENADILLO 2 13.2 KV; ANZOATEGUI 13.2 KV</t>
-  </si>
-  <si>
     <t>(-8343467.0, 520548.9)</t>
   </si>
   <si>
@@ -1351,6 +1336,27 @@
     <t>VDA PAVAS</t>
   </si>
   <si>
+    <t>INC 146616583</t>
+  </si>
+  <si>
+    <t>65931206A</t>
+  </si>
+  <si>
+    <t>BRISAS 2 13.2 KV</t>
+  </si>
+  <si>
+    <t>BOLV-330 (M-114A); BOLM-302 (I-2)</t>
+  </si>
+  <si>
+    <t>RC1168</t>
+  </si>
+  <si>
+    <t>(-8374969.1, 492303.0)</t>
+  </si>
+  <si>
+    <t>VDA MARTINICA ALTA</t>
+  </si>
+  <si>
     <t>INC 146616682</t>
   </si>
   <si>
@@ -1366,6 +1372,9 @@
     <t>S06993</t>
   </si>
   <si>
+    <t>SAN JUAN 13.2 KV; ANZOATEGUI 13.2 KV</t>
+  </si>
+  <si>
     <t>(-8356752.7, 517734.2)</t>
   </si>
   <si>
@@ -1450,135 +1459,183 @@
     <t>VDA INVASION ALTO EL ROMPE</t>
   </si>
   <si>
-    <t>INC 146617036</t>
-  </si>
-  <si>
-    <t>66037053A</t>
-  </si>
-  <si>
-    <t>BOLV-370 (M-20B); BOLM-369 (M-20A); DP-CA-S-NorteTolima</t>
+    <t>INC 146616780</t>
+  </si>
+  <si>
+    <t>66586634A</t>
+  </si>
+  <si>
+    <t>BOLM-324 (I-24); DP-CA-S-NorteTolima</t>
+  </si>
+  <si>
+    <t>S06526</t>
+  </si>
+  <si>
+    <t>(-8349520.7, 524635.5)</t>
+  </si>
+  <si>
+    <t>VDA MALABAR</t>
+  </si>
+  <si>
+    <t>INC 146616819</t>
+  </si>
+  <si>
+    <t>SAN JORGE 1 13.2 KV</t>
+  </si>
+  <si>
+    <t>SAN JORGE</t>
+  </si>
+  <si>
+    <t>Ninguna</t>
+  </si>
+  <si>
+    <t>BOLM-302 (I-2); DP-CA-S-CentroTolima</t>
+  </si>
+  <si>
+    <t>65918161-A</t>
+  </si>
+  <si>
+    <t>(-8376300.0, 496627.9)</t>
+  </si>
+  <si>
+    <t>CRA 14 No 1D 57 ALASKA PARTE ALTA IBAGUE</t>
+  </si>
+  <si>
+    <t>INC 146617040</t>
+  </si>
+  <si>
+    <t>INC 146616602</t>
+  </si>
+  <si>
+    <t>SAC362175</t>
+  </si>
+  <si>
+    <t>(-8392349.9, 493262.2)</t>
+  </si>
+  <si>
+    <t>VDA BRASIL LAVADERO LOS MANDARINO</t>
+  </si>
+  <si>
+    <t>INC 146617045</t>
+  </si>
+  <si>
+    <t>INC 146616747</t>
+  </si>
+  <si>
+    <t>SAC128825</t>
+  </si>
+  <si>
+    <t>(-8347209.9, 539693.9)</t>
+  </si>
+  <si>
+    <t>VDA CARABALI FCA EL TABOR</t>
+  </si>
+  <si>
+    <t>DP - NORMALIZAR FUSIBLE TRAFO SERVISIOS AUXILIARES RC420</t>
+  </si>
+  <si>
+    <t>INC 146617100</t>
+  </si>
+  <si>
+    <t>RC420</t>
+  </si>
+  <si>
+    <t>SANTA ISABEL 34.5 KV</t>
+  </si>
+  <si>
+    <t>SANTA ISABEL 34.5 KV; AMBALEMA 34.5 KV; RIORECIO 1 34.5 KV</t>
+  </si>
+  <si>
+    <t>(-8342192.9, 534426.8)</t>
+  </si>
+  <si>
+    <t>Reconectador</t>
+  </si>
+  <si>
+    <t>VDA LA SIERRA S/E RIORECIO</t>
+  </si>
+  <si>
+    <t>INC 146617722</t>
+  </si>
+  <si>
+    <t>65152630-A</t>
+  </si>
+  <si>
+    <t>BOLM-319 (I-19); BOLM-318 (I-18); DP-CA-S-NorteTolima</t>
+  </si>
+  <si>
+    <t>Finalizada; Finalizada; Pendiente</t>
+  </si>
+  <si>
+    <t>(-8354412.2, 576671.2)</t>
+  </si>
+  <si>
+    <t>VDA MULATO</t>
+  </si>
+  <si>
+    <t>INC 146617798</t>
+  </si>
+  <si>
+    <t>66752331A</t>
+  </si>
+  <si>
+    <t>LERIDA 3 13.2 KV</t>
+  </si>
+  <si>
+    <t>S07470</t>
+  </si>
+  <si>
+    <t>(-8335995.1, 545597.3)</t>
+  </si>
+  <si>
+    <t>VDA BLEDONIA</t>
+  </si>
+  <si>
+    <t>INC 146617866</t>
+  </si>
+  <si>
+    <t>2229463A</t>
+  </si>
+  <si>
+    <t>S07739</t>
+  </si>
+  <si>
+    <t>(-8354707.2, 558761.2)</t>
+  </si>
+  <si>
+    <t>VDA BAGAZAL</t>
+  </si>
+  <si>
+    <t>INC 146617966</t>
+  </si>
+  <si>
+    <t>SAC133793</t>
+  </si>
+  <si>
+    <t>BOLV-399 (Apoyo); DP-CA-S-CentroTolima</t>
+  </si>
+  <si>
+    <t>(-8366956.0, 495866.9)</t>
+  </si>
+  <si>
+    <t>VDA CHEMBE</t>
+  </si>
+  <si>
+    <t>DP - Revisar Posible puente averiado, entre el Cto. 1 13.2 kV S/E Arrieros y el RC1212 Frontera con el Cto. 3 13.2 kV S/E Libano</t>
+  </si>
+  <si>
+    <t>INC 146618019</t>
   </si>
   <si>
     <t>L250</t>
   </si>
   <si>
-    <t>ARRIEROS CTO 1; ARRIEROS LIBANO 34.5 kV; LIBANO 3 13.2 KV; LIBANO 34.5 KV</t>
-  </si>
-  <si>
-    <t>RSL; VCD</t>
-  </si>
-  <si>
-    <t>Finalizada; Cancelada; Pendiente</t>
-  </si>
-  <si>
-    <t>Critical</t>
-  </si>
-  <si>
-    <t>(-8354371.4, 550059.7)</t>
-  </si>
-  <si>
-    <t>INC 146617040</t>
-  </si>
-  <si>
-    <t>INC 146616602</t>
-  </si>
-  <si>
-    <t>SAC362175</t>
-  </si>
-  <si>
-    <t>(-8392349.9, 493262.2)</t>
-  </si>
-  <si>
-    <t>VDA BRASIL LAVADERO LOS MANDARINO</t>
-  </si>
-  <si>
-    <t>INC 146617045</t>
-  </si>
-  <si>
-    <t>INC 146616747</t>
-  </si>
-  <si>
-    <t>SAC128825</t>
-  </si>
-  <si>
-    <t>(-8347209.9, 539693.9)</t>
-  </si>
-  <si>
-    <t>VDA CARABALI FCA EL TABOR</t>
-  </si>
-  <si>
-    <t>DP - NORMALIZAR FUSIBLE TRAFO SERVISIOS AUXILIARES RC420</t>
-  </si>
-  <si>
-    <t>INC 146617100</t>
-  </si>
-  <si>
-    <t>RC420</t>
-  </si>
-  <si>
-    <t>SANTA ISABEL 34.5 KV</t>
-  </si>
-  <si>
-    <t>RIORECIO 1 34.5 KV; SANTA ISABEL 34.5 KV; AMBALEMA 34.5 KV</t>
-  </si>
-  <si>
-    <t>(-8342192.9, 534426.8)</t>
-  </si>
-  <si>
-    <t>Reconectador</t>
-  </si>
-  <si>
-    <t>VDA LA SIERRA S/E RIORECIO</t>
-  </si>
-  <si>
-    <t>INC 146617798</t>
-  </si>
-  <si>
-    <t>66752331A</t>
-  </si>
-  <si>
-    <t>LERIDA 3 13.2 KV</t>
-  </si>
-  <si>
-    <t>S07470</t>
-  </si>
-  <si>
-    <t>(-8335995.1, 545597.3)</t>
-  </si>
-  <si>
-    <t>VDA BLEDONIA</t>
-  </si>
-  <si>
-    <t>INC 146617966</t>
-  </si>
-  <si>
-    <t>SAC133793</t>
-  </si>
-  <si>
-    <t>BOLV-399 (Apoyo); DP-CA-S-CentroTolima</t>
-  </si>
-  <si>
-    <t>(-8366956.0, 495866.9)</t>
-  </si>
-  <si>
-    <t>VDA CHEMBE</t>
-  </si>
-  <si>
-    <t>DP - Revisar Posible puente averiado, entre el Cto. 1 13.2 kV S/E Arrieros y el RC1212 Frontera con el Cto. 3 13.2 kV S/E Libano</t>
-  </si>
-  <si>
-    <t>INC 146618019</t>
-  </si>
-  <si>
     <t>Punto caliente</t>
   </si>
   <si>
     <t>DP-CA-S-NorteTolima; BOLM-369 (M-20A)</t>
   </si>
   <si>
-    <t>Pendiente; Iniciada</t>
-  </si>
-  <si>
     <t>(-8357159.6, 548664.4)</t>
   </si>
   <si>
@@ -1622,6 +1679,111 @@
   </si>
   <si>
     <t>VDA LA JUDEA-FONDA BALCONCITO</t>
+  </si>
+  <si>
+    <t>INC 146618642</t>
+  </si>
+  <si>
+    <t>INC 146618555</t>
+  </si>
+  <si>
+    <t>2220172-A</t>
+  </si>
+  <si>
+    <t>(-8355953.6, 575271.8)</t>
+  </si>
+  <si>
+    <t>CORE\midrobo</t>
+  </si>
+  <si>
+    <t>VDA LA FLORIDA</t>
+  </si>
+  <si>
+    <t>INC 146618649</t>
+  </si>
+  <si>
+    <t>SAC135970</t>
+  </si>
+  <si>
+    <t>(-8381186.0, 499828.1)</t>
+  </si>
+  <si>
+    <t>VDA LA MARIA FINCA BALCONES</t>
+  </si>
+  <si>
+    <t>INC 146618711</t>
+  </si>
+  <si>
+    <t>66945340A</t>
+  </si>
+  <si>
+    <t>(-8348709.2, 568906.0)</t>
+  </si>
+  <si>
+    <t>VDA PAUJIL</t>
+  </si>
+  <si>
+    <t>INC 146618814</t>
+  </si>
+  <si>
+    <t>INC 146617701</t>
+  </si>
+  <si>
+    <t>SAC400206</t>
+  </si>
+  <si>
+    <t>(-8373989.9, 498858.8)</t>
+  </si>
+  <si>
+    <t>VDA ANCON AL LADO ESCUELA TESORITO</t>
+  </si>
+  <si>
+    <t>INC 146618961</t>
+  </si>
+  <si>
+    <t>1498657A</t>
+  </si>
+  <si>
+    <t>EL SALTO CTO 3 A 13,2 kV</t>
+  </si>
+  <si>
+    <t>EL SALTO</t>
+  </si>
+  <si>
+    <t>Fuga de aceite</t>
+  </si>
+  <si>
+    <t>BOLV-365 (M-18C); GRUA-358</t>
+  </si>
+  <si>
+    <t>(-8321818.8, 579880.5)</t>
+  </si>
+  <si>
+    <t>CRA 26ANº8A-05</t>
+  </si>
+  <si>
+    <t>POSIBLE DA DEL RB2533 CTO 2 13.2 KV SE PALOCABILDO; DP</t>
+  </si>
+  <si>
+    <t>INC 146619013</t>
+  </si>
+  <si>
+    <t>RB2533</t>
+  </si>
+  <si>
+    <t>PALOCABILDO 2 13.2 KV; GUAYABAL 2 13.2 KV</t>
+  </si>
+  <si>
+    <t>BOLM-320; CUAD-356; BOLM-321 (I-21); BOLM-315 (I-15)</t>
+  </si>
+  <si>
+    <t>Cancelada; Finalizada; Cancelada; Pendiente</t>
+  </si>
+  <si>
+    <t>(-8350424.5, 561589.1)</t>
+  </si>
+  <si>
+    <t>VDA ALTO DEL OSO</t>
   </si>
 </sst>
 </file>
@@ -2466,8 +2628,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6310389-F91D-43B3-B5A5-AF584BBA4434}">
-  <dimension ref="A1:AV70"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DFE9A1-4660-4F44-AAE8-0073F206D76E}">
+  <dimension ref="A1:AV79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
@@ -2752,7 +2914,7 @@
         <v>73</v>
       </c>
       <c r="AO7" s="1">
-        <v>46311.903002384257</v>
+        <v>46312.327777789353</v>
       </c>
       <c r="AP7" t="s">
         <v>74</v>
@@ -2773,7 +2935,7 @@
         <v>77</v>
       </c>
       <c r="AV7" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:48" x14ac:dyDescent="0.25">
@@ -2781,31 +2943,31 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C8" s="2">
         <v>46308.125798182868</v>
       </c>
       <c r="D8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" t="s">
         <v>80</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>81</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>82</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>83</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>84</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>85</v>
-      </c>
-      <c r="J8" t="s">
-        <v>86</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -2823,13 +2985,13 @@
         <v>61</v>
       </c>
       <c r="P8" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q8" t="s">
         <v>87</v>
       </c>
-      <c r="Q8" t="s">
-        <v>88</v>
-      </c>
       <c r="T8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U8" t="s">
         <v>64</v>
@@ -2859,7 +3021,7 @@
         <v>69</v>
       </c>
       <c r="AE8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF8" s="1">
         <v>46302.922558368053</v>
@@ -2880,13 +3042,13 @@
         <v>0</v>
       </c>
       <c r="AL8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="s">
         <v>90</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>91</v>
       </c>
       <c r="AO8" s="1">
         <v>46311.951288958335</v>
@@ -2895,7 +3057,7 @@
         <v>74</v>
       </c>
       <c r="AQ8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AR8" t="s">
         <v>65</v>
@@ -2907,7 +3069,7 @@
         <v>76</v>
       </c>
       <c r="AU8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AV8" t="s">
         <v>65</v>
@@ -2918,37 +3080,37 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C9" s="2">
         <v>46308.333507453703</v>
       </c>
       <c r="D9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" t="s">
         <v>95</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>96</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>97</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>98</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>99</v>
       </c>
-      <c r="J9" t="s">
-        <v>100</v>
-      </c>
       <c r="K9">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="N9" t="s">
         <v>60</v>
@@ -2963,10 +3125,10 @@
         <v>63</v>
       </c>
       <c r="R9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U9" t="s">
         <v>64</v>
@@ -2987,7 +3149,7 @@
         <v>67</v>
       </c>
       <c r="AB9" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -2996,7 +3158,7 @@
         <v>102</v>
       </c>
       <c r="AE9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF9" s="1">
         <v>46308.333506273149</v>
@@ -3025,9 +3187,6 @@
       <c r="AN9" t="s">
         <v>105</v>
       </c>
-      <c r="AO9" s="1">
-        <v>46311.235955150463</v>
-      </c>
       <c r="AP9" t="s">
         <v>106</v>
       </c>
@@ -3047,7 +3206,7 @@
         <v>77</v>
       </c>
       <c r="AV9" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:48" x14ac:dyDescent="0.25">
@@ -3055,28 +3214,28 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C10" s="2">
         <v>46308.366301817128</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K10">
         <v>14</v>
@@ -3100,7 +3259,7 @@
         <v>63</v>
       </c>
       <c r="T10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="U10" t="s">
         <v>64</v>
@@ -3118,22 +3277,22 @@
         <v>115</v>
       </c>
       <c r="Z10" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AA10" t="s">
         <v>67</v>
       </c>
       <c r="AB10" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="s">
         <v>116</v>
       </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="s">
+      <c r="AE10" t="s">
         <v>117</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>118</v>
       </c>
       <c r="AF10" s="1">
         <v>46308.366301215276</v>
@@ -3154,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="AL10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AM10">
         <v>0</v>
@@ -3166,7 +3325,7 @@
         <v>106</v>
       </c>
       <c r="AQ10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AR10" t="s">
         <v>65</v>
@@ -3178,10 +3337,10 @@
         <v>76</v>
       </c>
       <c r="AU10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AV10" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:48" x14ac:dyDescent="0.25">
@@ -3189,28 +3348,28 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C11" s="2">
         <v>46294.380958240741</v>
       </c>
       <c r="D11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F11" t="s">
         <v>121</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>122</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>123</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>124</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>125</v>
-      </c>
-      <c r="J11" t="s">
-        <v>126</v>
       </c>
       <c r="K11">
         <v>6</v>
@@ -3234,10 +3393,10 @@
         <v>63</v>
       </c>
       <c r="R11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="T11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="U11" t="s">
         <v>64</v>
@@ -3252,13 +3411,13 @@
         <v>66</v>
       </c>
       <c r="Z11" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AA11" t="s">
         <v>67</v>
       </c>
       <c r="AB11" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -3267,7 +3426,7 @@
         <v>102</v>
       </c>
       <c r="AE11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AF11" s="1">
         <v>46294.380957696761</v>
@@ -3288,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="AL11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AM11">
         <v>0</v>
@@ -3300,7 +3459,7 @@
         <v>106</v>
       </c>
       <c r="AQ11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AR11" t="s">
         <v>65</v>
@@ -3315,7 +3474,7 @@
         <v>77</v>
       </c>
       <c r="AV11" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:48" x14ac:dyDescent="0.25">
@@ -3323,28 +3482,28 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C12" s="2">
         <v>46296.351475081021</v>
       </c>
       <c r="D12" t="s">
+        <v>131</v>
+      </c>
+      <c r="F12" t="s">
         <v>132</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H12" t="s">
+        <v>112</v>
+      </c>
+      <c r="I12" t="s">
         <v>133</v>
       </c>
-      <c r="G12" t="s">
-        <v>110</v>
-      </c>
-      <c r="H12" t="s">
-        <v>111</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>134</v>
-      </c>
-      <c r="J12" t="s">
-        <v>135</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -3368,10 +3527,10 @@
         <v>63</v>
       </c>
       <c r="R12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="T12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="U12" t="s">
         <v>64</v>
@@ -3398,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="AD12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AE12" t="s">
         <v>70</v>
@@ -3422,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="AL12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AM12">
         <v>0</v>
@@ -3431,13 +3590,13 @@
         <v>105</v>
       </c>
       <c r="AO12" s="1">
-        <v>46311.032022500003</v>
+        <v>46313.360796678244</v>
       </c>
       <c r="AP12" t="s">
         <v>74</v>
       </c>
       <c r="AQ12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AR12" t="s">
         <v>65</v>
@@ -3452,7 +3611,7 @@
         <v>77</v>
       </c>
       <c r="AV12" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:48" x14ac:dyDescent="0.25">
@@ -3460,34 +3619,34 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C13" s="2">
         <v>46296.366125613429</v>
       </c>
       <c r="D13" t="s">
+        <v>138</v>
+      </c>
+      <c r="F13" t="s">
         <v>139</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
+        <v>111</v>
+      </c>
+      <c r="H13" t="s">
+        <v>112</v>
+      </c>
+      <c r="I13" t="s">
+        <v>113</v>
+      </c>
+      <c r="J13" t="s">
         <v>140</v>
       </c>
-      <c r="G13" t="s">
-        <v>110</v>
-      </c>
-      <c r="H13" t="s">
-        <v>111</v>
-      </c>
-      <c r="I13" t="s">
-        <v>112</v>
-      </c>
-      <c r="J13" t="s">
-        <v>141</v>
-      </c>
       <c r="K13">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13">
         <v>4</v>
@@ -3505,10 +3664,10 @@
         <v>63</v>
       </c>
       <c r="R13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="T13" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="U13" t="s">
         <v>64</v>
@@ -3523,22 +3682,22 @@
         <v>66</v>
       </c>
       <c r="Z13" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AA13" t="s">
         <v>67</v>
       </c>
       <c r="AB13" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="AC13" t="s">
+        <v>142</v>
+      </c>
+      <c r="AD13" t="s">
         <v>143</v>
       </c>
-      <c r="AD13" t="s">
+      <c r="AE13" t="s">
         <v>144</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>145</v>
       </c>
       <c r="AF13" s="1">
         <v>46296.366125115739</v>
@@ -3559,7 +3718,7 @@
         <v>0</v>
       </c>
       <c r="AL13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AM13">
         <v>0</v>
@@ -3567,14 +3726,11 @@
       <c r="AN13" t="s">
         <v>105</v>
       </c>
-      <c r="AO13" s="1">
-        <v>46309.705413090276</v>
-      </c>
       <c r="AP13" t="s">
+        <v>146</v>
+      </c>
+      <c r="AQ13" t="s">
         <v>147</v>
-      </c>
-      <c r="AQ13" t="s">
-        <v>148</v>
       </c>
       <c r="AR13" t="s">
         <v>65</v>
@@ -3586,10 +3742,10 @@
         <v>76</v>
       </c>
       <c r="AU13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AV13" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:48" x14ac:dyDescent="0.25">
@@ -3597,28 +3753,28 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2">
         <v>46296.679013796296</v>
       </c>
       <c r="D14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E14" t="s">
         <v>149</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>150</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>151</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>152</v>
       </c>
-      <c r="H14" t="s">
-        <v>153</v>
-      </c>
       <c r="I14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J14" t="s">
         <v>59</v>
@@ -3645,7 +3801,7 @@
         <v>63</v>
       </c>
       <c r="T14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="U14" t="s">
         <v>64</v>
@@ -3675,7 +3831,7 @@
         <v>69</v>
       </c>
       <c r="AE14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF14" s="1">
         <v>46289.379973622687</v>
@@ -3696,22 +3852,22 @@
         <v>0</v>
       </c>
       <c r="AL14" t="s">
+        <v>153</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="s">
         <v>154</v>
       </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="s">
-        <v>155</v>
-      </c>
       <c r="AO14" s="1">
-        <v>46307.074902766202</v>
+        <v>46313.352074074071</v>
       </c>
       <c r="AP14" t="s">
         <v>74</v>
       </c>
       <c r="AQ14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AR14" t="s">
         <v>65</v>
@@ -3734,28 +3890,28 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C15" s="2">
         <v>46297.341610752315</v>
       </c>
       <c r="D15" t="s">
+        <v>157</v>
+      </c>
+      <c r="F15" t="s">
         <v>158</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>159</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>160</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
+        <v>84</v>
+      </c>
+      <c r="J15" t="s">
         <v>161</v>
-      </c>
-      <c r="I15" t="s">
-        <v>85</v>
-      </c>
-      <c r="J15" t="s">
-        <v>162</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -3779,13 +3935,13 @@
         <v>63</v>
       </c>
       <c r="R15" t="s">
+        <v>162</v>
+      </c>
+      <c r="T15" t="s">
+        <v>159</v>
+      </c>
+      <c r="U15" t="s">
         <v>163</v>
-      </c>
-      <c r="T15" t="s">
-        <v>160</v>
-      </c>
-      <c r="U15" t="s">
-        <v>164</v>
       </c>
       <c r="V15">
         <v>1</v>
@@ -3803,16 +3959,16 @@
         <v>67</v>
       </c>
       <c r="AB15" t="s">
+        <v>164</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="s">
         <v>165</v>
       </c>
-      <c r="AC15">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="s">
+      <c r="AE15" t="s">
         <v>166</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>167</v>
       </c>
       <c r="AF15" s="1">
         <v>46297.341610208336</v>
@@ -3833,7 +3989,7 @@
         <v>0</v>
       </c>
       <c r="AL15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AM15">
         <v>0</v>
@@ -3848,7 +4004,7 @@
         <v>106</v>
       </c>
       <c r="AQ15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AR15" t="s">
         <v>65</v>
@@ -3871,28 +4027,28 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C16" s="2">
         <v>46297.979948715278</v>
       </c>
       <c r="D16" t="s">
+        <v>169</v>
+      </c>
+      <c r="F16" t="s">
         <v>170</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>171</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>172</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
+        <v>124</v>
+      </c>
+      <c r="J16" t="s">
         <v>173</v>
-      </c>
-      <c r="I16" t="s">
-        <v>85</v>
-      </c>
-      <c r="J16" t="s">
-        <v>174</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -3910,16 +4066,16 @@
         <v>61</v>
       </c>
       <c r="P16" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q16" t="s">
         <v>87</v>
       </c>
-      <c r="Q16" t="s">
-        <v>88</v>
-      </c>
       <c r="T16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="U16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="V16">
         <v>1</v>
@@ -3937,16 +4093,16 @@
         <v>67</v>
       </c>
       <c r="AB16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AC16">
         <v>0</v>
       </c>
       <c r="AD16" t="s">
-        <v>69</v>
+        <v>174</v>
       </c>
       <c r="AE16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AF16" s="1">
         <v>46297.979948715278</v>
@@ -3958,7 +4114,7 @@
         <v>0</v>
       </c>
       <c r="AI16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AJ16">
         <v>0</v>
@@ -4002,7 +4158,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C17" s="2">
         <v>46299.483265034723</v>
@@ -4020,10 +4176,10 @@
         <v>181</v>
       </c>
       <c r="H17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J17" t="s">
         <v>59</v>
@@ -4068,13 +4224,13 @@
         <v>66</v>
       </c>
       <c r="Z17" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AA17" t="s">
         <v>67</v>
       </c>
       <c r="AB17" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -4083,7 +4239,7 @@
         <v>69</v>
       </c>
       <c r="AE17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AF17" s="1">
         <v>46298.27023321759</v>
@@ -4128,7 +4284,7 @@
         <v>76</v>
       </c>
       <c r="AU17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AV17" t="s">
         <v>65</v>
@@ -4139,7 +4295,7 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C18" s="2">
         <v>46300.424044398147</v>
@@ -4157,10 +4313,10 @@
         <v>188</v>
       </c>
       <c r="I18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -4187,7 +4343,7 @@
         <v>189</v>
       </c>
       <c r="T18" t="s">
-        <v>187</v>
+        <v>151</v>
       </c>
       <c r="U18" t="s">
         <v>64</v>
@@ -4214,10 +4370,10 @@
         <v>0</v>
       </c>
       <c r="AD18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AE18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF18" s="1">
         <v>46300.424043900464</v>
@@ -4247,7 +4403,7 @@
         <v>105</v>
       </c>
       <c r="AO18" s="1">
-        <v>46308.672449560188</v>
+        <v>46313.352074074071</v>
       </c>
       <c r="AP18" t="s">
         <v>74</v>
@@ -4276,7 +4432,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C19" s="2">
         <v>46301.524036666669</v>
@@ -4339,19 +4495,19 @@
         <v>66</v>
       </c>
       <c r="Z19" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AA19" t="s">
         <v>67</v>
       </c>
       <c r="AB19" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="s">
         <v>116</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>117</v>
       </c>
       <c r="AE19" t="s">
         <v>200</v>
@@ -4410,7 +4566,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C20" s="2">
         <v>46301.888473657411</v>
@@ -4425,10 +4581,10 @@
         <v>181</v>
       </c>
       <c r="H20" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J20" t="s">
         <v>205</v>
@@ -4485,10 +4641,10 @@
         <v>0</v>
       </c>
       <c r="AD20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AE20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF20" s="1">
         <v>46301.888473043982</v>
@@ -4518,7 +4674,7 @@
         <v>105</v>
       </c>
       <c r="AO20" s="1">
-        <v>46307.074997673612</v>
+        <v>46313.35221070602</v>
       </c>
       <c r="AP20" t="s">
         <v>74</v>
@@ -4547,7 +4703,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C21" s="2">
         <v>46302.362088240741</v>
@@ -4565,10 +4721,10 @@
         <v>195</v>
       </c>
       <c r="I21" t="s">
-        <v>196</v>
+        <v>58</v>
       </c>
       <c r="J21" t="s">
-        <v>100</v>
+        <v>211</v>
       </c>
       <c r="K21">
         <v>11</v>
@@ -4610,22 +4766,22 @@
         <v>66</v>
       </c>
       <c r="Z21" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AA21" t="s">
         <v>67</v>
       </c>
       <c r="AB21" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="AC21">
         <v>0</v>
       </c>
       <c r="AD21" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="AE21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AF21" s="1">
         <v>46302.362087696762</v>
@@ -4646,7 +4802,7 @@
         <v>0</v>
       </c>
       <c r="AL21" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AM21">
         <v>0</v>
@@ -4658,7 +4814,7 @@
         <v>106</v>
       </c>
       <c r="AQ21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AR21" t="s">
         <v>65</v>
@@ -4681,28 +4837,28 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C22" s="2">
         <v>46302.470203912038</v>
       </c>
       <c r="D22" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F22" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G22" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H22" t="s">
+        <v>83</v>
+      </c>
+      <c r="I22" t="s">
         <v>84</v>
       </c>
-      <c r="I22" t="s">
-        <v>85</v>
-      </c>
       <c r="J22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -4720,16 +4876,16 @@
         <v>61</v>
       </c>
       <c r="P22" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q22" t="s">
         <v>87</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>88</v>
       </c>
       <c r="R22">
         <v>65612895</v>
       </c>
       <c r="T22" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="U22" t="s">
         <v>64</v>
@@ -4756,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AD22" t="s">
-        <v>217</v>
+        <v>174</v>
       </c>
       <c r="AE22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF22" s="1">
         <v>46302.470066608796</v>
@@ -4807,7 +4963,7 @@
         <v>76</v>
       </c>
       <c r="AU22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AV22" t="s">
         <v>65</v>
@@ -4818,7 +4974,7 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C23" s="2">
         <v>46302.813058368054</v>
@@ -4830,10 +4986,10 @@
         <v>221</v>
       </c>
       <c r="G23" t="s">
+        <v>159</v>
+      </c>
+      <c r="H23" t="s">
         <v>160</v>
-      </c>
-      <c r="H23" t="s">
-        <v>161</v>
       </c>
       <c r="I23" t="s">
         <v>196</v>
@@ -4866,7 +5022,7 @@
         <v>221</v>
       </c>
       <c r="T23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="U23" t="s">
         <v>64</v>
@@ -4881,22 +5037,22 @@
         <v>66</v>
       </c>
       <c r="Z23" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AA23" t="s">
         <v>67</v>
       </c>
       <c r="AB23" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="s">
         <v>116</v>
       </c>
-      <c r="AC23">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="s">
+      <c r="AE23" t="s">
         <v>117</v>
-      </c>
-      <c r="AE23" t="s">
-        <v>118</v>
       </c>
       <c r="AF23" s="1">
         <v>46302.813057141204</v>
@@ -4941,10 +5097,10 @@
         <v>76</v>
       </c>
       <c r="AU23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AV23" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:48" x14ac:dyDescent="0.25">
@@ -4952,7 +5108,7 @@
         <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C24" s="2">
         <v>46302.834448912035</v>
@@ -4973,13 +5129,13 @@
         <v>229</v>
       </c>
       <c r="I24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J24" t="s">
         <v>59</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -5021,7 +5177,7 @@
         <v>67</v>
       </c>
       <c r="AB24" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -5030,7 +5186,7 @@
         <v>69</v>
       </c>
       <c r="AE24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF24" s="1">
         <v>46300.903073344911</v>
@@ -5059,9 +5215,6 @@
       <c r="AN24" t="s">
         <v>231</v>
       </c>
-      <c r="AO24" s="1">
-        <v>46302.835580543979</v>
-      </c>
       <c r="AP24" t="s">
         <v>74</v>
       </c>
@@ -5081,7 +5234,7 @@
         <v>77</v>
       </c>
       <c r="AV24" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:48" x14ac:dyDescent="0.25">
@@ -5089,7 +5242,7 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C25" s="2">
         <v>46302.938876782406</v>
@@ -5104,10 +5257,10 @@
         <v>181</v>
       </c>
       <c r="H25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J25" t="s">
         <v>59</v>
@@ -5167,7 +5320,7 @@
         <v>69</v>
       </c>
       <c r="AE25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF25" s="1">
         <v>46302.379120381942</v>
@@ -5197,7 +5350,7 @@
         <v>237</v>
       </c>
       <c r="AO25" s="1">
-        <v>46307.074997673612</v>
+        <v>46313.35221070602</v>
       </c>
       <c r="AP25" t="s">
         <v>74</v>
@@ -5215,7 +5368,7 @@
         <v>76</v>
       </c>
       <c r="AU25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AV25" t="s">
         <v>65</v>
@@ -5226,7 +5379,7 @@
         <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C26" s="2">
         <v>46303.452258657409</v>
@@ -5244,7 +5397,7 @@
         <v>242</v>
       </c>
       <c r="I26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J26" t="s">
         <v>243</v>
@@ -5265,10 +5418,10 @@
         <v>61</v>
       </c>
       <c r="P26" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q26" t="s">
         <v>87</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>88</v>
       </c>
       <c r="R26" t="s">
         <v>240</v>
@@ -5289,22 +5442,22 @@
         <v>66</v>
       </c>
       <c r="Z26" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AA26" t="s">
         <v>67</v>
       </c>
       <c r="AB26" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="AC26">
         <v>0</v>
       </c>
       <c r="AD26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AE26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AF26" s="1">
         <v>46303.452257789351</v>
@@ -5360,10 +5513,10 @@
         <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C27" s="2">
-        <v>46303.507397453701</v>
+        <v>46303.582614988423</v>
       </c>
       <c r="D27" t="s">
         <v>246</v>
@@ -5375,25 +5528,25 @@
         <v>248</v>
       </c>
       <c r="G27" t="s">
-        <v>160</v>
+        <v>249</v>
       </c>
       <c r="H27" t="s">
-        <v>161</v>
+        <v>250</v>
       </c>
       <c r="I27" t="s">
-        <v>125</v>
+        <v>251</v>
       </c>
       <c r="J27" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="K27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N27" t="s">
         <v>60</v>
@@ -5402,16 +5555,13 @@
         <v>61</v>
       </c>
       <c r="P27" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="Q27" t="s">
-        <v>63</v>
-      </c>
-      <c r="R27" t="s">
-        <v>248</v>
+        <v>87</v>
       </c>
       <c r="T27" t="s">
-        <v>160</v>
+        <v>249</v>
       </c>
       <c r="U27" t="s">
         <v>64</v>
@@ -5432,22 +5582,22 @@
         <v>67</v>
       </c>
       <c r="AB27" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="AC27">
         <v>0</v>
       </c>
       <c r="AD27" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AE27" t="s">
-        <v>251</v>
+        <v>117</v>
       </c>
       <c r="AF27" s="1">
-        <v>46302.777953750003</v>
+        <v>46303.079102731484</v>
       </c>
       <c r="AG27">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AH27">
         <v>0</v>
@@ -5456,25 +5606,28 @@
         <v>71</v>
       </c>
       <c r="AJ27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK27">
         <v>0</v>
       </c>
       <c r="AL27" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AM27">
         <v>0</v>
       </c>
       <c r="AN27" t="s">
-        <v>253</v>
+        <v>255</v>
+      </c>
+      <c r="AO27" s="1">
+        <v>46305.528276307872</v>
       </c>
       <c r="AP27" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="AQ27" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AR27" t="s">
         <v>65</v>
@@ -5497,31 +5650,28 @@
         <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C28" s="2">
-        <v>46303.582614988423</v>
+        <v>46303.620899606482</v>
       </c>
       <c r="D28" t="s">
-        <v>255</v>
-      </c>
-      <c r="E28" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F28" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G28" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H28" t="s">
-        <v>259</v>
+        <v>152</v>
       </c>
       <c r="I28" t="s">
-        <v>260</v>
+        <v>84</v>
       </c>
       <c r="J28" t="s">
-        <v>261</v>
+        <v>134</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -5530,7 +5680,7 @@
         <v>0</v>
       </c>
       <c r="M28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N28" t="s">
         <v>60</v>
@@ -5539,13 +5689,16 @@
         <v>61</v>
       </c>
       <c r="P28" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="Q28" t="s">
-        <v>88</v>
+        <v>63</v>
+      </c>
+      <c r="R28" t="s">
+        <v>260</v>
       </c>
       <c r="T28" t="s">
-        <v>258</v>
+        <v>111</v>
       </c>
       <c r="U28" t="s">
         <v>64</v>
@@ -5559,6 +5712,9 @@
       <c r="X28" t="s">
         <v>66</v>
       </c>
+      <c r="Y28" t="s">
+        <v>261</v>
+      </c>
       <c r="Z28" t="s">
         <v>65</v>
       </c>
@@ -5572,16 +5728,16 @@
         <v>0</v>
       </c>
       <c r="AD28" t="s">
-        <v>262</v>
+        <v>165</v>
       </c>
       <c r="AE28" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="AF28" s="1">
-        <v>46303.079102731484</v>
+        <v>46303.618267685182</v>
       </c>
       <c r="AG28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH28">
         <v>0</v>
@@ -5596,22 +5752,22 @@
         <v>0</v>
       </c>
       <c r="AL28" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AM28">
         <v>0</v>
       </c>
       <c r="AN28" t="s">
-        <v>253</v>
+        <v>105</v>
       </c>
       <c r="AO28" s="1">
-        <v>46305.528276307872</v>
+        <v>46313.353976712962</v>
       </c>
       <c r="AP28" t="s">
         <v>74</v>
       </c>
       <c r="AQ28" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AR28" t="s">
         <v>65</v>
@@ -5634,37 +5790,37 @@
         <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C29" s="2">
-        <v>46303.620899606482</v>
+        <v>46303.625136435185</v>
       </c>
       <c r="D29" t="s">
+        <v>264</v>
+      </c>
+      <c r="F29" t="s">
         <v>265</v>
       </c>
-      <c r="F29" t="s">
-        <v>266</v>
-      </c>
       <c r="G29" t="s">
-        <v>267</v>
+        <v>96</v>
       </c>
       <c r="H29" t="s">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="I29" t="s">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="J29" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N29" t="s">
         <v>60</v>
@@ -5679,10 +5835,10 @@
         <v>63</v>
       </c>
       <c r="R29" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="T29" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="U29" t="s">
         <v>64</v>
@@ -5696,32 +5852,29 @@
       <c r="X29" t="s">
         <v>66</v>
       </c>
-      <c r="Y29" t="s">
-        <v>269</v>
-      </c>
       <c r="Z29" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="AA29" t="s">
         <v>67</v>
       </c>
       <c r="AB29" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="AC29">
         <v>0</v>
       </c>
       <c r="AD29" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AE29" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="AF29" s="1">
-        <v>46303.618267685182</v>
+        <v>46303.625135486109</v>
       </c>
       <c r="AG29">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AH29">
         <v>0</v>
@@ -5730,13 +5883,13 @@
         <v>71</v>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK29">
         <v>0</v>
       </c>
       <c r="AL29" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AM29">
         <v>0</v>
@@ -5744,14 +5897,11 @@
       <c r="AN29" t="s">
         <v>105</v>
       </c>
-      <c r="AO29" s="1">
-        <v>46311.501728425923</v>
-      </c>
       <c r="AP29" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AQ29" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="AR29" t="s">
         <v>65</v>
@@ -5766,7 +5916,7 @@
         <v>77</v>
       </c>
       <c r="AV29" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:48" x14ac:dyDescent="0.25">
@@ -5774,37 +5924,40 @@
         <v>24</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="C30" s="2">
-        <v>46303.625136435185</v>
+        <v>46303.834263124998</v>
       </c>
       <c r="D30" t="s">
+        <v>269</v>
+      </c>
+      <c r="E30" t="s">
+        <v>270</v>
+      </c>
+      <c r="F30" t="s">
+        <v>271</v>
+      </c>
+      <c r="G30" t="s">
         <v>272</v>
       </c>
-      <c r="F30" t="s">
+      <c r="H30" t="s">
         <v>273</v>
       </c>
-      <c r="G30" t="s">
-        <v>97</v>
-      </c>
-      <c r="H30" t="s">
-        <v>98</v>
-      </c>
       <c r="I30" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="J30" t="s">
-        <v>100</v>
+        <v>274</v>
       </c>
       <c r="K30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N30" t="s">
         <v>60</v>
@@ -5813,16 +5966,13 @@
         <v>61</v>
       </c>
       <c r="P30" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="Q30" t="s">
-        <v>63</v>
-      </c>
-      <c r="R30" t="s">
-        <v>274</v>
+        <v>87</v>
       </c>
       <c r="T30" t="s">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="U30" t="s">
         <v>64</v>
@@ -5837,28 +5987,28 @@
         <v>66</v>
       </c>
       <c r="Z30" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="AA30" t="s">
         <v>67</v>
       </c>
       <c r="AB30" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="AC30">
         <v>0</v>
       </c>
       <c r="AD30" t="s">
-        <v>166</v>
+        <v>253</v>
       </c>
       <c r="AE30" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="AF30" s="1">
-        <v>46303.625135486109</v>
+        <v>46302.85321872685</v>
       </c>
       <c r="AG30">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AH30">
         <v>0</v>
@@ -5867,7 +6017,7 @@
         <v>71</v>
       </c>
       <c r="AJ30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK30">
         <v>0</v>
@@ -5879,10 +6029,13 @@
         <v>0</v>
       </c>
       <c r="AN30" t="s">
-        <v>105</v>
+        <v>183</v>
+      </c>
+      <c r="AO30" s="1">
+        <v>46309.96033440972</v>
       </c>
       <c r="AP30" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="AQ30" t="s">
         <v>276</v>
@@ -5897,7 +6050,7 @@
         <v>76</v>
       </c>
       <c r="AU30" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AV30" t="s">
         <v>65</v>
@@ -5908,31 +6061,28 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C31" s="2">
-        <v>46303.834263124998</v>
+        <v>46304.417614247686</v>
       </c>
       <c r="D31" t="s">
         <v>277</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>278</v>
       </c>
-      <c r="F31" t="s">
-        <v>279</v>
-      </c>
       <c r="G31" t="s">
-        <v>280</v>
+        <v>216</v>
       </c>
       <c r="H31" t="s">
-        <v>281</v>
+        <v>83</v>
       </c>
       <c r="I31" t="s">
-        <v>125</v>
+        <v>84</v>
       </c>
       <c r="J31" t="s">
-        <v>282</v>
+        <v>217</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -5950,13 +6100,19 @@
         <v>61</v>
       </c>
       <c r="P31" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q31" t="s">
         <v>87</v>
       </c>
-      <c r="Q31" t="s">
-        <v>88</v>
+      <c r="R31" t="s">
+        <v>279</v>
+      </c>
+      <c r="S31" t="s">
+        <v>231</v>
       </c>
       <c r="T31" t="s">
-        <v>280</v>
+        <v>216</v>
       </c>
       <c r="U31" t="s">
         <v>64</v>
@@ -5983,13 +6139,13 @@
         <v>0</v>
       </c>
       <c r="AD31" t="s">
-        <v>262</v>
+        <v>174</v>
       </c>
       <c r="AE31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF31" s="1">
-        <v>46302.85321872685</v>
+        <v>46304.417613530095</v>
       </c>
       <c r="AG31">
         <v>1</v>
@@ -6007,22 +6163,22 @@
         <v>0</v>
       </c>
       <c r="AL31" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="AM31">
         <v>0</v>
       </c>
       <c r="AN31" t="s">
-        <v>183</v>
+        <v>105</v>
       </c>
       <c r="AO31" s="1">
-        <v>46309.96033440972</v>
+        <v>46310.136818657411</v>
       </c>
       <c r="AP31" t="s">
         <v>74</v>
       </c>
       <c r="AQ31" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AR31" t="s">
         <v>65</v>
@@ -6034,7 +6190,7 @@
         <v>76</v>
       </c>
       <c r="AU31" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AV31" t="s">
         <v>65</v>
@@ -6045,37 +6201,37 @@
         <v>26</v>
       </c>
       <c r="B32" t="s">
-        <v>131</v>
+        <v>282</v>
       </c>
       <c r="C32" s="2">
-        <v>46304.417614247686</v>
+        <v>46304.448332233798</v>
       </c>
       <c r="D32" t="s">
+        <v>283</v>
+      </c>
+      <c r="F32" t="s">
+        <v>284</v>
+      </c>
+      <c r="G32" t="s">
+        <v>228</v>
+      </c>
+      <c r="H32" t="s">
+        <v>229</v>
+      </c>
+      <c r="I32" t="s">
+        <v>133</v>
+      </c>
+      <c r="J32" t="s">
         <v>285</v>
       </c>
-      <c r="F32" t="s">
-        <v>286</v>
-      </c>
-      <c r="G32" t="s">
-        <v>215</v>
-      </c>
-      <c r="H32" t="s">
-        <v>84</v>
-      </c>
-      <c r="I32" t="s">
-        <v>85</v>
-      </c>
-      <c r="J32" t="s">
-        <v>216</v>
-      </c>
       <c r="K32">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N32" t="s">
         <v>60</v>
@@ -6084,19 +6240,16 @@
         <v>61</v>
       </c>
       <c r="P32" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="Q32" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="R32" t="s">
-        <v>287</v>
-      </c>
-      <c r="S32" t="s">
-        <v>231</v>
+        <v>286</v>
       </c>
       <c r="T32" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="U32" t="s">
         <v>64</v>
@@ -6117,37 +6270,37 @@
         <v>67</v>
       </c>
       <c r="AB32" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="AC32">
         <v>0</v>
       </c>
       <c r="AD32" t="s">
-        <v>217</v>
+        <v>116</v>
       </c>
       <c r="AE32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF32" s="1">
-        <v>46304.417613530095</v>
+        <v>46304.447403692131</v>
       </c>
       <c r="AG32">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI32" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK32">
         <v>0</v>
       </c>
       <c r="AL32" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AM32">
         <v>0</v>
@@ -6155,14 +6308,11 @@
       <c r="AN32" t="s">
         <v>105</v>
       </c>
-      <c r="AO32" s="1">
-        <v>46310.136818657411</v>
-      </c>
       <c r="AP32" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AQ32" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AR32" t="s">
         <v>65</v>
@@ -6174,10 +6324,10 @@
         <v>76</v>
       </c>
       <c r="AU32" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AV32" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:48" x14ac:dyDescent="0.25">
@@ -6185,37 +6335,37 @@
         <v>27</v>
       </c>
       <c r="B33" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" s="2">
+        <v>46304.454942291668</v>
+      </c>
+      <c r="D33" t="s">
+        <v>289</v>
+      </c>
+      <c r="F33" t="s">
         <v>290</v>
       </c>
-      <c r="C33" s="2">
-        <v>46304.448332233798</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="G33" t="s">
         <v>291</v>
       </c>
-      <c r="F33" t="s">
+      <c r="H33" t="s">
         <v>292</v>
       </c>
-      <c r="G33" t="s">
-        <v>228</v>
-      </c>
-      <c r="H33" t="s">
-        <v>229</v>
-      </c>
       <c r="I33" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="J33" t="s">
         <v>293</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N33" t="s">
         <v>60</v>
@@ -6233,7 +6383,7 @@
         <v>294</v>
       </c>
       <c r="T33" t="s">
-        <v>228</v>
+        <v>291</v>
       </c>
       <c r="U33" t="s">
         <v>64</v>
@@ -6248,34 +6398,34 @@
         <v>66</v>
       </c>
       <c r="Z33" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="AA33" t="s">
         <v>67</v>
       </c>
       <c r="AB33" t="s">
-        <v>165</v>
+        <v>101</v>
       </c>
       <c r="AC33">
         <v>0</v>
       </c>
       <c r="AD33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AE33" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="AF33" s="1">
-        <v>46304.447403692131</v>
+        <v>46304.454941678239</v>
       </c>
       <c r="AG33">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AH33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="AJ33">
         <v>1</v>
@@ -6308,10 +6458,10 @@
         <v>76</v>
       </c>
       <c r="AU33" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AV33" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:48" x14ac:dyDescent="0.25">
@@ -6319,37 +6469,40 @@
         <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="C34" s="2">
-        <v>46304.454942291668</v>
+        <v>46304.693424247685</v>
       </c>
       <c r="D34" t="s">
         <v>297</v>
       </c>
+      <c r="E34" t="s">
+        <v>298</v>
+      </c>
       <c r="F34" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G34" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H34" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I34" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="J34" t="s">
-        <v>301</v>
+        <v>85</v>
       </c>
       <c r="K34">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N34" t="s">
         <v>60</v>
@@ -6358,16 +6511,13 @@
         <v>61</v>
       </c>
       <c r="P34" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="Q34" t="s">
-        <v>63</v>
-      </c>
-      <c r="R34" t="s">
-        <v>302</v>
+        <v>87</v>
       </c>
       <c r="T34" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="U34" t="s">
         <v>64</v>
@@ -6382,28 +6532,28 @@
         <v>66</v>
       </c>
       <c r="Z34" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="AA34" t="s">
         <v>67</v>
       </c>
       <c r="AB34" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="AC34">
         <v>0</v>
       </c>
       <c r="AD34" t="s">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="AE34" t="s">
-        <v>128</v>
+        <v>200</v>
       </c>
       <c r="AF34" s="1">
-        <v>46304.454941678239</v>
+        <v>46303.667550081016</v>
       </c>
       <c r="AG34">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AH34">
         <v>0</v>
@@ -6412,25 +6562,28 @@
         <v>71</v>
       </c>
       <c r="AJ34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK34">
         <v>0</v>
       </c>
       <c r="AL34" t="s">
+        <v>302</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>154</v>
+      </c>
+      <c r="AO34" s="1">
+        <v>46310.105611516206</v>
+      </c>
+      <c r="AP34" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ34" t="s">
         <v>303</v>
-      </c>
-      <c r="AM34">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="s">
-        <v>105</v>
-      </c>
-      <c r="AP34" t="s">
-        <v>106</v>
-      </c>
-      <c r="AQ34" t="s">
-        <v>304</v>
       </c>
       <c r="AR34" t="s">
         <v>65</v>
@@ -6453,34 +6606,31 @@
         <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="C35" s="2">
-        <v>46304.693424247685</v>
+        <v>46304.920313912036</v>
       </c>
       <c r="D35" t="s">
+        <v>304</v>
+      </c>
+      <c r="F35" t="s">
         <v>305</v>
       </c>
-      <c r="E35" t="s">
-        <v>306</v>
-      </c>
-      <c r="F35" t="s">
-        <v>307</v>
-      </c>
       <c r="G35" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="H35" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="I35" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="J35" t="s">
-        <v>86</v>
+        <v>293</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -6495,13 +6645,16 @@
         <v>61</v>
       </c>
       <c r="P35" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="Q35" t="s">
-        <v>88</v>
+        <v>63</v>
+      </c>
+      <c r="R35" t="s">
+        <v>306</v>
       </c>
       <c r="T35" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="U35" t="s">
         <v>64</v>
@@ -6516,28 +6669,28 @@
         <v>66</v>
       </c>
       <c r="Z35" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="AA35" t="s">
         <v>67</v>
       </c>
       <c r="AB35" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="AC35">
         <v>0</v>
       </c>
       <c r="AD35" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="AE35" t="s">
-        <v>200</v>
+        <v>117</v>
       </c>
       <c r="AF35" s="1">
-        <v>46303.667550081016</v>
+        <v>46304.920313368057</v>
       </c>
       <c r="AG35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH35">
         <v>0</v>
@@ -6546,28 +6699,25 @@
         <v>71</v>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK35">
         <v>0</v>
       </c>
       <c r="AL35" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AM35">
         <v>0</v>
       </c>
       <c r="AN35" t="s">
-        <v>155</v>
-      </c>
-      <c r="AO35" s="1">
-        <v>46310.105611516206</v>
+        <v>105</v>
       </c>
       <c r="AP35" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AQ35" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AR35" t="s">
         <v>65</v>
@@ -6579,10 +6729,10 @@
         <v>76</v>
       </c>
       <c r="AU35" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AV35" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:48" x14ac:dyDescent="0.25">
@@ -6590,37 +6740,37 @@
         <v>30</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C36" s="2">
-        <v>46304.920313912036</v>
+        <v>46305.443223935188</v>
       </c>
       <c r="D36" t="s">
+        <v>309</v>
+      </c>
+      <c r="F36" t="s">
+        <v>310</v>
+      </c>
+      <c r="G36" t="s">
+        <v>311</v>
+      </c>
+      <c r="H36" t="s">
         <v>312</v>
       </c>
-      <c r="F36" t="s">
-        <v>313</v>
-      </c>
-      <c r="G36" t="s">
-        <v>299</v>
-      </c>
-      <c r="H36" t="s">
-        <v>300</v>
-      </c>
       <c r="I36" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J36" t="s">
-        <v>301</v>
+        <v>197</v>
       </c>
       <c r="K36">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N36" t="s">
         <v>60</v>
@@ -6634,11 +6784,8 @@
       <c r="Q36" t="s">
         <v>63</v>
       </c>
-      <c r="R36" t="s">
-        <v>314</v>
-      </c>
       <c r="T36" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="U36" t="s">
         <v>64</v>
@@ -6653,28 +6800,28 @@
         <v>66</v>
       </c>
       <c r="Z36" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AA36" t="s">
         <v>67</v>
       </c>
       <c r="AB36" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="s">
         <v>116</v>
       </c>
-      <c r="AC36">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="s">
+      <c r="AE36" t="s">
         <v>117</v>
       </c>
-      <c r="AE36" t="s">
-        <v>118</v>
-      </c>
       <c r="AF36" s="1">
-        <v>46304.920313368057</v>
+        <v>46305.443222581016</v>
       </c>
       <c r="AG36">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AH36">
         <v>0</v>
@@ -6689,7 +6836,7 @@
         <v>0</v>
       </c>
       <c r="AL36" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AM36">
         <v>0</v>
@@ -6701,7 +6848,7 @@
         <v>106</v>
       </c>
       <c r="AQ36" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AR36" t="s">
         <v>65</v>
@@ -6713,10 +6860,10 @@
         <v>76</v>
       </c>
       <c r="AU36" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AV36" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:48" x14ac:dyDescent="0.25">
@@ -6724,37 +6871,40 @@
         <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C37" s="2">
-        <v>46305.443223935188</v>
+        <v>46305.656685613423</v>
       </c>
       <c r="D37" t="s">
+        <v>315</v>
+      </c>
+      <c r="E37" t="s">
+        <v>316</v>
+      </c>
+      <c r="F37" t="s">
         <v>317</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>318</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>319</v>
       </c>
-      <c r="H37" t="s">
-        <v>320</v>
-      </c>
       <c r="I37" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="J37" t="s">
-        <v>197</v>
+        <v>59</v>
       </c>
       <c r="K37">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N37" t="s">
         <v>60</v>
@@ -6766,10 +6916,13 @@
         <v>62</v>
       </c>
       <c r="Q37" t="s">
-        <v>63</v>
+        <v>87</v>
+      </c>
+      <c r="R37" t="s">
+        <v>317</v>
       </c>
       <c r="T37" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="U37" t="s">
         <v>64</v>
@@ -6784,34 +6937,34 @@
         <v>66</v>
       </c>
       <c r="Z37" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AA37" t="s">
         <v>67</v>
       </c>
       <c r="AB37" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="AC37">
         <v>0</v>
       </c>
       <c r="AD37" t="s">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="AE37" t="s">
-        <v>118</v>
+        <v>320</v>
       </c>
       <c r="AF37" s="1">
-        <v>46305.443222581016</v>
+        <v>46305.242012905095</v>
       </c>
       <c r="AG37">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AH37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI37" t="s">
-        <v>71</v>
+        <v>321</v>
       </c>
       <c r="AJ37">
         <v>1</v>
@@ -6820,19 +6973,19 @@
         <v>0</v>
       </c>
       <c r="AL37" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM37">
         <v>0</v>
       </c>
       <c r="AN37" t="s">
-        <v>105</v>
+        <v>323</v>
       </c>
       <c r="AP37" t="s">
         <v>106</v>
       </c>
       <c r="AQ37" t="s">
-        <v>322</v>
+        <v>107</v>
       </c>
       <c r="AR37" t="s">
         <v>65</v>
@@ -6844,7 +6997,7 @@
         <v>76</v>
       </c>
       <c r="AU37" t="s">
-        <v>77</v>
+        <v>324</v>
       </c>
       <c r="AV37" t="s">
         <v>65</v>
@@ -6855,40 +7008,37 @@
         <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C38" s="2">
-        <v>46305.656685613423</v>
+        <v>46305.89986020833</v>
       </c>
       <c r="D38" t="s">
-        <v>323</v>
-      </c>
-      <c r="E38" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F38" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G38" t="s">
-        <v>326</v>
+        <v>111</v>
       </c>
       <c r="H38" t="s">
+        <v>112</v>
+      </c>
+      <c r="I38" t="s">
+        <v>113</v>
+      </c>
+      <c r="J38" t="s">
         <v>327</v>
       </c>
-      <c r="I38" t="s">
-        <v>85</v>
-      </c>
-      <c r="J38" t="s">
-        <v>59</v>
-      </c>
       <c r="K38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N38" t="s">
         <v>60</v>
@@ -6900,13 +7050,13 @@
         <v>62</v>
       </c>
       <c r="Q38" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="R38" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="T38" t="s">
-        <v>326</v>
+        <v>111</v>
       </c>
       <c r="U38" t="s">
         <v>64</v>
@@ -6921,55 +7071,55 @@
         <v>66</v>
       </c>
       <c r="Z38" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AA38" t="s">
         <v>67</v>
       </c>
       <c r="AB38" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="s">
         <v>116</v>
       </c>
-      <c r="AC38">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="s">
-        <v>69</v>
-      </c>
       <c r="AE38" t="s">
-        <v>328</v>
+        <v>117</v>
       </c>
       <c r="AF38" s="1">
-        <v>46305.242012905095</v>
+        <v>46305.899859259262</v>
       </c>
       <c r="AG38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ38">
+        <v>1</v>
+      </c>
+      <c r="AK38">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="s">
         <v>329</v>
       </c>
-      <c r="AJ38">
-        <v>1</v>
-      </c>
-      <c r="AK38">
-        <v>0</v>
-      </c>
-      <c r="AL38" t="s">
-        <v>330</v>
-      </c>
       <c r="AM38">
         <v>0</v>
       </c>
       <c r="AN38" t="s">
-        <v>331</v>
+        <v>105</v>
       </c>
       <c r="AP38" t="s">
         <v>106</v>
       </c>
       <c r="AQ38" t="s">
-        <v>107</v>
+        <v>330</v>
       </c>
       <c r="AR38" t="s">
         <v>65</v>
@@ -6981,10 +7131,10 @@
         <v>76</v>
       </c>
       <c r="AU38" t="s">
-        <v>332</v>
+        <v>77</v>
       </c>
       <c r="AV38" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:48" x14ac:dyDescent="0.25">
@@ -6992,37 +7142,37 @@
         <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C39" s="2">
-        <v>46305.89986020833</v>
+        <v>46305.919607268515</v>
       </c>
       <c r="D39" t="s">
+        <v>331</v>
+      </c>
+      <c r="F39" t="s">
+        <v>332</v>
+      </c>
+      <c r="G39" t="s">
+        <v>318</v>
+      </c>
+      <c r="H39" t="s">
         <v>333</v>
       </c>
-      <c r="F39" t="s">
+      <c r="I39" t="s">
+        <v>113</v>
+      </c>
+      <c r="J39" t="s">
         <v>334</v>
       </c>
-      <c r="G39" t="s">
-        <v>110</v>
-      </c>
-      <c r="H39" t="s">
-        <v>111</v>
-      </c>
-      <c r="I39" t="s">
-        <v>112</v>
-      </c>
-      <c r="J39" t="s">
-        <v>335</v>
-      </c>
       <c r="K39">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L39">
         <v>0</v>
       </c>
       <c r="M39">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N39" t="s">
         <v>60</v>
@@ -7031,16 +7181,16 @@
         <v>61</v>
       </c>
       <c r="P39" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="Q39" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="R39" t="s">
+        <v>335</v>
+      </c>
+      <c r="T39" t="s">
         <v>336</v>
-      </c>
-      <c r="T39" t="s">
-        <v>114</v>
       </c>
       <c r="U39" t="s">
         <v>64</v>
@@ -7055,28 +7205,28 @@
         <v>66</v>
       </c>
       <c r="Z39" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AA39" t="s">
         <v>67</v>
       </c>
       <c r="AB39" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="AC39">
         <v>0</v>
       </c>
       <c r="AD39" t="s">
-        <v>117</v>
+        <v>337</v>
       </c>
       <c r="AE39" t="s">
-        <v>118</v>
+        <v>338</v>
       </c>
       <c r="AF39" s="1">
-        <v>46305.899859259262</v>
+        <v>46304.50348003472</v>
       </c>
       <c r="AG39">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AH39">
         <v>0</v>
@@ -7091,7 +7241,7 @@
         <v>0</v>
       </c>
       <c r="AL39" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AM39">
         <v>0</v>
@@ -7103,7 +7253,7 @@
         <v>106</v>
       </c>
       <c r="AQ39" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AR39" t="s">
         <v>65</v>
@@ -7126,37 +7276,40 @@
         <v>34</v>
       </c>
       <c r="B40" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="C40" s="2">
-        <v>46305.919607268515</v>
+        <v>46306.538759444447</v>
       </c>
       <c r="D40" t="s">
-        <v>339</v>
+        <v>341</v>
+      </c>
+      <c r="E40" t="s">
+        <v>342</v>
       </c>
       <c r="F40" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="G40" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="H40" t="s">
-        <v>341</v>
+        <v>273</v>
       </c>
       <c r="I40" t="s">
-        <v>112</v>
+        <v>251</v>
       </c>
       <c r="J40" t="s">
-        <v>342</v>
+        <v>274</v>
       </c>
       <c r="K40">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L40">
         <v>0</v>
       </c>
       <c r="M40">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N40" t="s">
         <v>60</v>
@@ -7165,13 +7318,10 @@
         <v>61</v>
       </c>
       <c r="P40" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q40" t="s">
         <v>87</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>88</v>
-      </c>
-      <c r="R40" t="s">
-        <v>343</v>
       </c>
       <c r="T40" t="s">
         <v>344</v>
@@ -7188,29 +7338,32 @@
       <c r="X40" t="s">
         <v>66</v>
       </c>
+      <c r="Y40" t="s">
+        <v>261</v>
+      </c>
       <c r="Z40" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="AA40" t="s">
         <v>67</v>
       </c>
       <c r="AB40" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="AC40">
         <v>0</v>
       </c>
       <c r="AD40" t="s">
-        <v>345</v>
+        <v>253</v>
       </c>
       <c r="AE40" t="s">
-        <v>251</v>
+        <v>200</v>
       </c>
       <c r="AF40" s="1">
-        <v>46304.50348003472</v>
+        <v>46304.418572407405</v>
       </c>
       <c r="AG40">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AH40">
         <v>0</v>
@@ -7219,22 +7372,25 @@
         <v>71</v>
       </c>
       <c r="AJ40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK40">
         <v>0</v>
       </c>
       <c r="AL40" t="s">
+        <v>345</v>
+      </c>
+      <c r="AM40">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="s">
         <v>346</v>
       </c>
-      <c r="AM40">
-        <v>0</v>
-      </c>
-      <c r="AN40" t="s">
-        <v>105</v>
+      <c r="AO40" s="1">
+        <v>46310.830416273151</v>
       </c>
       <c r="AP40" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="AQ40" t="s">
         <v>347</v>
@@ -7260,31 +7416,28 @@
         <v>35</v>
       </c>
       <c r="B41" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="C41" s="2">
-        <v>46306.538759444447</v>
+        <v>46306.692922222224</v>
       </c>
       <c r="D41" t="s">
         <v>348</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>349</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>350</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
+        <v>112</v>
+      </c>
+      <c r="I41" t="s">
         <v>351</v>
       </c>
-      <c r="H41" t="s">
-        <v>281</v>
-      </c>
-      <c r="I41" t="s">
-        <v>260</v>
-      </c>
       <c r="J41" t="s">
-        <v>282</v>
+        <v>59</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -7293,7 +7446,7 @@
         <v>0</v>
       </c>
       <c r="M41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N41" t="s">
         <v>60</v>
@@ -7302,16 +7455,16 @@
         <v>61</v>
       </c>
       <c r="P41" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="Q41" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="T41" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="U41" t="s">
-        <v>64</v>
+        <v>163</v>
       </c>
       <c r="V41">
         <v>1</v>
@@ -7322,9 +7475,6 @@
       <c r="X41" t="s">
         <v>66</v>
       </c>
-      <c r="Y41" t="s">
-        <v>269</v>
-      </c>
       <c r="Z41" t="s">
         <v>65</v>
       </c>
@@ -7332,28 +7482,28 @@
         <v>67</v>
       </c>
       <c r="AB41" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="AC41">
         <v>0</v>
       </c>
       <c r="AD41" t="s">
-        <v>262</v>
+        <v>69</v>
       </c>
       <c r="AE41" t="s">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="AF41" s="1">
-        <v>46304.418572407405</v>
+        <v>46306.692922222224</v>
       </c>
       <c r="AG41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH41">
         <v>0</v>
       </c>
       <c r="AI41" t="s">
-        <v>71</v>
+        <v>166</v>
       </c>
       <c r="AJ41">
         <v>0</v>
@@ -7362,19 +7512,16 @@
         <v>0</v>
       </c>
       <c r="AL41" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AM41">
         <v>0</v>
       </c>
       <c r="AN41" t="s">
-        <v>353</v>
-      </c>
-      <c r="AO41" s="1">
-        <v>46310.830416273151</v>
+        <v>346</v>
       </c>
       <c r="AP41" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AQ41" t="s">
         <v>354</v>
@@ -7400,10 +7547,10 @@
         <v>36</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C42" s="2">
-        <v>46306.692922222224</v>
+        <v>46307.312114722219</v>
       </c>
       <c r="D42" t="s">
         <v>355</v>
@@ -7412,25 +7559,25 @@
         <v>356</v>
       </c>
       <c r="G42" t="s">
+        <v>111</v>
+      </c>
+      <c r="H42" t="s">
+        <v>112</v>
+      </c>
+      <c r="I42" t="s">
+        <v>196</v>
+      </c>
+      <c r="J42" t="s">
         <v>357</v>
       </c>
-      <c r="H42" t="s">
-        <v>111</v>
-      </c>
-      <c r="I42" t="s">
-        <v>358</v>
-      </c>
-      <c r="J42" t="s">
-        <v>59</v>
-      </c>
       <c r="K42">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L42">
         <v>0</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N42" t="s">
         <v>60</v>
@@ -7445,10 +7592,10 @@
         <v>63</v>
       </c>
       <c r="T42" t="s">
-        <v>359</v>
+        <v>111</v>
       </c>
       <c r="U42" t="s">
-        <v>164</v>
+        <v>64</v>
       </c>
       <c r="V42">
         <v>1</v>
@@ -7460,55 +7607,55 @@
         <v>66</v>
       </c>
       <c r="Z42" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="AA42" t="s">
         <v>67</v>
       </c>
       <c r="AB42" t="s">
-        <v>165</v>
+        <v>101</v>
       </c>
       <c r="AC42">
         <v>0</v>
       </c>
       <c r="AD42" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="AE42" t="s">
-        <v>167</v>
+        <v>117</v>
       </c>
       <c r="AF42" s="1">
-        <v>46306.692922222224</v>
+        <v>46307.312114097222</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH42">
         <v>0</v>
       </c>
       <c r="AI42" t="s">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK42">
         <v>0</v>
       </c>
       <c r="AL42" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AM42">
         <v>0</v>
       </c>
       <c r="AN42" t="s">
-        <v>353</v>
+        <v>105</v>
       </c>
       <c r="AP42" t="s">
         <v>106</v>
       </c>
       <c r="AQ42" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AR42" t="s">
         <v>65</v>
@@ -7520,10 +7667,10 @@
         <v>76</v>
       </c>
       <c r="AU42" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AV42" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:48" x14ac:dyDescent="0.25">
@@ -7531,37 +7678,37 @@
         <v>37</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C43" s="2">
-        <v>46307.312114722219</v>
+        <v>46307.315618969908</v>
       </c>
       <c r="D43" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F43" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G43" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H43" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I43" t="s">
         <v>196</v>
       </c>
       <c r="J43" t="s">
-        <v>113</v>
+        <v>362</v>
       </c>
       <c r="K43">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L43">
         <v>0</v>
       </c>
       <c r="M43">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N43" t="s">
         <v>60</v>
@@ -7575,8 +7722,11 @@
       <c r="Q43" t="s">
         <v>63</v>
       </c>
+      <c r="R43" t="s">
+        <v>363</v>
+      </c>
       <c r="T43" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="U43" t="s">
         <v>64</v>
@@ -7591,28 +7741,28 @@
         <v>66</v>
       </c>
       <c r="Z43" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AA43" t="s">
         <v>67</v>
       </c>
       <c r="AB43" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="AC43">
         <v>0</v>
       </c>
       <c r="AD43" t="s">
+        <v>364</v>
+      </c>
+      <c r="AE43" t="s">
         <v>117</v>
       </c>
-      <c r="AE43" t="s">
-        <v>118</v>
-      </c>
       <c r="AF43" s="1">
-        <v>46307.312114097222</v>
+        <v>46307.315617800923</v>
       </c>
       <c r="AG43">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AH43">
         <v>0</v>
@@ -7627,7 +7777,7 @@
         <v>0</v>
       </c>
       <c r="AL43" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AM43">
         <v>0</v>
@@ -7639,7 +7789,7 @@
         <v>106</v>
       </c>
       <c r="AQ43" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AR43" t="s">
         <v>65</v>
@@ -7651,10 +7801,10 @@
         <v>76</v>
       </c>
       <c r="AU43" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AV43" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:48" x14ac:dyDescent="0.25">
@@ -7662,31 +7812,34 @@
         <v>38</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C44" s="2">
-        <v>46307.315618969908</v>
+        <v>46307.480043946758</v>
       </c>
       <c r="D44" t="s">
-        <v>366</v>
+        <v>367</v>
+      </c>
+      <c r="E44" t="s">
+        <v>368</v>
       </c>
       <c r="F44" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G44" t="s">
-        <v>110</v>
+        <v>272</v>
       </c>
       <c r="H44" t="s">
-        <v>111</v>
+        <v>273</v>
       </c>
       <c r="I44" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="J44" t="s">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="K44">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -7701,16 +7854,13 @@
         <v>61</v>
       </c>
       <c r="P44" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="Q44" t="s">
-        <v>63</v>
-      </c>
-      <c r="R44" t="s">
-        <v>368</v>
+        <v>87</v>
       </c>
       <c r="T44" t="s">
-        <v>114</v>
+        <v>272</v>
       </c>
       <c r="U44" t="s">
         <v>64</v>
@@ -7725,28 +7875,28 @@
         <v>66</v>
       </c>
       <c r="Z44" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="AA44" t="s">
         <v>67</v>
       </c>
       <c r="AB44" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="AC44">
         <v>0</v>
       </c>
       <c r="AD44" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="AE44" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="AF44" s="1">
-        <v>46307.315617800923</v>
+        <v>46306.394415243056</v>
       </c>
       <c r="AG44">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AH44">
         <v>0</v>
@@ -7755,25 +7905,28 @@
         <v>71</v>
       </c>
       <c r="AJ44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK44">
         <v>0</v>
       </c>
       <c r="AL44" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AM44">
         <v>0</v>
       </c>
       <c r="AN44" t="s">
-        <v>105</v>
+        <v>371</v>
+      </c>
+      <c r="AO44" s="1">
+        <v>46309.96033440972</v>
       </c>
       <c r="AP44" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="AQ44" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AR44" t="s">
         <v>65</v>
@@ -7796,40 +7949,37 @@
         <v>39</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C45" s="2">
-        <v>46307.480043946758</v>
+        <v>46307.845660590276</v>
       </c>
       <c r="D45" t="s">
-        <v>371</v>
-      </c>
-      <c r="E45" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F45" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G45" t="s">
-        <v>280</v>
+        <v>111</v>
       </c>
       <c r="H45" t="s">
-        <v>281</v>
+        <v>112</v>
       </c>
       <c r="I45" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="J45" t="s">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L45">
         <v>0</v>
       </c>
       <c r="M45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N45" t="s">
         <v>60</v>
@@ -7838,13 +7988,13 @@
         <v>61</v>
       </c>
       <c r="P45" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="Q45" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="T45" t="s">
-        <v>280</v>
+        <v>111</v>
       </c>
       <c r="U45" t="s">
         <v>64</v>
@@ -7859,28 +8009,28 @@
         <v>66</v>
       </c>
       <c r="Z45" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="AA45" t="s">
         <v>67</v>
       </c>
       <c r="AB45" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="AC45">
         <v>0</v>
       </c>
       <c r="AD45" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="AE45" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="AF45" s="1">
-        <v>46306.394415243056</v>
+        <v>46307.84565974537</v>
       </c>
       <c r="AG45">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AH45">
         <v>0</v>
@@ -7889,25 +8039,22 @@
         <v>71</v>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK45">
         <v>0</v>
       </c>
       <c r="AL45" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM45">
         <v>0</v>
       </c>
       <c r="AN45" t="s">
-        <v>375</v>
-      </c>
-      <c r="AO45" s="1">
-        <v>46309.96033440972</v>
+        <v>105</v>
       </c>
       <c r="AP45" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AQ45" t="s">
         <v>376</v>
@@ -7922,10 +8069,10 @@
         <v>76</v>
       </c>
       <c r="AU45" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AV45" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:48" x14ac:dyDescent="0.25">
@@ -7933,10 +8080,10 @@
         <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C46" s="2">
-        <v>46307.845660590276</v>
+        <v>46308.689703449076</v>
       </c>
       <c r="D46" t="s">
         <v>377</v>
@@ -7945,25 +8092,25 @@
         <v>378</v>
       </c>
       <c r="G46" t="s">
-        <v>110</v>
+        <v>318</v>
       </c>
       <c r="H46" t="s">
-        <v>111</v>
+        <v>319</v>
       </c>
       <c r="I46" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="J46" t="s">
-        <v>141</v>
+        <v>59</v>
       </c>
       <c r="K46">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
       <c r="M46">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N46" t="s">
         <v>60</v>
@@ -7972,16 +8119,16 @@
         <v>61</v>
       </c>
       <c r="P46" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="Q46" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="T46" t="s">
-        <v>114</v>
+        <v>336</v>
       </c>
       <c r="U46" t="s">
-        <v>64</v>
+        <v>163</v>
       </c>
       <c r="V46">
         <v>1</v>
@@ -7993,37 +8140,37 @@
         <v>66</v>
       </c>
       <c r="Z46" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="AA46" t="s">
         <v>67</v>
       </c>
       <c r="AB46" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="AC46">
         <v>0</v>
       </c>
       <c r="AD46" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="AE46" t="s">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="AF46" s="1">
-        <v>46307.84565974537</v>
+        <v>46308.689703449076</v>
       </c>
       <c r="AG46">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH46">
         <v>0</v>
       </c>
       <c r="AI46" t="s">
-        <v>71</v>
+        <v>166</v>
       </c>
       <c r="AJ46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK46">
         <v>0</v>
@@ -8035,13 +8182,13 @@
         <v>0</v>
       </c>
       <c r="AN46" t="s">
-        <v>105</v>
+        <v>380</v>
       </c>
       <c r="AP46" t="s">
         <v>106</v>
       </c>
       <c r="AQ46" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AR46" t="s">
         <v>65</v>
@@ -8053,7 +8200,7 @@
         <v>76</v>
       </c>
       <c r="AU46" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AV46" t="s">
         <v>65</v>
@@ -8064,28 +8211,31 @@
         <v>41</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="C47" s="2">
-        <v>46308.689703449076</v>
+        <v>46308.724995983794</v>
       </c>
       <c r="D47" t="s">
-        <v>381</v>
+        <v>382</v>
+      </c>
+      <c r="E47" t="s">
+        <v>383</v>
       </c>
       <c r="F47" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G47" t="s">
-        <v>326</v>
+        <v>385</v>
       </c>
       <c r="H47" t="s">
-        <v>327</v>
+        <v>172</v>
       </c>
       <c r="I47" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="J47" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -8094,7 +8244,7 @@
         <v>0</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" t="s">
         <v>60</v>
@@ -8103,16 +8253,16 @@
         <v>61</v>
       </c>
       <c r="P47" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q47" t="s">
         <v>87</v>
       </c>
-      <c r="Q47" t="s">
-        <v>88</v>
-      </c>
       <c r="T47" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="U47" t="s">
-        <v>164</v>
+        <v>64</v>
       </c>
       <c r="V47">
         <v>1</v>
@@ -8130,7 +8280,7 @@
         <v>67</v>
       </c>
       <c r="AB47" t="s">
-        <v>165</v>
+        <v>68</v>
       </c>
       <c r="AC47">
         <v>0</v>
@@ -8139,19 +8289,19 @@
         <v>69</v>
       </c>
       <c r="AE47" t="s">
-        <v>167</v>
+        <v>88</v>
       </c>
       <c r="AF47" s="1">
-        <v>46308.689703449076</v>
+        <v>46308.308068101855</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH47">
         <v>0</v>
       </c>
       <c r="AI47" t="s">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="AJ47">
         <v>0</v>
@@ -8160,19 +8310,22 @@
         <v>0</v>
       </c>
       <c r="AL47" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AM47">
         <v>0</v>
       </c>
       <c r="AN47" t="s">
-        <v>385</v>
+        <v>387</v>
+      </c>
+      <c r="AO47" s="1">
+        <v>46309.598431041668</v>
       </c>
       <c r="AP47" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="AQ47" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AR47" t="s">
         <v>65</v>
@@ -8184,7 +8337,7 @@
         <v>76</v>
       </c>
       <c r="AU47" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AV47" t="s">
         <v>65</v>
@@ -8195,31 +8348,31 @@
         <v>42</v>
       </c>
       <c r="B48" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="C48" s="2">
-        <v>46308.724995983794</v>
+        <v>46308.791972488427</v>
       </c>
       <c r="D48" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E48" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F48" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G48" t="s">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s">
-        <v>173</v>
+        <v>83</v>
       </c>
       <c r="I48" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="J48" t="s">
-        <v>86</v>
+        <v>392</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -8228,7 +8381,7 @@
         <v>0</v>
       </c>
       <c r="M48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N48" t="s">
         <v>60</v>
@@ -8237,13 +8390,13 @@
         <v>61</v>
       </c>
       <c r="P48" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q48" t="s">
         <v>87</v>
       </c>
-      <c r="Q48" t="s">
-        <v>88</v>
-      </c>
       <c r="T48" t="s">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="U48" t="s">
         <v>64</v>
@@ -8270,13 +8423,13 @@
         <v>0</v>
       </c>
       <c r="AD48" t="s">
-        <v>69</v>
+        <v>393</v>
       </c>
       <c r="AE48" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF48" s="1">
-        <v>46308.308068101855</v>
+        <v>46308.254661377316</v>
       </c>
       <c r="AG48">
         <v>1</v>
@@ -8294,22 +8447,22 @@
         <v>0</v>
       </c>
       <c r="AL48" t="s">
-        <v>391</v>
+        <v>89</v>
       </c>
       <c r="AM48">
         <v>0</v>
       </c>
       <c r="AN48" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO48" s="1">
-        <v>46309.598431041668</v>
+        <v>46311.951288958335</v>
       </c>
       <c r="AP48" t="s">
         <v>74</v>
       </c>
       <c r="AQ48" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AR48" t="s">
         <v>65</v>
@@ -8321,7 +8474,7 @@
         <v>76</v>
       </c>
       <c r="AU48" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AV48" t="s">
         <v>65</v>
@@ -8332,31 +8485,31 @@
         <v>43</v>
       </c>
       <c r="B49" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="C49" s="2">
-        <v>46308.791972488427</v>
+        <v>46308.841964930558</v>
       </c>
       <c r="D49" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E49" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F49" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G49" t="s">
-        <v>83</v>
+        <v>399</v>
       </c>
       <c r="H49" t="s">
-        <v>84</v>
+        <v>400</v>
       </c>
       <c r="I49" t="s">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="J49" t="s">
-        <v>397</v>
+        <v>59</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -8365,7 +8518,7 @@
         <v>0</v>
       </c>
       <c r="M49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N49" t="s">
         <v>60</v>
@@ -8374,13 +8527,13 @@
         <v>61</v>
       </c>
       <c r="P49" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q49" t="s">
         <v>87</v>
       </c>
-      <c r="Q49" t="s">
-        <v>88</v>
-      </c>
       <c r="T49" t="s">
-        <v>83</v>
+        <v>399</v>
       </c>
       <c r="U49" t="s">
         <v>64</v>
@@ -8407,13 +8560,13 @@
         <v>0</v>
       </c>
       <c r="AD49" t="s">
-        <v>398</v>
+        <v>69</v>
       </c>
       <c r="AE49" t="s">
-        <v>89</v>
+        <v>200</v>
       </c>
       <c r="AF49" s="1">
-        <v>46308.254661377316</v>
+        <v>46308.585931307869</v>
       </c>
       <c r="AG49">
         <v>1</v>
@@ -8422,7 +8575,7 @@
         <v>0</v>
       </c>
       <c r="AI49" t="s">
-        <v>71</v>
+        <v>401</v>
       </c>
       <c r="AJ49">
         <v>0</v>
@@ -8431,22 +8584,22 @@
         <v>0</v>
       </c>
       <c r="AL49" t="s">
-        <v>90</v>
+        <v>402</v>
       </c>
       <c r="AM49">
         <v>0</v>
       </c>
       <c r="AN49" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="AO49" s="1">
-        <v>46311.951288958335</v>
+        <v>46310.11667166667</v>
       </c>
       <c r="AP49" t="s">
         <v>74</v>
       </c>
       <c r="AQ49" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AR49" t="s">
         <v>65</v>
@@ -8469,31 +8622,28 @@
         <v>44</v>
       </c>
       <c r="B50" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C50" s="2">
-        <v>46308.841964930558</v>
+        <v>46308.912080636575</v>
       </c>
       <c r="D50" t="s">
-        <v>401</v>
-      </c>
-      <c r="E50" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F50" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="G50" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
       <c r="H50" t="s">
-        <v>405</v>
+        <v>172</v>
       </c>
       <c r="I50" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="J50" t="s">
-        <v>59</v>
+        <v>406</v>
       </c>
       <c r="K50">
         <v>0</v>
@@ -8511,13 +8661,16 @@
         <v>61</v>
       </c>
       <c r="P50" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q50" t="s">
         <v>87</v>
       </c>
-      <c r="Q50" t="s">
-        <v>88</v>
+      <c r="R50" t="s">
+        <v>407</v>
       </c>
       <c r="T50" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
       <c r="U50" t="s">
         <v>64</v>
@@ -8538,52 +8691,49 @@
         <v>67</v>
       </c>
       <c r="AB50" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="AC50">
         <v>0</v>
       </c>
       <c r="AD50" t="s">
-        <v>69</v>
+        <v>165</v>
       </c>
       <c r="AE50" t="s">
-        <v>200</v>
+        <v>88</v>
       </c>
       <c r="AF50" s="1">
-        <v>46308.585931307869</v>
+        <v>46308.912080196758</v>
       </c>
       <c r="AG50">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AH50">
         <v>0</v>
       </c>
       <c r="AI50" t="s">
-        <v>406</v>
+        <v>71</v>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK50">
         <v>0</v>
       </c>
       <c r="AL50" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AM50">
         <v>0</v>
       </c>
       <c r="AN50" t="s">
-        <v>399</v>
-      </c>
-      <c r="AO50" s="1">
-        <v>46310.11667166667</v>
+        <v>105</v>
       </c>
       <c r="AP50" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AQ50" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AR50" t="s">
         <v>65</v>
@@ -8595,7 +8745,7 @@
         <v>76</v>
       </c>
       <c r="AU50" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AV50" t="s">
         <v>65</v>
@@ -8606,28 +8756,28 @@
         <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="C51" s="2">
-        <v>46308.912080636575</v>
+        <v>46309.345147569446</v>
       </c>
       <c r="D51" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F51" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G51" t="s">
-        <v>390</v>
+        <v>159</v>
       </c>
       <c r="H51" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="I51" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="J51" t="s">
-        <v>411</v>
+        <v>161</v>
       </c>
       <c r="K51">
         <v>0</v>
@@ -8645,16 +8795,16 @@
         <v>61</v>
       </c>
       <c r="P51" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="Q51" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="R51" t="s">
         <v>412</v>
       </c>
       <c r="T51" t="s">
-        <v>390</v>
+        <v>159</v>
       </c>
       <c r="U51" t="s">
         <v>64</v>
@@ -8675,22 +8825,22 @@
         <v>67</v>
       </c>
       <c r="AB51" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC51">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="s">
         <v>165</v>
       </c>
-      <c r="AC51">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="s">
-        <v>166</v>
-      </c>
       <c r="AE51" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="AF51" s="1">
-        <v>46308.912080196758</v>
+        <v>46309.345146840278</v>
       </c>
       <c r="AG51">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AH51">
         <v>0</v>
@@ -8699,7 +8849,7 @@
         <v>71</v>
       </c>
       <c r="AJ51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK51">
         <v>0</v>
@@ -8713,8 +8863,11 @@
       <c r="AN51" t="s">
         <v>105</v>
       </c>
+      <c r="AO51" s="1">
+        <v>46312.972784641206</v>
+      </c>
       <c r="AP51" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="AQ51" t="s">
         <v>414</v>
@@ -8729,7 +8882,7 @@
         <v>76</v>
       </c>
       <c r="AU51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AV51" t="s">
         <v>65</v>
@@ -8740,10 +8893,10 @@
         <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="C52" s="2">
-        <v>46309.345147569446</v>
+        <v>46309.623780254631</v>
       </c>
       <c r="D52" t="s">
         <v>415</v>
@@ -8752,16 +8905,16 @@
         <v>416</v>
       </c>
       <c r="G52" t="s">
-        <v>160</v>
+        <v>249</v>
       </c>
       <c r="H52" t="s">
-        <v>161</v>
+        <v>250</v>
       </c>
       <c r="I52" t="s">
-        <v>85</v>
+        <v>251</v>
       </c>
       <c r="J52" t="s">
-        <v>162</v>
+        <v>417</v>
       </c>
       <c r="K52">
         <v>0</v>
@@ -8770,7 +8923,7 @@
         <v>0</v>
       </c>
       <c r="M52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N52" t="s">
         <v>60</v>
@@ -8779,16 +8932,16 @@
         <v>61</v>
       </c>
       <c r="P52" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="Q52" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="R52" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="T52" t="s">
-        <v>160</v>
+        <v>249</v>
       </c>
       <c r="U52" t="s">
         <v>64</v>
@@ -8809,37 +8962,37 @@
         <v>67</v>
       </c>
       <c r="AB52" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="AC52">
         <v>0</v>
       </c>
       <c r="AD52" t="s">
-        <v>166</v>
+        <v>419</v>
       </c>
       <c r="AE52" t="s">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="AF52" s="1">
-        <v>46309.345146840278</v>
+        <v>46309.623779895832</v>
       </c>
       <c r="AG52">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="AH52">
         <v>0</v>
       </c>
       <c r="AI52" t="s">
-        <v>71</v>
+        <v>401</v>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK52">
         <v>0</v>
       </c>
       <c r="AL52" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AM52">
         <v>0</v>
@@ -8847,14 +9000,11 @@
       <c r="AN52" t="s">
         <v>105</v>
       </c>
-      <c r="AO52" s="1">
-        <v>46310.978230243054</v>
-      </c>
       <c r="AP52" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AQ52" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AR52" t="s">
         <v>65</v>
@@ -8866,7 +9016,7 @@
         <v>76</v>
       </c>
       <c r="AU52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AV52" t="s">
         <v>65</v>
@@ -8877,28 +9027,31 @@
         <v>47</v>
       </c>
       <c r="B53" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C53" s="2">
-        <v>46309.623780254631</v>
+        <v>46309.635386435184</v>
       </c>
       <c r="D53" t="s">
-        <v>420</v>
+        <v>422</v>
+      </c>
+      <c r="E53" t="s">
+        <v>423</v>
       </c>
       <c r="F53" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="G53" t="s">
-        <v>258</v>
+        <v>111</v>
       </c>
       <c r="H53" t="s">
-        <v>259</v>
+        <v>112</v>
       </c>
       <c r="I53" t="s">
-        <v>260</v>
+        <v>133</v>
       </c>
       <c r="J53" t="s">
-        <v>422</v>
+        <v>59</v>
       </c>
       <c r="K53">
         <v>0</v>
@@ -8907,7 +9060,7 @@
         <v>0</v>
       </c>
       <c r="M53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N53" t="s">
         <v>60</v>
@@ -8916,16 +9069,13 @@
         <v>61</v>
       </c>
       <c r="P53" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="Q53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R53" t="s">
-        <v>423</v>
+        <v>63</v>
       </c>
       <c r="T53" t="s">
-        <v>258</v>
+        <v>111</v>
       </c>
       <c r="U53" t="s">
         <v>64</v>
@@ -8946,31 +9096,31 @@
         <v>67</v>
       </c>
       <c r="AB53" t="s">
-        <v>165</v>
+        <v>68</v>
       </c>
       <c r="AC53">
         <v>0</v>
       </c>
       <c r="AD53" t="s">
-        <v>424</v>
+        <v>69</v>
       </c>
       <c r="AE53" t="s">
-        <v>328</v>
+        <v>200</v>
       </c>
       <c r="AF53" s="1">
-        <v>46309.623779895832</v>
+        <v>46309.635022604169</v>
       </c>
       <c r="AG53">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="AH53">
         <v>0</v>
       </c>
       <c r="AI53" t="s">
-        <v>406</v>
+        <v>71</v>
       </c>
       <c r="AJ53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK53">
         <v>0</v>
@@ -8982,10 +9132,13 @@
         <v>0</v>
       </c>
       <c r="AN53" t="s">
-        <v>105</v>
+        <v>237</v>
+      </c>
+      <c r="AO53" s="1">
+        <v>46313.360796678244</v>
       </c>
       <c r="AP53" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="AQ53" t="s">
         <v>426</v>
@@ -9000,10 +9153,10 @@
         <v>76</v>
       </c>
       <c r="AU53" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AV53" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:48" x14ac:dyDescent="0.25">
@@ -9011,10 +9164,10 @@
         <v>48</v>
       </c>
       <c r="B54" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C54" s="2">
-        <v>46309.635386435184</v>
+        <v>46309.765710081017</v>
       </c>
       <c r="D54" t="s">
         <v>427</v>
@@ -9026,13 +9179,13 @@
         <v>429</v>
       </c>
       <c r="G54" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="H54" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="I54" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J54" t="s">
         <v>59</v>
@@ -9059,7 +9212,7 @@
         <v>63</v>
       </c>
       <c r="T54" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="U54" t="s">
         <v>64</v>
@@ -9089,10 +9242,10 @@
         <v>69</v>
       </c>
       <c r="AE54" t="s">
-        <v>200</v>
+        <v>88</v>
       </c>
       <c r="AF54" s="1">
-        <v>46309.635022604169</v>
+        <v>46308.667246944446</v>
       </c>
       <c r="AG54">
         <v>1</v>
@@ -9119,7 +9272,7 @@
         <v>237</v>
       </c>
       <c r="AO54" s="1">
-        <v>46311.032022500003</v>
+        <v>46312.958797025465</v>
       </c>
       <c r="AP54" t="s">
         <v>74</v>
@@ -9137,7 +9290,7 @@
         <v>76</v>
       </c>
       <c r="AU54" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AV54" t="s">
         <v>65</v>
@@ -9148,28 +9301,25 @@
         <v>49</v>
       </c>
       <c r="B55" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C55" s="2">
-        <v>46309.765710081017</v>
+        <v>46309.971438715278</v>
       </c>
       <c r="D55" t="s">
         <v>432</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>433</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
+        <v>159</v>
+      </c>
+      <c r="H55" t="s">
+        <v>160</v>
+      </c>
+      <c r="I55" t="s">
         <v>434</v>
-      </c>
-      <c r="G55" t="s">
-        <v>97</v>
-      </c>
-      <c r="H55" t="s">
-        <v>98</v>
-      </c>
-      <c r="I55" t="s">
-        <v>134</v>
       </c>
       <c r="J55" t="s">
         <v>59</v>
@@ -9181,7 +9331,7 @@
         <v>0</v>
       </c>
       <c r="M55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N55" t="s">
         <v>60</v>
@@ -9189,17 +9339,8 @@
       <c r="O55" t="s">
         <v>61</v>
       </c>
-      <c r="P55" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>63</v>
-      </c>
-      <c r="T55" t="s">
-        <v>97</v>
-      </c>
       <c r="U55" t="s">
-        <v>64</v>
+        <v>163</v>
       </c>
       <c r="V55">
         <v>1</v>
@@ -9217,28 +9358,25 @@
         <v>67</v>
       </c>
       <c r="AB55" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC55">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="AD55" t="s">
         <v>69</v>
       </c>
       <c r="AE55" t="s">
-        <v>89</v>
+        <v>166</v>
       </c>
       <c r="AF55" s="1">
-        <v>46308.667246944446</v>
+        <v>46309.971438715278</v>
       </c>
       <c r="AG55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH55">
         <v>0</v>
       </c>
       <c r="AI55" t="s">
-        <v>71</v>
+        <v>166</v>
       </c>
       <c r="AJ55">
         <v>0</v>
@@ -9253,16 +9391,13 @@
         <v>0</v>
       </c>
       <c r="AN55" t="s">
-        <v>237</v>
-      </c>
-      <c r="AO55" s="1">
-        <v>46312.07108627315</v>
+        <v>73</v>
       </c>
       <c r="AP55" t="s">
-        <v>74</v>
+        <v>436</v>
       </c>
       <c r="AQ55" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AR55" t="s">
         <v>65</v>
@@ -9270,11 +9405,8 @@
       <c r="AS55" t="s">
         <v>65</v>
       </c>
-      <c r="AT55" t="s">
-        <v>76</v>
-      </c>
       <c r="AU55" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AV55" t="s">
         <v>65</v>
@@ -9285,28 +9417,28 @@
         <v>50</v>
       </c>
       <c r="B56" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C56" s="2">
-        <v>46309.971438715278</v>
+        <v>46310.278506562499</v>
       </c>
       <c r="D56" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F56" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G56" t="s">
-        <v>160</v>
+        <v>440</v>
       </c>
       <c r="H56" t="s">
-        <v>161</v>
+        <v>250</v>
       </c>
       <c r="I56" t="s">
-        <v>439</v>
+        <v>84</v>
       </c>
       <c r="J56" t="s">
-        <v>59</v>
+        <v>441</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -9315,7 +9447,7 @@
         <v>0</v>
       </c>
       <c r="M56">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N56" t="s">
         <v>60</v>
@@ -9323,8 +9455,20 @@
       <c r="O56" t="s">
         <v>61</v>
       </c>
+      <c r="P56" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>87</v>
+      </c>
+      <c r="R56" t="s">
+        <v>442</v>
+      </c>
+      <c r="T56" t="s">
+        <v>440</v>
+      </c>
       <c r="U56" t="s">
-        <v>164</v>
+        <v>64</v>
       </c>
       <c r="V56">
         <v>1</v>
@@ -9342,52 +9486,58 @@
         <v>67</v>
       </c>
       <c r="AB56" t="s">
+        <v>164</v>
+      </c>
+      <c r="AC56">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="s">
         <v>165</v>
       </c>
-      <c r="AD56" t="s">
-        <v>69</v>
-      </c>
       <c r="AE56" t="s">
-        <v>167</v>
+        <v>88</v>
       </c>
       <c r="AF56" s="1">
-        <v>46309.971438715278</v>
+        <v>46310.278506053241</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH56">
         <v>0</v>
       </c>
       <c r="AI56" t="s">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK56">
         <v>0</v>
       </c>
       <c r="AL56" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AM56">
         <v>0</v>
       </c>
       <c r="AN56" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="AP56" t="s">
-        <v>441</v>
+        <v>106</v>
       </c>
       <c r="AQ56" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AR56" t="s">
         <v>65</v>
       </c>
       <c r="AS56" t="s">
         <v>65</v>
+      </c>
+      <c r="AT56" t="s">
+        <v>76</v>
       </c>
       <c r="AU56" t="s">
         <v>77</v>
@@ -9401,28 +9551,28 @@
         <v>51</v>
       </c>
       <c r="B57" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C57" s="2">
         <v>46310.345687685185</v>
       </c>
       <c r="D57" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F57" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G57" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H57" t="s">
         <v>188</v>
       </c>
       <c r="I57" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J57" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K57">
         <v>67</v>
@@ -9446,10 +9596,10 @@
         <v>63</v>
       </c>
       <c r="R57" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="T57" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="U57" t="s">
         <v>64</v>
@@ -9464,22 +9614,22 @@
         <v>66</v>
       </c>
       <c r="Z57" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AA57" t="s">
         <v>67</v>
       </c>
       <c r="AB57" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC57">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="s">
         <v>116</v>
       </c>
-      <c r="AC57">
-        <v>0</v>
-      </c>
-      <c r="AD57" t="s">
-        <v>117</v>
-      </c>
       <c r="AE57" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="AF57" s="1">
         <v>46310.345687245368</v>
@@ -9500,7 +9650,7 @@
         <v>0</v>
       </c>
       <c r="AL57" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AM57">
         <v>0</v>
@@ -9512,7 +9662,7 @@
         <v>106</v>
       </c>
       <c r="AQ57" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AR57" t="s">
         <v>65</v>
@@ -9535,28 +9685,28 @@
         <v>52</v>
       </c>
       <c r="B58" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C58" s="2">
         <v>46310.360796608795</v>
       </c>
       <c r="D58" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="F58" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="G58" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="H58" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="I58" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J58" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="K58">
         <v>10</v>
@@ -9574,19 +9724,19 @@
         <v>61</v>
       </c>
       <c r="P58" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q58" t="s">
         <v>87</v>
       </c>
-      <c r="Q58" t="s">
-        <v>88</v>
-      </c>
       <c r="R58" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="S58" t="s">
         <v>231</v>
       </c>
       <c r="T58" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="U58" t="s">
         <v>64</v>
@@ -9601,22 +9751,22 @@
         <v>66</v>
       </c>
       <c r="Z58" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AA58" t="s">
         <v>67</v>
       </c>
       <c r="AB58" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC58">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="s">
         <v>116</v>
       </c>
-      <c r="AC58">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="s">
+      <c r="AE58" t="s">
         <v>117</v>
-      </c>
-      <c r="AE58" t="s">
-        <v>118</v>
       </c>
       <c r="AF58" s="1">
         <v>46310.360796064815</v>
@@ -9637,7 +9787,7 @@
         <v>0</v>
       </c>
       <c r="AL58" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AM58">
         <v>0</v>
@@ -9649,7 +9799,7 @@
         <v>106</v>
       </c>
       <c r="AQ58" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AR58" t="s">
         <v>65</v>
@@ -9672,16 +9822,16 @@
         <v>53</v>
       </c>
       <c r="B59" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C59" s="2">
         <v>46310.365529490744</v>
       </c>
       <c r="D59" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F59" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="G59" t="s">
         <v>228</v>
@@ -9690,13 +9840,13 @@
         <v>229</v>
       </c>
       <c r="I59" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J59" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -9717,7 +9867,7 @@
         <v>63</v>
       </c>
       <c r="R59" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="S59" t="s">
         <v>231</v>
@@ -9738,7 +9888,7 @@
         <v>66</v>
       </c>
       <c r="Y59" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="Z59" t="s">
         <v>65</v>
@@ -9747,16 +9897,16 @@
         <v>67</v>
       </c>
       <c r="AB59" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC59">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="s">
         <v>165</v>
       </c>
-      <c r="AC59">
-        <v>0</v>
-      </c>
-      <c r="AD59" t="s">
-        <v>166</v>
-      </c>
       <c r="AE59" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF59" s="1">
         <v>46310.364017199077</v>
@@ -9777,7 +9927,7 @@
         <v>0</v>
       </c>
       <c r="AL59" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AM59">
         <v>0</v>
@@ -9789,7 +9939,7 @@
         <v>74</v>
       </c>
       <c r="AQ59" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AR59" t="s">
         <v>65</v>
@@ -9804,7 +9954,7 @@
         <v>77</v>
       </c>
       <c r="AV59" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60" spans="1:48" x14ac:dyDescent="0.25">
@@ -9812,28 +9962,28 @@
         <v>54</v>
       </c>
       <c r="B60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C60" s="2">
         <v>46310.367131909719</v>
       </c>
       <c r="D60" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F60" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="G60" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="H60" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="I60" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J60" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="K60">
         <v>3</v>
@@ -9857,7 +10007,7 @@
         <v>63</v>
       </c>
       <c r="T60" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="U60" t="s">
         <v>64</v>
@@ -9872,22 +10022,22 @@
         <v>66</v>
       </c>
       <c r="Z60" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AA60" t="s">
         <v>67</v>
       </c>
       <c r="AB60" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC60">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="s">
         <v>116</v>
       </c>
-      <c r="AC60">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="s">
-        <v>117</v>
-      </c>
       <c r="AE60" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="AF60" s="1">
         <v>46310.367131481478</v>
@@ -9899,7 +10049,7 @@
         <v>1</v>
       </c>
       <c r="AI60" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="AJ60">
         <v>1</v>
@@ -9908,7 +10058,7 @@
         <v>0</v>
       </c>
       <c r="AL60" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AM60">
         <v>0</v>
@@ -9920,7 +10070,7 @@
         <v>106</v>
       </c>
       <c r="AQ60" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="AR60" t="s">
         <v>65</v>
@@ -9943,31 +10093,31 @@
         <v>55</v>
       </c>
       <c r="B61" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C61" s="2">
         <v>46310.386779826389</v>
       </c>
       <c r="D61" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F61" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="G61" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="H61" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I61" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J61" t="s">
         <v>222</v>
       </c>
       <c r="K61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -9988,10 +10138,10 @@
         <v>63</v>
       </c>
       <c r="R61" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="T61" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="U61" t="s">
         <v>64</v>
@@ -10012,16 +10162,16 @@
         <v>67</v>
       </c>
       <c r="AB61" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="AC61">
         <v>0</v>
       </c>
       <c r="AD61" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AE61" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF61" s="1">
         <v>46310.386627222222</v>
@@ -10042,7 +10192,7 @@
         <v>0</v>
       </c>
       <c r="AL61" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AM61">
         <v>0</v>
@@ -10050,14 +10200,11 @@
       <c r="AN61" t="s">
         <v>105</v>
       </c>
-      <c r="AO61" s="1">
-        <v>46311.235778055554</v>
-      </c>
       <c r="AP61" t="s">
         <v>74</v>
       </c>
       <c r="AQ61" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AR61" t="s">
         <v>65</v>
@@ -10069,10 +10216,10 @@
         <v>76</v>
       </c>
       <c r="AU61" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AV61" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62" spans="1:48" x14ac:dyDescent="0.25">
@@ -10080,37 +10227,37 @@
         <v>56</v>
       </c>
       <c r="B62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C62" s="2">
-        <v>46310.545142060182</v>
+        <v>46310.390056909724</v>
       </c>
       <c r="D62" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F62" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="G62" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="H62" t="s">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="I62" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="J62" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L62">
         <v>0</v>
       </c>
       <c r="M62">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="N62" t="s">
         <v>60</v>
@@ -10125,13 +10272,10 @@
         <v>63</v>
       </c>
       <c r="R62" t="s">
-        <v>479</v>
-      </c>
-      <c r="S62" t="s">
-        <v>155</v>
+        <v>482</v>
       </c>
       <c r="T62" t="s">
-        <v>480</v>
+        <v>291</v>
       </c>
       <c r="U62" t="s">
         <v>64</v>
@@ -10145,47 +10289,44 @@
       <c r="X62" t="s">
         <v>66</v>
       </c>
-      <c r="Y62" t="s">
-        <v>481</v>
-      </c>
       <c r="Z62" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="AA62" t="s">
         <v>67</v>
       </c>
       <c r="AB62" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="AC62">
         <v>0</v>
       </c>
       <c r="AD62" t="s">
-        <v>482</v>
+        <v>143</v>
       </c>
       <c r="AE62" t="s">
-        <v>328</v>
+        <v>127</v>
       </c>
       <c r="AF62" s="1">
-        <v>46310.545141655093</v>
+        <v>46310.390056412034</v>
       </c>
       <c r="AG62">
-        <v>2005</v>
+        <v>7</v>
       </c>
       <c r="AH62">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ62">
+        <v>1</v>
+      </c>
+      <c r="AK62">
+        <v>0</v>
+      </c>
+      <c r="AL62" t="s">
         <v>483</v>
-      </c>
-      <c r="AJ62">
-        <v>147</v>
-      </c>
-      <c r="AK62">
-        <v>0</v>
-      </c>
-      <c r="AL62" t="s">
-        <v>484</v>
       </c>
       <c r="AM62">
         <v>0</v>
@@ -10193,14 +10334,11 @@
       <c r="AN62" t="s">
         <v>105</v>
       </c>
-      <c r="AO62" s="1">
-        <v>46311.501728425923</v>
-      </c>
       <c r="AP62" t="s">
         <v>106</v>
       </c>
       <c r="AQ62" t="s">
-        <v>107</v>
+        <v>484</v>
       </c>
       <c r="AR62" t="s">
         <v>65</v>
@@ -10215,7 +10353,7 @@
         <v>77</v>
       </c>
       <c r="AV62" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
     </row>
     <row r="63" spans="1:48" x14ac:dyDescent="0.25">
@@ -10223,31 +10361,28 @@
         <v>57</v>
       </c>
       <c r="B63" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="C63" s="2">
-        <v>46310.548003460652</v>
+        <v>46310.411839733795</v>
       </c>
       <c r="D63" t="s">
         <v>485</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63">
+        <v>20615648</v>
+      </c>
+      <c r="G63" t="s">
         <v>486</v>
       </c>
-      <c r="F63" t="s">
+      <c r="H63" t="s">
         <v>487</v>
       </c>
-      <c r="G63" t="s">
-        <v>172</v>
-      </c>
-      <c r="H63" t="s">
-        <v>173</v>
-      </c>
       <c r="I63" t="s">
-        <v>85</v>
+        <v>488</v>
       </c>
       <c r="J63" t="s">
-        <v>86</v>
+        <v>489</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -10265,13 +10400,16 @@
         <v>61</v>
       </c>
       <c r="P63" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q63" t="s">
         <v>87</v>
       </c>
-      <c r="Q63" t="s">
-        <v>88</v>
+      <c r="R63" t="s">
+        <v>490</v>
       </c>
       <c r="T63" t="s">
-        <v>172</v>
+        <v>486</v>
       </c>
       <c r="U63" t="s">
         <v>64</v>
@@ -10292,19 +10430,19 @@
         <v>67</v>
       </c>
       <c r="AB63" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="AC63">
         <v>0</v>
       </c>
       <c r="AD63" t="s">
-        <v>69</v>
+        <v>165</v>
       </c>
       <c r="AE63" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF63" s="1">
-        <v>46310.293574374999</v>
+        <v>46310.411839247688</v>
       </c>
       <c r="AG63">
         <v>1</v>
@@ -10313,7 +10451,7 @@
         <v>0</v>
       </c>
       <c r="AI63" t="s">
-        <v>406</v>
+        <v>71</v>
       </c>
       <c r="AJ63">
         <v>0</v>
@@ -10322,22 +10460,19 @@
         <v>0</v>
       </c>
       <c r="AL63" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AM63">
         <v>0</v>
       </c>
       <c r="AN63" t="s">
-        <v>91</v>
-      </c>
-      <c r="AO63" s="1">
-        <v>46310.501391770835</v>
+        <v>105</v>
       </c>
       <c r="AP63" t="s">
         <v>74</v>
       </c>
       <c r="AQ63" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AR63" t="s">
         <v>65</v>
@@ -10349,7 +10484,7 @@
         <v>76</v>
       </c>
       <c r="AU63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AV63" t="s">
         <v>65</v>
@@ -10360,32 +10495,32 @@
         <v>58</v>
       </c>
       <c r="B64" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="C64" s="2">
-        <v>46310.550791365742</v>
+        <v>46310.548003460652</v>
       </c>
       <c r="D64" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E64" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F64" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="G64" t="s">
-        <v>110</v>
+        <v>171</v>
       </c>
       <c r="H64" t="s">
-        <v>111</v>
+        <v>172</v>
       </c>
       <c r="I64" t="s">
+        <v>84</v>
+      </c>
+      <c r="J64" t="s">
         <v>85</v>
       </c>
-      <c r="J64" t="s">
-        <v>59</v>
-      </c>
       <c r="K64">
         <v>0</v>
       </c>
@@ -10393,7 +10528,7 @@
         <v>0</v>
       </c>
       <c r="M64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N64" t="s">
         <v>60</v>
@@ -10402,13 +10537,13 @@
         <v>61</v>
       </c>
       <c r="P64" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="Q64" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="T64" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="U64" t="s">
         <v>64</v>
@@ -10438,10 +10573,10 @@
         <v>69</v>
       </c>
       <c r="AE64" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="AF64" s="1">
-        <v>46310.374097511572</v>
+        <v>46310.293574374999</v>
       </c>
       <c r="AG64">
         <v>1</v>
@@ -10450,7 +10585,7 @@
         <v>0</v>
       </c>
       <c r="AI64" t="s">
-        <v>71</v>
+        <v>401</v>
       </c>
       <c r="AJ64">
         <v>0</v>
@@ -10459,22 +10594,22 @@
         <v>0</v>
       </c>
       <c r="AL64" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="AM64">
         <v>0</v>
       </c>
       <c r="AN64" t="s">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="AO64" s="1">
-        <v>46310.482646111108</v>
+        <v>46310.501391770835</v>
       </c>
       <c r="AP64" t="s">
         <v>74</v>
       </c>
       <c r="AQ64" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AR64" t="s">
         <v>65</v>
@@ -10486,7 +10621,7 @@
         <v>76</v>
       </c>
       <c r="AU64" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AV64" t="s">
         <v>65</v>
@@ -10497,31 +10632,34 @@
         <v>59</v>
       </c>
       <c r="B65" t="s">
-        <v>495</v>
+        <v>130</v>
       </c>
       <c r="C65" s="2">
-        <v>46310.585787812503</v>
+        <v>46310.550791365742</v>
       </c>
       <c r="D65" t="s">
-        <v>496</v>
+        <v>498</v>
+      </c>
+      <c r="E65" t="s">
+        <v>499</v>
       </c>
       <c r="F65" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="G65" t="s">
-        <v>498</v>
+        <v>111</v>
       </c>
       <c r="H65" t="s">
-        <v>468</v>
+        <v>112</v>
       </c>
       <c r="I65" t="s">
-        <v>196</v>
+        <v>84</v>
       </c>
       <c r="J65" t="s">
-        <v>335</v>
+        <v>59</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -10536,16 +10674,16 @@
         <v>61</v>
       </c>
       <c r="P65" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="Q65" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="T65" t="s">
-        <v>499</v>
+        <v>111</v>
       </c>
       <c r="U65" t="s">
-        <v>164</v>
+        <v>64</v>
       </c>
       <c r="V65">
         <v>1</v>
@@ -10563,28 +10701,28 @@
         <v>67</v>
       </c>
       <c r="AB65" t="s">
-        <v>165</v>
+        <v>101</v>
       </c>
       <c r="AC65">
         <v>0</v>
       </c>
       <c r="AD65" t="s">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="AE65" t="s">
-        <v>167</v>
+        <v>70</v>
       </c>
       <c r="AF65" s="1">
-        <v>46310.585787812503</v>
+        <v>46310.374097511572</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH65">
         <v>0</v>
       </c>
       <c r="AI65" t="s">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="AJ65">
         <v>0</v>
@@ -10593,16 +10731,16 @@
         <v>0</v>
       </c>
       <c r="AL65" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM65">
         <v>0</v>
       </c>
       <c r="AN65" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AP65" t="s">
-        <v>501</v>
+        <v>74</v>
       </c>
       <c r="AQ65" t="s">
         <v>502</v>
@@ -10620,7 +10758,7 @@
         <v>77</v>
       </c>
       <c r="AV65" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="66" spans="1:48" x14ac:dyDescent="0.25">
@@ -10628,37 +10766,37 @@
         <v>60</v>
       </c>
       <c r="B66" t="s">
-        <v>94</v>
+        <v>503</v>
       </c>
       <c r="C66" s="2">
-        <v>46311.382125937504</v>
+        <v>46310.585787812503</v>
       </c>
       <c r="D66" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F66" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G66" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H66" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="I66" t="s">
-        <v>112</v>
+        <v>196</v>
       </c>
       <c r="J66" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="K66">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L66">
         <v>0</v>
       </c>
       <c r="M66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N66" t="s">
         <v>60</v>
@@ -10667,19 +10805,16 @@
         <v>61</v>
       </c>
       <c r="P66" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="Q66" t="s">
-        <v>63</v>
-      </c>
-      <c r="R66" t="s">
-        <v>506</v>
+        <v>87</v>
       </c>
       <c r="T66" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="U66" t="s">
-        <v>64</v>
+        <v>163</v>
       </c>
       <c r="V66">
         <v>1</v>
@@ -10691,55 +10826,55 @@
         <v>66</v>
       </c>
       <c r="Z66" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="AA66" t="s">
         <v>67</v>
       </c>
       <c r="AB66" t="s">
+        <v>164</v>
+      </c>
+      <c r="AC66">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="s">
         <v>116</v>
       </c>
-      <c r="AC66">
-        <v>0</v>
-      </c>
-      <c r="AD66" t="s">
-        <v>117</v>
-      </c>
       <c r="AE66" t="s">
-        <v>328</v>
+        <v>166</v>
       </c>
       <c r="AF66" s="1">
-        <v>46311.382125277778</v>
+        <v>46310.585787812503</v>
       </c>
       <c r="AG66">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH66">
         <v>0</v>
       </c>
       <c r="AI66" t="s">
-        <v>406</v>
+        <v>166</v>
       </c>
       <c r="AJ66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK66">
         <v>0</v>
       </c>
       <c r="AL66" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AM66">
         <v>0</v>
       </c>
       <c r="AN66" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="AP66" t="s">
-        <v>106</v>
+        <v>509</v>
       </c>
       <c r="AQ66" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AR66" t="s">
         <v>65</v>
@@ -10762,37 +10897,37 @@
         <v>61</v>
       </c>
       <c r="B67" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="C67" s="2">
-        <v>46311.493548206017</v>
+        <v>46311.341283402777</v>
       </c>
       <c r="D67" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F67" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="G67" t="s">
-        <v>83</v>
+        <v>311</v>
       </c>
       <c r="H67" t="s">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="I67" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="J67" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="K67">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L67">
         <v>0</v>
       </c>
       <c r="M67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N67" t="s">
         <v>60</v>
@@ -10801,16 +10936,13 @@
         <v>61</v>
       </c>
       <c r="P67" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="Q67" t="s">
-        <v>88</v>
-      </c>
-      <c r="R67">
-        <v>65557835</v>
+        <v>63</v>
       </c>
       <c r="T67" t="s">
-        <v>83</v>
+        <v>311</v>
       </c>
       <c r="U67" t="s">
         <v>64</v>
@@ -10825,28 +10957,28 @@
         <v>66</v>
       </c>
       <c r="Z67" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="AA67" t="s">
         <v>67</v>
       </c>
       <c r="AB67" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="AC67">
         <v>0</v>
       </c>
       <c r="AD67" t="s">
-        <v>166</v>
+        <v>514</v>
       </c>
       <c r="AE67" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="AF67" s="1">
-        <v>46311.493545960649</v>
+        <v>46311.341282905094</v>
       </c>
       <c r="AG67">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH67">
         <v>0</v>
@@ -10855,13 +10987,13 @@
         <v>71</v>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK67">
         <v>0</v>
       </c>
       <c r="AL67" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AM67">
         <v>0</v>
@@ -10869,14 +11001,11 @@
       <c r="AN67" t="s">
         <v>105</v>
       </c>
-      <c r="AO67" s="1">
-        <v>46311.951299652777</v>
-      </c>
       <c r="AP67" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AQ67" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AR67" t="s">
         <v>65</v>
@@ -10891,7 +11020,7 @@
         <v>77</v>
       </c>
       <c r="AV67" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="68" spans="1:48" x14ac:dyDescent="0.25">
@@ -10899,34 +11028,37 @@
         <v>62</v>
       </c>
       <c r="B68" t="s">
-        <v>514</v>
+        <v>93</v>
       </c>
       <c r="C68" s="2">
-        <v>46311.551411377317</v>
+        <v>46311.382125937504</v>
       </c>
       <c r="D68" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F68" t="s">
-        <v>479</v>
+        <v>518</v>
+      </c>
+      <c r="G68" t="s">
+        <v>519</v>
       </c>
       <c r="H68" t="s">
-        <v>153</v>
+        <v>471</v>
       </c>
       <c r="I68" t="s">
-        <v>516</v>
+        <v>113</v>
       </c>
       <c r="J68" t="s">
-        <v>517</v>
+        <v>327</v>
       </c>
       <c r="K68">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L68">
         <v>0</v>
       </c>
       <c r="M68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N68" t="s">
         <v>60</v>
@@ -10940,14 +11072,14 @@
       <c r="Q68" t="s">
         <v>63</v>
       </c>
-      <c r="S68" t="s">
-        <v>237</v>
+      <c r="R68" t="s">
+        <v>520</v>
       </c>
       <c r="T68" t="s">
-        <v>114</v>
+        <v>519</v>
       </c>
       <c r="U68" t="s">
-        <v>164</v>
+        <v>64</v>
       </c>
       <c r="V68">
         <v>1</v>
@@ -10959,58 +11091,64 @@
         <v>66</v>
       </c>
       <c r="Z68" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="AA68" t="s">
         <v>67</v>
       </c>
       <c r="AB68" t="s">
-        <v>165</v>
+        <v>101</v>
       </c>
       <c r="AC68">
         <v>0</v>
       </c>
       <c r="AD68" t="s">
-        <v>518</v>
+        <v>116</v>
       </c>
       <c r="AE68" t="s">
-        <v>167</v>
+        <v>320</v>
       </c>
       <c r="AF68" s="1">
-        <v>46311.551411377317</v>
+        <v>46311.382125277778</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH68">
         <v>0</v>
       </c>
       <c r="AI68" t="s">
-        <v>167</v>
+        <v>401</v>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK68">
         <v>0</v>
       </c>
       <c r="AL68" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AM68">
         <v>0</v>
       </c>
       <c r="AN68" t="s">
-        <v>155</v>
+        <v>105</v>
       </c>
       <c r="AP68" t="s">
-        <v>520</v>
+        <v>106</v>
+      </c>
+      <c r="AQ68" t="s">
+        <v>522</v>
       </c>
       <c r="AR68" t="s">
         <v>65</v>
       </c>
       <c r="AS68" t="s">
         <v>65</v>
+      </c>
+      <c r="AT68" t="s">
+        <v>76</v>
       </c>
       <c r="AU68" t="s">
         <v>77</v>
@@ -11024,34 +11162,31 @@
         <v>63</v>
       </c>
       <c r="B69" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="C69" s="2">
-        <v>46311.632166111114</v>
+        <v>46311.413829895835</v>
       </c>
       <c r="D69" t="s">
-        <v>521</v>
-      </c>
-      <c r="E69" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F69" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G69" t="s">
-        <v>258</v>
+        <v>159</v>
       </c>
       <c r="H69" t="s">
-        <v>259</v>
+        <v>160</v>
       </c>
       <c r="I69" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="J69" t="s">
-        <v>86</v>
+        <v>222</v>
       </c>
       <c r="K69">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L69">
         <v>0</v>
@@ -11066,13 +11201,16 @@
         <v>61</v>
       </c>
       <c r="P69" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="Q69" t="s">
-        <v>88</v>
+        <v>63</v>
+      </c>
+      <c r="R69" t="s">
+        <v>525</v>
       </c>
       <c r="T69" t="s">
-        <v>258</v>
+        <v>159</v>
       </c>
       <c r="U69" t="s">
         <v>64</v>
@@ -11087,28 +11225,28 @@
         <v>66</v>
       </c>
       <c r="Z69" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="AA69" t="s">
         <v>67</v>
       </c>
       <c r="AB69" t="s">
-        <v>165</v>
+        <v>101</v>
       </c>
       <c r="AC69">
         <v>0</v>
       </c>
       <c r="AD69" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="AE69" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="AF69" s="1">
-        <v>46310.403628622684</v>
+        <v>46311.413829895835</v>
       </c>
       <c r="AG69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH69">
         <v>0</v>
@@ -11117,25 +11255,25 @@
         <v>71</v>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK69">
         <v>0</v>
       </c>
       <c r="AL69" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AM69">
         <v>0</v>
       </c>
       <c r="AN69" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="AP69" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AQ69" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AR69" t="s">
         <v>65</v>
@@ -11150,7 +11288,7 @@
         <v>77</v>
       </c>
       <c r="AV69" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="70" spans="1:48" x14ac:dyDescent="0.25">
@@ -11158,31 +11296,28 @@
         <v>64</v>
       </c>
       <c r="B70" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C70" s="2">
-        <v>46311.634805428243</v>
+        <v>46311.493548206017</v>
       </c>
       <c r="D70" t="s">
-        <v>526</v>
-      </c>
-      <c r="E70" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F70" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G70" t="s">
-        <v>529</v>
+        <v>82</v>
       </c>
       <c r="H70" t="s">
+        <v>83</v>
+      </c>
+      <c r="I70" t="s">
+        <v>133</v>
+      </c>
+      <c r="J70" t="s">
         <v>530</v>
-      </c>
-      <c r="I70" t="s">
-        <v>85</v>
-      </c>
-      <c r="J70" t="s">
-        <v>86</v>
       </c>
       <c r="K70">
         <v>0</v>
@@ -11200,13 +11335,16 @@
         <v>61</v>
       </c>
       <c r="P70" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q70" t="s">
         <v>87</v>
       </c>
-      <c r="Q70" t="s">
-        <v>88</v>
+      <c r="R70">
+        <v>65557835</v>
       </c>
       <c r="T70" t="s">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="U70" t="s">
         <v>64</v>
@@ -11233,13 +11371,13 @@
         <v>0</v>
       </c>
       <c r="AD70" t="s">
-        <v>69</v>
+        <v>165</v>
       </c>
       <c r="AE70" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF70" s="1">
-        <v>46310.849041469904</v>
+        <v>46311.493545960649</v>
       </c>
       <c r="AG70">
         <v>1</v>
@@ -11263,16 +11401,16 @@
         <v>0</v>
       </c>
       <c r="AN70" t="s">
-        <v>532</v>
+        <v>105</v>
       </c>
       <c r="AO70" s="1">
-        <v>46311.555555567131</v>
+        <v>46311.951299652777</v>
       </c>
       <c r="AP70" t="s">
         <v>74</v>
       </c>
       <c r="AQ70" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AR70" t="s">
         <v>65</v>
@@ -11288,6 +11426,1209 @@
       </c>
       <c r="AV70" t="s">
         <v>65</v>
+      </c>
+    </row>
+    <row r="71" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>65</v>
+      </c>
+      <c r="B71" t="s">
+        <v>533</v>
+      </c>
+      <c r="C71" s="2">
+        <v>46311.551411377317</v>
+      </c>
+      <c r="D71" t="s">
+        <v>534</v>
+      </c>
+      <c r="F71" t="s">
+        <v>535</v>
+      </c>
+      <c r="H71" t="s">
+        <v>152</v>
+      </c>
+      <c r="I71" t="s">
+        <v>536</v>
+      </c>
+      <c r="J71" t="s">
+        <v>537</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71" t="s">
+        <v>60</v>
+      </c>
+      <c r="O71" t="s">
+        <v>61</v>
+      </c>
+      <c r="P71" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>63</v>
+      </c>
+      <c r="S71" t="s">
+        <v>237</v>
+      </c>
+      <c r="T71" t="s">
+        <v>111</v>
+      </c>
+      <c r="U71" t="s">
+        <v>163</v>
+      </c>
+      <c r="V71">
+        <v>1</v>
+      </c>
+      <c r="W71" t="s">
+        <v>65</v>
+      </c>
+      <c r="X71" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA71" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB71" t="s">
+        <v>164</v>
+      </c>
+      <c r="AC71">
+        <v>0</v>
+      </c>
+      <c r="AD71" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE71" t="s">
+        <v>166</v>
+      </c>
+      <c r="AF71" s="1">
+        <v>46311.551411377317</v>
+      </c>
+      <c r="AG71">
+        <v>0</v>
+      </c>
+      <c r="AH71">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="s">
+        <v>166</v>
+      </c>
+      <c r="AJ71">
+        <v>0</v>
+      </c>
+      <c r="AK71">
+        <v>0</v>
+      </c>
+      <c r="AL71" t="s">
+        <v>538</v>
+      </c>
+      <c r="AM71">
+        <v>0</v>
+      </c>
+      <c r="AN71" t="s">
+        <v>154</v>
+      </c>
+      <c r="AP71" t="s">
+        <v>539</v>
+      </c>
+      <c r="AR71" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS71" t="s">
+        <v>65</v>
+      </c>
+      <c r="AU71" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV71" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="72" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>66</v>
+      </c>
+      <c r="B72" t="s">
+        <v>130</v>
+      </c>
+      <c r="C72" s="2">
+        <v>46311.632166111114</v>
+      </c>
+      <c r="D72" t="s">
+        <v>540</v>
+      </c>
+      <c r="E72" t="s">
+        <v>541</v>
+      </c>
+      <c r="F72" t="s">
+        <v>542</v>
+      </c>
+      <c r="G72" t="s">
+        <v>249</v>
+      </c>
+      <c r="H72" t="s">
+        <v>250</v>
+      </c>
+      <c r="I72" t="s">
+        <v>84</v>
+      </c>
+      <c r="J72" t="s">
+        <v>85</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>1</v>
+      </c>
+      <c r="N72" t="s">
+        <v>60</v>
+      </c>
+      <c r="O72" t="s">
+        <v>61</v>
+      </c>
+      <c r="P72" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>87</v>
+      </c>
+      <c r="T72" t="s">
+        <v>249</v>
+      </c>
+      <c r="U72" t="s">
+        <v>64</v>
+      </c>
+      <c r="V72">
+        <v>1</v>
+      </c>
+      <c r="W72" t="s">
+        <v>65</v>
+      </c>
+      <c r="X72" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA72" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB72" t="s">
+        <v>164</v>
+      </c>
+      <c r="AC72">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE72" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF72" s="1">
+        <v>46310.403628622684</v>
+      </c>
+      <c r="AG72">
+        <v>1</v>
+      </c>
+      <c r="AH72">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ72">
+        <v>0</v>
+      </c>
+      <c r="AK72">
+        <v>0</v>
+      </c>
+      <c r="AL72" t="s">
+        <v>543</v>
+      </c>
+      <c r="AM72">
+        <v>0</v>
+      </c>
+      <c r="AN72" t="s">
+        <v>73</v>
+      </c>
+      <c r="AP72" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ72" t="s">
+        <v>544</v>
+      </c>
+      <c r="AR72" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS72" t="s">
+        <v>65</v>
+      </c>
+      <c r="AT72" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU72" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV72" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="73" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>67</v>
+      </c>
+      <c r="B73" t="s">
+        <v>130</v>
+      </c>
+      <c r="C73" s="2">
+        <v>46311.634805428243</v>
+      </c>
+      <c r="D73" t="s">
+        <v>545</v>
+      </c>
+      <c r="E73" t="s">
+        <v>546</v>
+      </c>
+      <c r="F73" t="s">
+        <v>547</v>
+      </c>
+      <c r="G73" t="s">
+        <v>548</v>
+      </c>
+      <c r="H73" t="s">
+        <v>549</v>
+      </c>
+      <c r="I73" t="s">
+        <v>84</v>
+      </c>
+      <c r="J73" t="s">
+        <v>85</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>1</v>
+      </c>
+      <c r="N73" t="s">
+        <v>60</v>
+      </c>
+      <c r="O73" t="s">
+        <v>61</v>
+      </c>
+      <c r="P73" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>87</v>
+      </c>
+      <c r="T73" t="s">
+        <v>171</v>
+      </c>
+      <c r="U73" t="s">
+        <v>64</v>
+      </c>
+      <c r="V73">
+        <v>1</v>
+      </c>
+      <c r="W73" t="s">
+        <v>65</v>
+      </c>
+      <c r="X73" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA73" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB73" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC73">
+        <v>0</v>
+      </c>
+      <c r="AD73" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE73" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF73" s="1">
+        <v>46310.849041469904</v>
+      </c>
+      <c r="AG73">
+        <v>1</v>
+      </c>
+      <c r="AH73">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ73">
+        <v>0</v>
+      </c>
+      <c r="AK73">
+        <v>0</v>
+      </c>
+      <c r="AL73" t="s">
+        <v>550</v>
+      </c>
+      <c r="AM73">
+        <v>0</v>
+      </c>
+      <c r="AN73" t="s">
+        <v>551</v>
+      </c>
+      <c r="AO73" s="1">
+        <v>46312.687442256945</v>
+      </c>
+      <c r="AP73" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ73" t="s">
+        <v>552</v>
+      </c>
+      <c r="AR73" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS73" t="s">
+        <v>65</v>
+      </c>
+      <c r="AT73" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU73" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV73" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="74" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>68</v>
+      </c>
+      <c r="B74" t="s">
+        <v>93</v>
+      </c>
+      <c r="C74" s="2">
+        <v>46312.487674421296</v>
+      </c>
+      <c r="D74" t="s">
+        <v>553</v>
+      </c>
+      <c r="E74" t="s">
+        <v>554</v>
+      </c>
+      <c r="F74" t="s">
+        <v>555</v>
+      </c>
+      <c r="G74" t="s">
+        <v>96</v>
+      </c>
+      <c r="H74" t="s">
+        <v>97</v>
+      </c>
+      <c r="I74" t="s">
+        <v>133</v>
+      </c>
+      <c r="J74" t="s">
+        <v>59</v>
+      </c>
+      <c r="K74">
+        <v>6</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74" t="s">
+        <v>60</v>
+      </c>
+      <c r="O74" t="s">
+        <v>61</v>
+      </c>
+      <c r="P74" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>63</v>
+      </c>
+      <c r="R74" t="s">
+        <v>555</v>
+      </c>
+      <c r="T74" t="s">
+        <v>96</v>
+      </c>
+      <c r="U74" t="s">
+        <v>64</v>
+      </c>
+      <c r="V74">
+        <v>1</v>
+      </c>
+      <c r="W74" t="s">
+        <v>65</v>
+      </c>
+      <c r="X74" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA74" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB74" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC74">
+        <v>0</v>
+      </c>
+      <c r="AD74" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE74" t="s">
+        <v>127</v>
+      </c>
+      <c r="AF74" s="1">
+        <v>46311.296268333332</v>
+      </c>
+      <c r="AG74">
+        <v>6</v>
+      </c>
+      <c r="AH74">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ74">
+        <v>1</v>
+      </c>
+      <c r="AK74">
+        <v>0</v>
+      </c>
+      <c r="AL74" t="s">
+        <v>556</v>
+      </c>
+      <c r="AM74">
+        <v>0</v>
+      </c>
+      <c r="AN74" t="s">
+        <v>557</v>
+      </c>
+      <c r="AP74" t="s">
+        <v>106</v>
+      </c>
+      <c r="AQ74" t="s">
+        <v>558</v>
+      </c>
+      <c r="AR74" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS74" t="s">
+        <v>65</v>
+      </c>
+      <c r="AT74" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU74" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV74" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="75" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>69</v>
+      </c>
+      <c r="B75" t="s">
+        <v>130</v>
+      </c>
+      <c r="C75" s="2">
+        <v>46312.491727199071</v>
+      </c>
+      <c r="D75" t="s">
+        <v>559</v>
+      </c>
+      <c r="F75" t="s">
+        <v>560</v>
+      </c>
+      <c r="G75" t="s">
+        <v>272</v>
+      </c>
+      <c r="H75" t="s">
+        <v>273</v>
+      </c>
+      <c r="I75" t="s">
+        <v>488</v>
+      </c>
+      <c r="J75" t="s">
+        <v>530</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>1</v>
+      </c>
+      <c r="N75" t="s">
+        <v>60</v>
+      </c>
+      <c r="O75" t="s">
+        <v>61</v>
+      </c>
+      <c r="P75" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>87</v>
+      </c>
+      <c r="R75">
+        <v>65570793</v>
+      </c>
+      <c r="T75" t="s">
+        <v>272</v>
+      </c>
+      <c r="U75" t="s">
+        <v>64</v>
+      </c>
+      <c r="V75">
+        <v>1</v>
+      </c>
+      <c r="W75" t="s">
+        <v>65</v>
+      </c>
+      <c r="X75" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA75" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB75" t="s">
+        <v>164</v>
+      </c>
+      <c r="AC75">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE75" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF75" s="1">
+        <v>46312.491726481479</v>
+      </c>
+      <c r="AG75">
+        <v>1</v>
+      </c>
+      <c r="AH75">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ75">
+        <v>0</v>
+      </c>
+      <c r="AK75">
+        <v>0</v>
+      </c>
+      <c r="AL75" t="s">
+        <v>561</v>
+      </c>
+      <c r="AM75">
+        <v>0</v>
+      </c>
+      <c r="AN75" t="s">
+        <v>105</v>
+      </c>
+      <c r="AP75" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ75" t="s">
+        <v>562</v>
+      </c>
+      <c r="AR75" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS75" t="s">
+        <v>65</v>
+      </c>
+      <c r="AT75" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU75" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV75" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="76" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>70</v>
+      </c>
+      <c r="B76" t="s">
+        <v>130</v>
+      </c>
+      <c r="C76" s="2">
+        <v>46312.566487696757</v>
+      </c>
+      <c r="D76" t="s">
+        <v>563</v>
+      </c>
+      <c r="F76" t="s">
+        <v>564</v>
+      </c>
+      <c r="G76" t="s">
+        <v>475</v>
+      </c>
+      <c r="H76" t="s">
+        <v>160</v>
+      </c>
+      <c r="I76" t="s">
+        <v>488</v>
+      </c>
+      <c r="J76" t="s">
+        <v>59</v>
+      </c>
+      <c r="K76">
+        <v>32</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>1</v>
+      </c>
+      <c r="N76" t="s">
+        <v>60</v>
+      </c>
+      <c r="O76" t="s">
+        <v>61</v>
+      </c>
+      <c r="P76" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>63</v>
+      </c>
+      <c r="T76" t="s">
+        <v>475</v>
+      </c>
+      <c r="U76" t="s">
+        <v>64</v>
+      </c>
+      <c r="V76">
+        <v>4</v>
+      </c>
+      <c r="W76" t="s">
+        <v>65</v>
+      </c>
+      <c r="X76" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA76" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB76" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC76">
+        <v>0</v>
+      </c>
+      <c r="AD76" t="s">
+        <v>393</v>
+      </c>
+      <c r="AE76" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF76" s="1">
+        <v>46312.566486979165</v>
+      </c>
+      <c r="AG76">
+        <v>32</v>
+      </c>
+      <c r="AH76">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ76">
+        <v>1</v>
+      </c>
+      <c r="AK76">
+        <v>0</v>
+      </c>
+      <c r="AL76" t="s">
+        <v>565</v>
+      </c>
+      <c r="AM76">
+        <v>0</v>
+      </c>
+      <c r="AN76" t="s">
+        <v>105</v>
+      </c>
+      <c r="AP76" t="s">
+        <v>106</v>
+      </c>
+      <c r="AQ76" t="s">
+        <v>566</v>
+      </c>
+      <c r="AR76" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS76" t="s">
+        <v>65</v>
+      </c>
+      <c r="AT76" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU76" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV76" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="77" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>71</v>
+      </c>
+      <c r="B77" t="s">
+        <v>130</v>
+      </c>
+      <c r="C77" s="2">
+        <v>46312.662956203705</v>
+      </c>
+      <c r="D77" t="s">
+        <v>567</v>
+      </c>
+      <c r="E77" t="s">
+        <v>568</v>
+      </c>
+      <c r="F77" t="s">
+        <v>569</v>
+      </c>
+      <c r="G77" t="s">
+        <v>486</v>
+      </c>
+      <c r="H77" t="s">
+        <v>487</v>
+      </c>
+      <c r="I77" t="s">
+        <v>84</v>
+      </c>
+      <c r="J77" t="s">
+        <v>85</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>1</v>
+      </c>
+      <c r="N77" t="s">
+        <v>60</v>
+      </c>
+      <c r="O77" t="s">
+        <v>61</v>
+      </c>
+      <c r="P77" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>87</v>
+      </c>
+      <c r="T77" t="s">
+        <v>486</v>
+      </c>
+      <c r="U77" t="s">
+        <v>64</v>
+      </c>
+      <c r="V77">
+        <v>1</v>
+      </c>
+      <c r="W77" t="s">
+        <v>65</v>
+      </c>
+      <c r="X77" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA77" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB77" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC77">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE77" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF77" s="1">
+        <v>46311.328909097225</v>
+      </c>
+      <c r="AG77">
+        <v>1</v>
+      </c>
+      <c r="AH77">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ77">
+        <v>0</v>
+      </c>
+      <c r="AK77">
+        <v>0</v>
+      </c>
+      <c r="AL77" t="s">
+        <v>570</v>
+      </c>
+      <c r="AM77">
+        <v>0</v>
+      </c>
+      <c r="AN77" t="s">
+        <v>237</v>
+      </c>
+      <c r="AO77" s="1">
+        <v>46312.625000011576</v>
+      </c>
+      <c r="AP77" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ77" t="s">
+        <v>571</v>
+      </c>
+      <c r="AR77" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS77" t="s">
+        <v>65</v>
+      </c>
+      <c r="AT77" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU77" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV77" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="78" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>72</v>
+      </c>
+      <c r="B78" t="s">
+        <v>93</v>
+      </c>
+      <c r="C78" s="2">
+        <v>46312.826678194448</v>
+      </c>
+      <c r="D78" t="s">
+        <v>572</v>
+      </c>
+      <c r="F78" t="s">
+        <v>573</v>
+      </c>
+      <c r="G78" t="s">
+        <v>574</v>
+      </c>
+      <c r="H78" t="s">
+        <v>575</v>
+      </c>
+      <c r="I78" t="s">
+        <v>576</v>
+      </c>
+      <c r="J78" t="s">
+        <v>577</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>1</v>
+      </c>
+      <c r="N78" t="s">
+        <v>60</v>
+      </c>
+      <c r="O78" t="s">
+        <v>61</v>
+      </c>
+      <c r="P78" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>87</v>
+      </c>
+      <c r="S78" t="s">
+        <v>231</v>
+      </c>
+      <c r="T78" t="s">
+        <v>574</v>
+      </c>
+      <c r="U78" t="s">
+        <v>64</v>
+      </c>
+      <c r="V78">
+        <v>1</v>
+      </c>
+      <c r="W78" t="s">
+        <v>65</v>
+      </c>
+      <c r="X78" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA78" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB78" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC78">
+        <v>0</v>
+      </c>
+      <c r="AD78" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE78" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF78" s="1">
+        <v>46312.826677488425</v>
+      </c>
+      <c r="AG78">
+        <v>34</v>
+      </c>
+      <c r="AH78">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ78">
+        <v>1</v>
+      </c>
+      <c r="AK78">
+        <v>0</v>
+      </c>
+      <c r="AL78" t="s">
+        <v>578</v>
+      </c>
+      <c r="AM78">
+        <v>0</v>
+      </c>
+      <c r="AN78" t="s">
+        <v>105</v>
+      </c>
+      <c r="AO78" s="1">
+        <v>46313.009765740739</v>
+      </c>
+      <c r="AP78" t="s">
+        <v>106</v>
+      </c>
+      <c r="AQ78" t="s">
+        <v>579</v>
+      </c>
+      <c r="AR78" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS78" t="s">
+        <v>65</v>
+      </c>
+      <c r="AT78" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU78" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV78" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="79" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>73</v>
+      </c>
+      <c r="B79" t="s">
+        <v>580</v>
+      </c>
+      <c r="C79" s="2">
+        <v>46312.920849895832</v>
+      </c>
+      <c r="D79" t="s">
+        <v>581</v>
+      </c>
+      <c r="F79" t="s">
+        <v>582</v>
+      </c>
+      <c r="G79" t="s">
+        <v>583</v>
+      </c>
+      <c r="H79" t="s">
+        <v>160</v>
+      </c>
+      <c r="I79" t="s">
+        <v>196</v>
+      </c>
+      <c r="J79" t="s">
+        <v>584</v>
+      </c>
+      <c r="K79">
+        <v>1251</v>
+      </c>
+      <c r="L79">
+        <v>24</v>
+      </c>
+      <c r="M79">
+        <v>22</v>
+      </c>
+      <c r="N79" t="s">
+        <v>60</v>
+      </c>
+      <c r="O79" t="s">
+        <v>61</v>
+      </c>
+      <c r="P79" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>63</v>
+      </c>
+      <c r="T79" t="s">
+        <v>583</v>
+      </c>
+      <c r="U79" t="s">
+        <v>64</v>
+      </c>
+      <c r="V79">
+        <v>1</v>
+      </c>
+      <c r="W79" t="s">
+        <v>65</v>
+      </c>
+      <c r="X79" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA79" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB79" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC79">
+        <v>0</v>
+      </c>
+      <c r="AD79" t="s">
+        <v>585</v>
+      </c>
+      <c r="AE79" t="s">
+        <v>320</v>
+      </c>
+      <c r="AF79" s="1">
+        <v>46312.926802106478</v>
+      </c>
+      <c r="AG79">
+        <v>1251</v>
+      </c>
+      <c r="AH79">
+        <v>24</v>
+      </c>
+      <c r="AI79" t="s">
+        <v>103</v>
+      </c>
+      <c r="AJ79">
+        <v>92</v>
+      </c>
+      <c r="AK79">
+        <v>0</v>
+      </c>
+      <c r="AL79" t="s">
+        <v>586</v>
+      </c>
+      <c r="AM79">
+        <v>0</v>
+      </c>
+      <c r="AN79" t="s">
+        <v>371</v>
+      </c>
+      <c r="AP79" t="s">
+        <v>509</v>
+      </c>
+      <c r="AQ79" t="s">
+        <v>587</v>
+      </c>
+      <c r="AR79" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS79" t="s">
+        <v>65</v>
+      </c>
+      <c r="AT79" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU79" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV79" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
